--- a/factor_test/outputs/03_regression_fusion_implication.xlsx
+++ b/factor_test/outputs/03_regression_fusion_implication.xlsx
@@ -478,25 +478,25 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.03361841827575535</v>
+        <v>0.01492296767960774</v>
       </c>
       <c r="C2" t="n">
-        <v>0.04643983463951914</v>
+        <v>0.1043345881613297</v>
       </c>
       <c r="D2" t="n">
-        <v>0.01050764907121231</v>
+        <v>0.01597091218720414</v>
       </c>
       <c r="E2" t="n">
-        <v>4.419621775031469</v>
+        <v>6.532788292764036</v>
       </c>
       <c r="F2" t="n">
-        <v>1.053094243861236e-05</v>
+        <v>8.84133133869321e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>0.01168571363683513</v>
+        <v>0.02789955910294706</v>
       </c>
       <c r="H2" t="n">
-        <v>1654</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="3">
@@ -506,25 +506,25 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>-0.01748533754127997</v>
+        <v>0.1466894813203405</v>
       </c>
       <c r="C3" t="n">
-        <v>0.002588428696516688</v>
+        <v>-0.007085285300014437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.003055185901260724</v>
+        <v>0.004890123824818537</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8472246142038597</v>
+        <v>-1.44889691014672</v>
       </c>
       <c r="F3" t="n">
-        <v>0.396992656148507</v>
+        <v>0.1475772115829524</v>
       </c>
       <c r="G3" t="n">
-        <v>0.0004343085985112349</v>
+        <v>0.001409779893826846</v>
       </c>
       <c r="H3" t="n">
-        <v>1654</v>
+        <v>1489</v>
       </c>
     </row>
     <row r="4">
@@ -534,25 +534,25 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.2154106801101219</v>
+        <v>0.1713339242023109</v>
       </c>
       <c r="C4" t="n">
-        <v>-8.275638509207081e-05</v>
+        <v>-7.094299891842089e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>7.47859339363577e-05</v>
+        <v>0.0001281514414098948</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.106576875305133</v>
+        <v>-0.5535872100845777</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2686380180002407</v>
+        <v>0.5799446066453109</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0007406812394746831</v>
+        <v>0.0002060495315917565</v>
       </c>
       <c r="H4" t="n">
-        <v>1654</v>
+        <v>1489</v>
       </c>
     </row>
   </sheetData>
@@ -593,7002 +593,7002 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.414213562373095</v>
+        <v>0.1432787014047787</v>
       </c>
       <c r="B2" t="n">
-        <v>1.01</v>
+        <v>0.11</v>
       </c>
       <c r="C2" t="n">
-        <v>22.1865</v>
+        <v>16.9803</v>
       </c>
       <c r="D2" t="n">
-        <v>1888.9207</v>
+        <v>1971.0724</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>-2.061143248883747</v>
+        <v>-0.8432990751343366</v>
       </c>
       <c r="B3" t="n">
-        <v>-0.77</v>
+        <v>-0.1100000000000001</v>
       </c>
       <c r="C3" t="n">
-        <v>21.6174</v>
+        <v>16.8812</v>
       </c>
       <c r="D3" t="n">
-        <v>1892.3936</v>
+        <v>1970.9773</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.08476691808518111</v>
+        <v>-0.5322380063865801</v>
       </c>
       <c r="B4" t="n">
-        <v>-2.15</v>
+        <v>-0.19</v>
       </c>
       <c r="C4" t="n">
-        <v>21.9296</v>
+        <v>16.4876</v>
       </c>
       <c r="D4" t="n">
-        <v>1895.1441</v>
+        <v>1971.4915</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.188553468208906</v>
+        <v>1.978534999955508</v>
       </c>
       <c r="B5" t="n">
-        <v>-0.2</v>
+        <v>1.56</v>
       </c>
       <c r="C5" t="n">
-        <v>20.8552</v>
+        <v>16.7105</v>
       </c>
       <c r="D5" t="n">
-        <v>1896.2931</v>
+        <v>1970.368</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.3852491625387408</v>
+        <v>-0.9401855726676595</v>
       </c>
       <c r="B6" t="n">
-        <v>0.99</v>
+        <v>3.24</v>
       </c>
       <c r="C6" t="n">
-        <v>19.0909</v>
+        <v>16.8382</v>
       </c>
       <c r="D6" t="n">
-        <v>1899.0394</v>
+        <v>1969.4364</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>-0.8153665002384451</v>
+        <v>0.2613019293377339</v>
       </c>
       <c r="B7" t="n">
-        <v>0.23</v>
+        <v>-0.85</v>
       </c>
       <c r="C7" t="n">
-        <v>18.7966</v>
+        <v>17.255</v>
       </c>
       <c r="D7" t="n">
-        <v>1899.8869</v>
+        <v>1968.6791</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.3008606920989415</v>
+        <v>0.3248424052713267</v>
       </c>
       <c r="B8" t="n">
-        <v>0.12</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="C8" t="n">
-        <v>18.1752</v>
+        <v>17.4738</v>
       </c>
       <c r="D8" t="n">
-        <v>1900.7066</v>
+        <v>1969.2818</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>0.3008606920989415</v>
+        <v>1.552453799194589</v>
       </c>
       <c r="B9" t="n">
-        <v>-0.4</v>
+        <v>0.76</v>
       </c>
       <c r="C9" t="n">
-        <v>18.5278</v>
+        <v>16.1107</v>
       </c>
       <c r="D9" t="n">
-        <v>1900.6983</v>
+        <v>1971.1194</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>-1.799885048410433</v>
+        <v>-0.9367829241459608</v>
       </c>
       <c r="B10" t="n">
-        <v>0.9399999999999997</v>
+        <v>-0.9</v>
       </c>
       <c r="C10" t="n">
-        <v>17.7981</v>
+        <v>15.3776</v>
       </c>
       <c r="D10" t="n">
-        <v>1901.1792</v>
+        <v>1971.7492</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1.198438111714983</v>
+        <v>-1.121589111930254</v>
       </c>
       <c r="B11" t="n">
-        <v>0.27</v>
+        <v>-0.9400000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>16.7583</v>
+        <v>15.5586</v>
       </c>
       <c r="D11" t="n">
-        <v>1901.0846</v>
+        <v>1972.4866</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2.239840368426121</v>
+        <v>0.173376443757768</v>
       </c>
       <c r="B12" t="n">
-        <v>0.49</v>
+        <v>1.37</v>
       </c>
       <c r="C12" t="n">
-        <v>17.0658</v>
+        <v>15.8691</v>
       </c>
       <c r="D12" t="n">
-        <v>1902.524</v>
+        <v>1972.5347</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>0.1971675209515937</v>
+        <v>0.5108390461220546</v>
       </c>
       <c r="B13" t="n">
-        <v>1.27</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="C13" t="n">
-        <v>17.5418</v>
+        <v>14.845</v>
       </c>
       <c r="D13" t="n">
-        <v>1903.7499</v>
+        <v>1972.9574</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.1971675209515937</v>
+        <v>-1.094454772112163</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01000000000000001</v>
+        <v>1.53</v>
       </c>
       <c r="C14" t="n">
-        <v>18.9079</v>
+        <v>14.3605</v>
       </c>
       <c r="D14" t="n">
-        <v>1904.381</v>
+        <v>1971.8757</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>-1.176926046457191</v>
+        <v>-1.123100586148675</v>
       </c>
       <c r="B15" t="n">
-        <v>-0.1599999999999999</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C15" t="n">
-        <v>17.44</v>
+        <v>14.2602</v>
       </c>
       <c r="D15" t="n">
-        <v>1902.9833</v>
+        <v>1971.4762</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1.944383215493079</v>
+        <v>-0.626028493321619</v>
       </c>
       <c r="B16" t="n">
-        <v>-0.3100000000000001</v>
+        <v>0.34</v>
       </c>
       <c r="C16" t="n">
-        <v>16.9072</v>
+        <v>14.6497</v>
       </c>
       <c r="D16" t="n">
-        <v>1903.7253</v>
+        <v>1971.8582</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>-0.5269988385508035</v>
+        <v>-0.4581511506990851</v>
       </c>
       <c r="B17" t="n">
-        <v>0.04000000000000004</v>
+        <v>-0.3600000000000001</v>
       </c>
       <c r="C17" t="n">
-        <v>15.3563</v>
+        <v>15.0031</v>
       </c>
       <c r="D17" t="n">
-        <v>1904.4803</v>
+        <v>1970.9095</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>-0.6480201146534511</v>
+        <v>-0.3875675361078739</v>
       </c>
       <c r="B18" t="n">
-        <v>1.85</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="C18" t="n">
-        <v>15.0496</v>
+        <v>14.4608</v>
       </c>
       <c r="D18" t="n">
-        <v>1903.8392</v>
+        <v>1971.5131</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>-0.9696294521794142</v>
+        <v>0.2162556304699118</v>
       </c>
       <c r="B19" t="n">
-        <v>0.6200000000000001</v>
+        <v>-1.09</v>
       </c>
       <c r="C19" t="n">
-        <v>16.5108</v>
+        <v>14.2045</v>
       </c>
       <c r="D19" t="n">
-        <v>1903.6766</v>
+        <v>1971.2666</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>-0.6182215155666134</v>
+        <v>0.61105674820309</v>
       </c>
       <c r="B20" t="n">
-        <v>2.53</v>
+        <v>0.16</v>
       </c>
       <c r="C20" t="n">
-        <v>17.77</v>
+        <v>14.4123</v>
       </c>
       <c r="D20" t="n">
-        <v>1903.7051</v>
+        <v>1970.7765</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>-0.6924979971913017</v>
+        <v>-0.2784824861503322</v>
       </c>
       <c r="B21" t="n">
-        <v>0.84</v>
+        <v>0.35</v>
       </c>
       <c r="C21" t="n">
-        <v>18.6398</v>
+        <v>14.0568</v>
       </c>
       <c r="D21" t="n">
-        <v>1903.692</v>
+        <v>1970.2777</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>-1.200260627272528</v>
+        <v>-0.6369516764528138</v>
       </c>
       <c r="B22" t="n">
-        <v>3.3</v>
+        <v>-0.5</v>
       </c>
       <c r="C22" t="n">
-        <v>18.7143</v>
+        <v>13.7203</v>
       </c>
       <c r="D22" t="n">
-        <v>1904.494</v>
+        <v>1970.6628</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1.077565446575785</v>
+        <v>0.3561746293212177</v>
       </c>
       <c r="B23" t="n">
-        <v>-2.27</v>
+        <v>-1.89</v>
       </c>
       <c r="C23" t="n">
-        <v>19.4313</v>
+        <v>13.8436</v>
       </c>
       <c r="D23" t="n">
-        <v>1906.6792</v>
+        <v>1970.272</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.5956885791433744</v>
+        <v>0.004641218397335736</v>
       </c>
       <c r="B24" t="n">
-        <v>-1.76</v>
+        <v>0.6500000000000001</v>
       </c>
       <c r="C24" t="n">
-        <v>21.287</v>
+        <v>14.0265</v>
       </c>
       <c r="D24" t="n">
-        <v>1911.2194</v>
+        <v>1969.1021</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>0.5956885791433744</v>
+        <v>0.7874204596452424</v>
       </c>
       <c r="B25" t="n">
-        <v>-1.16</v>
+        <v>0.45</v>
       </c>
       <c r="C25" t="n">
-        <v>20.9824</v>
+        <v>14.3101</v>
       </c>
       <c r="D25" t="n">
-        <v>1912.9376</v>
+        <v>1967.4493</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1.059973159514694</v>
+        <v>-0.8842617183048999</v>
       </c>
       <c r="B26" t="n">
-        <v>0.07000000000000006</v>
+        <v>1.21</v>
       </c>
       <c r="C26" t="n">
-        <v>21.5748</v>
+        <v>14.478</v>
       </c>
       <c r="D26" t="n">
-        <v>1915.3333</v>
+        <v>1966.0263</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>-0.09786186457205281</v>
+        <v>-0.178909843363288</v>
       </c>
       <c r="B27" t="n">
-        <v>-0.59</v>
+        <v>0.6700000000000002</v>
       </c>
       <c r="C27" t="n">
-        <v>22.8022</v>
+        <v>13.7086</v>
       </c>
       <c r="D27" t="n">
-        <v>1915.9364</v>
+        <v>1966.9656</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>-0.6564640415888566</v>
+        <v>-3.277896708512825</v>
       </c>
       <c r="B28" t="n">
-        <v>-2.14</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="C28" t="n">
-        <v>23.2502</v>
+        <v>13.8007</v>
       </c>
       <c r="D28" t="n">
-        <v>1915.4371</v>
+        <v>1968.163</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>0.9343966181480083</v>
+        <v>0.796334561773629</v>
       </c>
       <c r="B29" t="n">
-        <v>-0.9499999999999997</v>
+        <v>0.3099999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>23.3874</v>
+        <v>14.0353</v>
       </c>
       <c r="D29" t="n">
-        <v>1918.4736</v>
+        <v>1969.1633</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1.561552010794419</v>
+        <v>-1.14287089624243</v>
       </c>
       <c r="B30" t="n">
-        <v>-0.57</v>
+        <v>0.64</v>
       </c>
       <c r="C30" t="n">
-        <v>24.625</v>
+        <v>13.8457</v>
       </c>
       <c r="D30" t="n">
-        <v>1917.5945</v>
+        <v>1969.7564</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>-0.5537836607102004</v>
+        <v>-0.3149883894659444</v>
       </c>
       <c r="B31" t="n">
-        <v>0.28</v>
+        <v>-0.65</v>
       </c>
       <c r="C31" t="n">
-        <v>25.0891</v>
+        <v>14.0674</v>
       </c>
       <c r="D31" t="n">
-        <v>1917.684</v>
+        <v>1970.628</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.09860032285957332</v>
+        <v>1.69464999659837</v>
       </c>
       <c r="B32" t="n">
-        <v>-0.02999999999999997</v>
+        <v>-0.3499999999999999</v>
       </c>
       <c r="C32" t="n">
-        <v>24.8733</v>
+        <v>14.3448</v>
       </c>
       <c r="D32" t="n">
-        <v>1917.3565</v>
+        <v>1971.1352</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>-0.7622386749796823</v>
+        <v>0.3098291376411997</v>
       </c>
       <c r="B33" t="n">
-        <v>-0.4799999999999998</v>
+        <v>1.05</v>
       </c>
       <c r="C33" t="n">
-        <v>23.4801</v>
+        <v>15.2748</v>
       </c>
       <c r="D33" t="n">
-        <v>1919.0723</v>
+        <v>1970.6331</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>-0.1043608873042068</v>
+        <v>1.016045182150108</v>
       </c>
       <c r="B34" t="n">
-        <v>1.05</v>
+        <v>-0.06</v>
       </c>
       <c r="C34" t="n">
-        <v>26.0385</v>
+        <v>14.7736</v>
       </c>
       <c r="D34" t="n">
-        <v>1924.8382</v>
+        <v>1972.0518</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.1710194941991378</v>
+        <v>0.6303159717087936</v>
       </c>
       <c r="B35" t="n">
-        <v>-1.92</v>
+        <v>0.17</v>
       </c>
       <c r="C35" t="n">
-        <v>31.7251</v>
+        <v>15.0156</v>
       </c>
       <c r="D35" t="n">
-        <v>1921.0194</v>
+        <v>1972.175</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>-0.104636875206999</v>
+        <v>0.8025406523142417</v>
       </c>
       <c r="B36" t="n">
-        <v>0.85</v>
+        <v>-0.65</v>
       </c>
       <c r="C36" t="n">
-        <v>31.4938</v>
+        <v>15.2936</v>
       </c>
       <c r="D36" t="n">
-        <v>1918.5019</v>
+        <v>1973.0004</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>0.04177460801677813</v>
+        <v>0.6388395294761026</v>
       </c>
       <c r="B37" t="n">
-        <v>-0.61</v>
+        <v>0.76</v>
       </c>
       <c r="C37" t="n">
-        <v>29.0075</v>
+        <v>15.2595</v>
       </c>
       <c r="D37" t="n">
-        <v>1919.1127</v>
+        <v>1972.8072</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>-0.02855722506275793</v>
+        <v>-1.089012101440056</v>
       </c>
       <c r="B38" t="n">
-        <v>2.11</v>
+        <v>0.18</v>
       </c>
       <c r="C38" t="n">
-        <v>27.6186</v>
+        <v>14.4413</v>
       </c>
       <c r="D38" t="n">
-        <v>1919.237</v>
+        <v>1974.7561</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.04052705483370163</v>
+        <v>1.180910100416992</v>
       </c>
       <c r="B39" t="n">
-        <v>-1.73</v>
+        <v>-1.21</v>
       </c>
       <c r="C39" t="n">
-        <v>29.8553</v>
+        <v>13.6545</v>
       </c>
       <c r="D39" t="n">
-        <v>1919.6313</v>
+        <v>1977.4015</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>-0.1737578845957237</v>
+        <v>0.6712796578315184</v>
       </c>
       <c r="B40" t="n">
-        <v>-3.27</v>
+        <v>-0.5900000000000001</v>
       </c>
       <c r="C40" t="n">
-        <v>30.6253</v>
+        <v>13.6818</v>
       </c>
       <c r="D40" t="n">
-        <v>1920.1635</v>
+        <v>1977.8773</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>0.2913292460755607</v>
+        <v>-0.5592903769098024</v>
       </c>
       <c r="B41" t="n">
-        <v>-1.77</v>
+        <v>-0.46</v>
       </c>
       <c r="C41" t="n">
-        <v>31.5552</v>
+        <v>13.8587</v>
       </c>
       <c r="D41" t="n">
-        <v>1920.8681</v>
+        <v>1979.3761</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.2323353251012167</v>
+        <v>-0.4691076214726767</v>
       </c>
       <c r="B42" t="n">
-        <v>-3.52</v>
+        <v>0.4</v>
       </c>
       <c r="C42" t="n">
-        <v>32.9032</v>
+        <v>14.401</v>
       </c>
       <c r="D42" t="n">
-        <v>1921.189</v>
+        <v>1979.6186</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.04931316278476838</v>
+        <v>-0.6146597934157247</v>
       </c>
       <c r="B43" t="n">
-        <v>0.4200000000000004</v>
+        <v>1.56</v>
       </c>
       <c r="C43" t="n">
-        <v>33.6253</v>
+        <v>14.3679</v>
       </c>
       <c r="D43" t="n">
-        <v>1919.3108</v>
+        <v>1979.8269</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>-0.1718502538410054</v>
+        <v>0.1987338693880724</v>
       </c>
       <c r="B44" t="n">
-        <v>-3.45</v>
+        <v>-0.09</v>
       </c>
       <c r="C44" t="n">
-        <v>30.3805</v>
+        <v>14.401</v>
       </c>
       <c r="D44" t="n">
-        <v>1923.2172</v>
+        <v>1979.6826</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>0.1436508354338586</v>
+        <v>2.089054043721031</v>
       </c>
       <c r="B45" t="n">
-        <v>-1.8</v>
+        <v>-0.05</v>
       </c>
       <c r="C45" t="n">
-        <v>30.3659</v>
+        <v>14.079</v>
       </c>
       <c r="D45" t="n">
-        <v>1924.4094</v>
+        <v>1980.117</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.1944181069897449</v>
+        <v>-0.5642186387905622</v>
       </c>
       <c r="B46" t="n">
-        <v>2.47</v>
+        <v>-0.18</v>
       </c>
       <c r="C46" t="n">
-        <v>30.2158</v>
+        <v>13.4649</v>
       </c>
       <c r="D46" t="n">
-        <v>1921.9787</v>
+        <v>1980.5624</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>-0.2623551191150261</v>
+        <v>0.6811402411877605</v>
       </c>
       <c r="B47" t="n">
-        <v>3.22</v>
+        <v>-1.13</v>
       </c>
       <c r="C47" t="n">
-        <v>28.8844</v>
+        <v>13.9736</v>
       </c>
       <c r="D47" t="n">
-        <v>1920.3161</v>
+        <v>1980.4471</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.0655166285041377</v>
+        <v>0.939396764948441</v>
       </c>
       <c r="B48" t="n">
-        <v>-0.5700000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="C48" t="n">
-        <v>27.0594</v>
+        <v>13.4182</v>
       </c>
       <c r="D48" t="n">
-        <v>1921.1473</v>
+        <v>1980.7667</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>-0.1092311075636955</v>
+        <v>1.403883172431133</v>
       </c>
       <c r="B49" t="n">
-        <v>0.1099999999999999</v>
+        <v>-0.3</v>
       </c>
       <c r="C49" t="n">
-        <v>27.8545</v>
+        <v>13.1739</v>
       </c>
       <c r="D49" t="n">
-        <v>1924.0893</v>
+        <v>1980.7415</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>-0.03090096975390005</v>
+        <v>1.358114735650127</v>
       </c>
       <c r="B50" t="n">
-        <v>-1.08</v>
+        <v>-0.45</v>
       </c>
       <c r="C50" t="n">
-        <v>28.5048</v>
+        <v>13.2029</v>
       </c>
       <c r="D50" t="n">
-        <v>1924.4825</v>
+        <v>1981.3657</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>0.0905612718989427</v>
+        <v>-0.4989475088194645</v>
       </c>
       <c r="B51" t="n">
-        <v>0.47</v>
+        <v>-0.4099999999999999</v>
       </c>
       <c r="C51" t="n">
-        <v>28.6245</v>
+        <v>12.5676</v>
       </c>
       <c r="D51" t="n">
-        <v>1924.4745</v>
+        <v>1982.4426</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>0.3009471094320664</v>
+        <v>0.9109240154334772</v>
       </c>
       <c r="B52" t="n">
-        <v>-1.44</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="C52" t="n">
-        <v>29.2409</v>
+        <v>12.0093</v>
       </c>
       <c r="D52" t="n">
-        <v>1926.2246</v>
+        <v>1983.1374</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>0.3009471094320664</v>
+        <v>1.251238453707665</v>
       </c>
       <c r="B53" t="n">
-        <v>-0.67</v>
+        <v>-0.59</v>
       </c>
       <c r="C53" t="n">
-        <v>28.8745</v>
+        <v>12.2021</v>
       </c>
       <c r="D53" t="n">
-        <v>1927.4272</v>
+        <v>1983.5884</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>-0.896872937567559</v>
+        <v>-0.2416819222913171</v>
       </c>
       <c r="B54" t="n">
-        <v>-1.88</v>
+        <v>-0.48</v>
       </c>
       <c r="C54" t="n">
-        <v>27.0058</v>
+        <v>12.0622</v>
       </c>
       <c r="D54" t="n">
-        <v>1926.2746</v>
+        <v>1984.0215</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>0.01495045609896439</v>
+        <v>2.988628256674973</v>
       </c>
       <c r="B55" t="n">
-        <v>2.46</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="C55" t="n">
-        <v>25.4424</v>
+        <v>12.3144</v>
       </c>
       <c r="D55" t="n">
-        <v>1925.8938</v>
+        <v>1984.1043</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>-0.6616920559911081</v>
+        <v>0.2482238034698453</v>
       </c>
       <c r="B56" t="n">
-        <v>0.65</v>
+        <v>-0.38</v>
       </c>
       <c r="C56" t="n">
-        <v>24.5866</v>
+        <v>11.9643</v>
       </c>
       <c r="D56" t="n">
-        <v>1927.9613</v>
+        <v>1985.1612</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>-0.4263559813873392</v>
+        <v>-0.6403274339986678</v>
       </c>
       <c r="B57" t="n">
-        <v>1.07</v>
+        <v>0.9699999999999998</v>
       </c>
       <c r="C57" t="n">
-        <v>23.3471</v>
+        <v>13.935</v>
       </c>
       <c r="D57" t="n">
-        <v>1927.7715</v>
+        <v>1986.4188</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>-0.3763203367488381</v>
+        <v>0.3685862374387293</v>
       </c>
       <c r="B58" t="n">
-        <v>0.98</v>
+        <v>-2.12</v>
       </c>
       <c r="C58" t="n">
-        <v>24.445</v>
+        <v>13.2301</v>
       </c>
       <c r="D58" t="n">
-        <v>1932.2696</v>
+        <v>1987.6401</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>-0.685262471808775</v>
+        <v>-0.0505432395336003</v>
       </c>
       <c r="B59" t="n">
-        <v>-1.92</v>
+        <v>-0.1200000000000001</v>
       </c>
       <c r="C59" t="n">
-        <v>26.3128</v>
+        <v>14.0029</v>
       </c>
       <c r="D59" t="n">
-        <v>1934.6936</v>
+        <v>1989.0044</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>-1.287791943810064</v>
+        <v>-0.9053289738953646</v>
       </c>
       <c r="B60" t="n">
-        <v>-0.75</v>
+        <v>-0.21</v>
       </c>
       <c r="C60" t="n">
-        <v>28.6633</v>
+        <v>14.3602</v>
       </c>
       <c r="D60" t="n">
-        <v>1933.7426</v>
+        <v>1988.7177</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>-1.940591170421388</v>
+        <v>-2.340634002678762</v>
       </c>
       <c r="B61" t="n">
-        <v>0.08000000000000007</v>
+        <v>-0.71</v>
       </c>
       <c r="C61" t="n">
-        <v>28.0931</v>
+        <v>14.976</v>
       </c>
       <c r="D61" t="n">
-        <v>1932.8082</v>
+        <v>1989.5088</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>-0.2438224827706575</v>
+        <v>0.1972116234664557</v>
       </c>
       <c r="B62" t="n">
-        <v>0.7300000000000001</v>
+        <v>1.03</v>
       </c>
       <c r="C62" t="n">
-        <v>29.7596</v>
+        <v>14.6729</v>
       </c>
       <c r="D62" t="n">
-        <v>1931.9567</v>
+        <v>1989.5534</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>-0.4490280089109428</v>
+        <v>-0.5151503944804594</v>
       </c>
       <c r="B63" t="n">
-        <v>0.83</v>
+        <v>1.32</v>
       </c>
       <c r="C63" t="n">
-        <v>31.7968</v>
+        <v>13.7589</v>
       </c>
       <c r="D63" t="n">
-        <v>1930.8963</v>
+        <v>1989.4631</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>-0.6333461710723092</v>
+        <v>-0.5086684238147495</v>
       </c>
       <c r="B64" t="n">
-        <v>-0.06</v>
+        <v>-1.34</v>
       </c>
       <c r="C64" t="n">
-        <v>29.9565</v>
+        <v>13.413</v>
       </c>
       <c r="D64" t="n">
-        <v>1929.9908</v>
+        <v>1991.6045</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>-0.9357032174240605</v>
+        <v>-0.2967698114818755</v>
       </c>
       <c r="B65" t="n">
-        <v>0.55</v>
+        <v>-0.96</v>
       </c>
       <c r="C65" t="n">
-        <v>30.1592</v>
+        <v>13.0134</v>
       </c>
       <c r="D65" t="n">
-        <v>1927.9965</v>
+        <v>1992.9504</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>-0.2684185381995599</v>
+        <v>0.993257366187584</v>
       </c>
       <c r="B66" t="n">
-        <v>0.3600000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="C66" t="n">
-        <v>30.056</v>
+        <v>13.2607</v>
       </c>
       <c r="D66" t="n">
-        <v>1925.4047</v>
+        <v>1995.0525</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>-0.563805591330608</v>
+        <v>-1.900511469674768</v>
       </c>
       <c r="B67" t="n">
-        <v>-0.18</v>
+        <v>1.01</v>
       </c>
       <c r="C67" t="n">
-        <v>27.4994</v>
+        <v>13.5736</v>
       </c>
       <c r="D67" t="n">
-        <v>1926.1167</v>
+        <v>1995.9536</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>1.769155022988924</v>
+        <v>2.149282435994132</v>
       </c>
       <c r="B68" t="n">
-        <v>0.9600000000000001</v>
+        <v>0.92</v>
       </c>
       <c r="C68" t="n">
-        <v>27.6013</v>
+        <v>14.5704</v>
       </c>
       <c r="D68" t="n">
-        <v>1922.2801</v>
+        <v>1998.1383</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>-1.070332371338663</v>
+        <v>1.533995460636226</v>
       </c>
       <c r="B69" t="n">
-        <v>1.24</v>
+        <v>-0.65</v>
       </c>
       <c r="C69" t="n">
-        <v>27.4162</v>
+        <v>15.0492</v>
       </c>
       <c r="D69" t="n">
-        <v>1922.8174</v>
+        <v>1998.9271</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>0.9901866855056864</v>
+        <v>0.7280805998076316</v>
       </c>
       <c r="B70" t="n">
         <v>-1.07</v>
       </c>
       <c r="C70" t="n">
-        <v>28.4243</v>
+        <v>15.4504</v>
       </c>
       <c r="D70" t="n">
-        <v>1922.437</v>
+        <v>1999.7239</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>0.5660087219211151</v>
+        <v>2.606994131313207</v>
       </c>
       <c r="B71" t="n">
-        <v>0.09000000000000002</v>
+        <v>-0.9299999999999999</v>
       </c>
       <c r="C71" t="n">
-        <v>28.3375</v>
+        <v>14.9596</v>
       </c>
       <c r="D71" t="n">
-        <v>1922.5264</v>
+        <v>1999.6054</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>-1.055251821151117</v>
+        <v>1.720989922454984</v>
       </c>
       <c r="B72" t="n">
-        <v>0.41</v>
+        <v>-1.73</v>
       </c>
       <c r="C72" t="n">
-        <v>27.8945</v>
+        <v>15.6222</v>
       </c>
       <c r="D72" t="n">
-        <v>1925.3352</v>
+        <v>2000.4161</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>-0.8715482817354572</v>
+        <v>1.881826590022006</v>
       </c>
       <c r="B73" t="n">
-        <v>-1.35</v>
+        <v>-0.96</v>
       </c>
       <c r="C73" t="n">
-        <v>29.1904</v>
+        <v>15.8362</v>
       </c>
       <c r="D73" t="n">
-        <v>1922.462</v>
+        <v>2001.6679</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>1.205343479973152</v>
+        <v>-2.73013044087022</v>
       </c>
       <c r="B74" t="n">
-        <v>2.12</v>
+        <v>0.1900000000000002</v>
       </c>
       <c r="C74" t="n">
-        <v>27.3134</v>
+        <v>16.0295</v>
       </c>
       <c r="D74" t="n">
-        <v>1920.4607</v>
+        <v>2001.5285</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>0.365986959158962</v>
+        <v>0.6049333466844913</v>
       </c>
       <c r="B75" t="n">
-        <v>-1.37</v>
+        <v>-0.6100000000000001</v>
       </c>
       <c r="C75" t="n">
-        <v>26.7863</v>
+        <v>15.3041</v>
       </c>
       <c r="D75" t="n">
-        <v>1920.5589</v>
+        <v>2002.8869</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>0.365986959158962</v>
+        <v>0.3528981328217606</v>
       </c>
       <c r="B76" t="n">
-        <v>2.55</v>
+        <v>0.22</v>
       </c>
       <c r="C76" t="n">
-        <v>26.5321</v>
+        <v>14.8701</v>
       </c>
       <c r="D76" t="n">
-        <v>1917.1638</v>
+        <v>2003.7863</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>0.6797555772049115</v>
+        <v>-0.393272836091097</v>
       </c>
       <c r="B77" t="n">
-        <v>-0.08999999999999986</v>
+        <v>-0.55</v>
       </c>
       <c r="C77" t="n">
-        <v>25.7794</v>
+        <v>15.0204</v>
       </c>
       <c r="D77" t="n">
-        <v>1916.7048</v>
+        <v>2006.0238</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>-1.112723092447153</v>
+        <v>1.49568376274708</v>
       </c>
       <c r="B78" t="n">
-        <v>5.24</v>
+        <v>-0.1</v>
       </c>
       <c r="C78" t="n">
-        <v>25.2741</v>
+        <v>14.1725</v>
       </c>
       <c r="D78" t="n">
-        <v>1915.4698</v>
+        <v>2005.6437</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>0.8290729719443666</v>
+        <v>-0.497123078214145</v>
       </c>
       <c r="B79" t="n">
-        <v>-0.8600000000000001</v>
+        <v>-0.72</v>
       </c>
       <c r="C79" t="n">
-        <v>25.4609</v>
+        <v>14.275</v>
       </c>
       <c r="D79" t="n">
-        <v>1917.0679</v>
+        <v>2005.2127</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>1.534729338546757</v>
+        <v>2.185109867109855</v>
       </c>
       <c r="B80" t="n">
-        <v>2.9</v>
+        <v>-0.3</v>
       </c>
       <c r="C80" t="n">
-        <v>29.5034</v>
+        <v>13.7159</v>
       </c>
       <c r="D80" t="n">
-        <v>1913.2999</v>
+        <v>2005.5256</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>0.837286060099643</v>
+        <v>-2.549624418766129</v>
       </c>
       <c r="B81" t="n">
-        <v>-1.21</v>
+        <v>0.71</v>
       </c>
       <c r="C81" t="n">
-        <v>26.3951</v>
+        <v>13.1982</v>
       </c>
       <c r="D81" t="n">
-        <v>1916.4586</v>
+        <v>2006.2776</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>0.5294177131905539</v>
+        <v>0.2317013274997712</v>
       </c>
       <c r="B82" t="n">
-        <v>-1.34</v>
+        <v>-0.8600000000000001</v>
       </c>
       <c r="C82" t="n">
-        <v>27.5089</v>
+        <v>13.6694</v>
       </c>
       <c r="D82" t="n">
-        <v>1915.8918</v>
+        <v>2008.7983</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>-1.413760807303689</v>
+        <v>-3.074033766628628</v>
       </c>
       <c r="B83" t="n">
-        <v>-1.12</v>
+        <v>-0.87</v>
       </c>
       <c r="C83" t="n">
-        <v>29.5803</v>
+        <v>15.7377</v>
       </c>
       <c r="D83" t="n">
-        <v>1916.3277</v>
+        <v>2008.9715</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2.186353948907219</v>
+        <v>-0.6225966071249447</v>
       </c>
       <c r="B84" t="n">
-        <v>-0.4500000000000002</v>
+        <v>-0.11</v>
       </c>
       <c r="C84" t="n">
-        <v>29.2527</v>
+        <v>15.0123</v>
       </c>
       <c r="D84" t="n">
-        <v>1920.5311</v>
+        <v>2010.5944</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>-0.2538925445305028</v>
+        <v>2.259910748718748</v>
       </c>
       <c r="B85" t="n">
-        <v>-1.15</v>
+        <v>0.8999999999999999</v>
       </c>
       <c r="C85" t="n">
-        <v>28.2002</v>
+        <v>16.7793</v>
       </c>
       <c r="D85" t="n">
-        <v>1920.5219</v>
+        <v>2009.3824</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>-0.1254356160511585</v>
+        <v>-0.6720923754726146</v>
       </c>
       <c r="B86" t="n">
-        <v>0.08999999999999997</v>
+        <v>1.75</v>
       </c>
       <c r="C86" t="n">
-        <v>27.2936</v>
+        <v>19.1026</v>
       </c>
       <c r="D86" t="n">
-        <v>1921.331</v>
+        <v>2017.1592</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>-0.6447591093077882</v>
+        <v>1.425873774569671</v>
       </c>
       <c r="B87" t="n">
-        <v>-0.04000000000000004</v>
+        <v>2.25</v>
       </c>
       <c r="C87" t="n">
-        <v>25.3339</v>
+        <v>23.1268</v>
       </c>
       <c r="D87" t="n">
-        <v>1923.2942</v>
+        <v>2018.5954</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>0.07691763264665269</v>
+        <v>-1.743178174420947</v>
       </c>
       <c r="B88" t="n">
-        <v>-0.47</v>
+        <v>-1.96</v>
       </c>
       <c r="C88" t="n">
-        <v>24.2011</v>
+        <v>20.4829</v>
       </c>
       <c r="D88" t="n">
-        <v>1924.8755</v>
+        <v>2019.4528</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>1.402184244997247</v>
+        <v>0.1095286888175195</v>
       </c>
       <c r="B89" t="n">
-        <v>1.54</v>
+        <v>-1.64</v>
       </c>
       <c r="C89" t="n">
-        <v>24.1478</v>
+        <v>20.6198</v>
       </c>
       <c r="D89" t="n">
-        <v>1922.7918</v>
+        <v>2021.0566</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>-0.2895780661618881</v>
+        <v>-0.3354293067391164</v>
       </c>
       <c r="B90" t="n">
-        <v>-0.39</v>
+        <v>-1.34</v>
       </c>
       <c r="C90" t="n">
-        <v>23.7929</v>
+        <v>21.9349</v>
       </c>
       <c r="D90" t="n">
-        <v>1923.0138</v>
+        <v>2022.8995</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>-0.5610454305077344</v>
+        <v>0.1130377349908665</v>
       </c>
       <c r="B91" t="n">
-        <v>-1.07</v>
+        <v>-1.46</v>
       </c>
       <c r="C91" t="n">
-        <v>22.7716</v>
+        <v>21.531</v>
       </c>
       <c r="D91" t="n">
-        <v>1924.6437</v>
+        <v>2025.4557</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>-0.9531157686668978</v>
+        <v>-1.78192136479876</v>
       </c>
       <c r="B92" t="n">
-        <v>-0.09000000000000002</v>
+        <v>1.73</v>
       </c>
       <c r="C92" t="n">
-        <v>22.019</v>
+        <v>19.7756</v>
       </c>
       <c r="D92" t="n">
-        <v>1923.7753</v>
+        <v>2026.6094</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>-1.755138693034254</v>
+        <v>0.1259111304722211</v>
       </c>
       <c r="B93" t="n">
-        <v>0.9100000000000001</v>
+        <v>-1.78</v>
       </c>
       <c r="C93" t="n">
-        <v>22.2836</v>
+        <v>18.9608</v>
       </c>
       <c r="D93" t="n">
-        <v>1922.0736</v>
+        <v>2027.4278</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>-1.197611072001423</v>
+        <v>0.1096258149475919</v>
       </c>
       <c r="B94" t="n">
-        <v>1.87</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="C94" t="n">
-        <v>22.5634</v>
+        <v>19.4232</v>
       </c>
       <c r="D94" t="n">
-        <v>1922.7303</v>
+        <v>2027.3488</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>1.331700354243431</v>
+        <v>-4.083976521258015</v>
       </c>
       <c r="B95" t="n">
-        <v>-2.21</v>
+        <v>0.3200000000000001</v>
       </c>
       <c r="C95" t="n">
-        <v>23.6039</v>
+        <v>18.5282</v>
       </c>
       <c r="D95" t="n">
-        <v>1923.8999</v>
+        <v>2028.3308</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>-0.4136380195728964</v>
+        <v>-1.880802821330828</v>
       </c>
       <c r="B96" t="n">
-        <v>-0.16</v>
+        <v>-1.74</v>
       </c>
       <c r="C96" t="n">
-        <v>21.7997</v>
+        <v>18.6563</v>
       </c>
       <c r="D96" t="n">
-        <v>1924.7629</v>
+        <v>2030.8458</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>-0.523961590149406</v>
+        <v>1.326987991678542</v>
       </c>
       <c r="B97" t="n">
-        <v>0.17</v>
+        <v>-3.16</v>
       </c>
       <c r="C97" t="n">
-        <v>21.6116</v>
+        <v>18.8297</v>
       </c>
       <c r="D97" t="n">
-        <v>1925.5547</v>
+        <v>2031.1482</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>-0.7042427775357161</v>
+        <v>0.1401010901487027</v>
       </c>
       <c r="B98" t="n">
-        <v>-0.37</v>
+        <v>0.87</v>
       </c>
       <c r="C98" t="n">
-        <v>22.2959</v>
+        <v>19.1301</v>
       </c>
       <c r="D98" t="n">
-        <v>1926.9164</v>
+        <v>2030.8366</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>-0.5372288666914247</v>
+        <v>-0.08693201466061716</v>
       </c>
       <c r="B99" t="n">
-        <v>2</v>
+        <v>-0.06999999999999984</v>
       </c>
       <c r="C99" t="n">
-        <v>22.6035</v>
+        <v>19.3823</v>
       </c>
       <c r="D99" t="n">
-        <v>1926.8073</v>
+        <v>2032.3102</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>-0.3653435316224386</v>
+        <v>-0.3959828203567227</v>
       </c>
       <c r="B100" t="n">
-        <v>1</v>
+        <v>-2.12</v>
       </c>
       <c r="C100" t="n">
-        <v>23.1986</v>
+        <v>20.5533</v>
       </c>
       <c r="D100" t="n">
-        <v>1926.6425</v>
+        <v>2033.7791</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>0.0729890086873381</v>
+        <v>-1.130151308604389</v>
       </c>
       <c r="B101" t="n">
-        <v>-0.009999999999999995</v>
+        <v>-3.47</v>
       </c>
       <c r="C101" t="n">
-        <v>22.7673</v>
+        <v>22.4713</v>
       </c>
       <c r="D101" t="n">
-        <v>1927.7053</v>
+        <v>2035.9974</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>-0.4084049750731659</v>
+        <v>2.226217962799386</v>
       </c>
       <c r="B102" t="n">
-        <v>2</v>
+        <v>-1.13</v>
       </c>
       <c r="C102" t="n">
-        <v>22.8318</v>
+        <v>22.905</v>
       </c>
       <c r="D102" t="n">
-        <v>1926.5422</v>
+        <v>2037.0541</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>-0.8787002183178598</v>
+        <v>3.17250738302406</v>
       </c>
       <c r="B103" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="C103" t="n">
-        <v>21.4491</v>
+        <v>23.5757</v>
       </c>
       <c r="D103" t="n">
-        <v>1928.2001</v>
+        <v>2036.117</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>-0.3223558488404185</v>
+        <v>-3.867499770645587</v>
       </c>
       <c r="B104" t="n">
-        <v>-1.21</v>
+        <v>0.2</v>
       </c>
       <c r="C104" t="n">
-        <v>20.5056</v>
+        <v>20.2366</v>
       </c>
       <c r="D104" t="n">
-        <v>1930.5871</v>
+        <v>2037.8741</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>1.158233709021883</v>
+        <v>-2.714451899716229</v>
       </c>
       <c r="B105" t="n">
-        <v>-0.09999999999999998</v>
+        <v>2.67</v>
       </c>
       <c r="C105" t="n">
-        <v>20.8881</v>
+        <v>23.5348</v>
       </c>
       <c r="D105" t="n">
-        <v>1929.5949</v>
+        <v>2036.5137</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>0.343741686579925</v>
+        <v>-0.3999601097426011</v>
       </c>
       <c r="B106" t="n">
-        <v>-0.64</v>
+        <v>-1.05</v>
       </c>
       <c r="C106" t="n">
-        <v>20.3126</v>
+        <v>20.8815</v>
       </c>
       <c r="D106" t="n">
-        <v>1929.7608</v>
+        <v>2041.0907</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>0.5693101408991471</v>
+        <v>-1.141151857220763</v>
       </c>
       <c r="B107" t="n">
-        <v>1.97</v>
+        <v>-0.8800000000000001</v>
       </c>
       <c r="C107" t="n">
-        <v>20.2818</v>
+        <v>20.5151</v>
       </c>
       <c r="D107" t="n">
-        <v>1928.6724</v>
+        <v>2041.7792</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>0.302345185068297</v>
+        <v>-0.4936880624816904</v>
       </c>
       <c r="B108" t="n">
-        <v>0.53</v>
+        <v>0.4</v>
       </c>
       <c r="C108" t="n">
-        <v>20.3385</v>
+        <v>20.5143</v>
       </c>
       <c r="D108" t="n">
-        <v>1929.3438</v>
+        <v>2044.2475</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>-0.8696716558930575</v>
+        <v>-0.4299198953461935</v>
       </c>
       <c r="B109" t="n">
-        <v>-0.1299999999999999</v>
+        <v>0.9600000000000002</v>
       </c>
       <c r="C109" t="n">
-        <v>18.5834</v>
+        <v>21.2373</v>
       </c>
       <c r="D109" t="n">
-        <v>1931.4977</v>
+        <v>2047.464</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>-0.8696716558930575</v>
+        <v>1.408563291527876</v>
       </c>
       <c r="B110" t="n">
-        <v>1.92</v>
+        <v>-1.46</v>
       </c>
       <c r="C110" t="n">
-        <v>22.1506</v>
+        <v>22.5488</v>
       </c>
       <c r="D110" t="n">
-        <v>1934.141</v>
+        <v>2047.9498</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>0.6290497288934678</v>
+        <v>-0.8942209951332188</v>
       </c>
       <c r="B111" t="n">
-        <v>-1.8</v>
+        <v>0.6799999999999997</v>
       </c>
       <c r="C111" t="n">
-        <v>24.7106</v>
+        <v>27.701</v>
       </c>
       <c r="D111" t="n">
-        <v>1935.5965</v>
+        <v>2050.0986</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>-0.1226455856981062</v>
+        <v>0.7265406442511969</v>
       </c>
       <c r="B112" t="n">
-        <v>0.41</v>
+        <v>-0.6599999999999999</v>
       </c>
       <c r="C112" t="n">
-        <v>25.7794</v>
+        <v>27.1659</v>
       </c>
       <c r="D112" t="n">
-        <v>1936.4922</v>
+        <v>2052.0037</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>0.4576589526809707</v>
+        <v>2.289447098355472</v>
       </c>
       <c r="B113" t="n">
-        <v>-0.3800000000000001</v>
+        <v>0.1200000000000001</v>
       </c>
       <c r="C113" t="n">
-        <v>25.9052</v>
+        <v>27.0297</v>
       </c>
       <c r="D113" t="n">
-        <v>1936.5536</v>
+        <v>2048.4922</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>-0.7900059994227762</v>
+        <v>0.6188014994187526</v>
       </c>
       <c r="B114" t="n">
-        <v>-0.22</v>
+        <v>0.3999999999999997</v>
       </c>
       <c r="C114" t="n">
-        <v>25.8971</v>
+        <v>29.4112</v>
       </c>
       <c r="D114" t="n">
-        <v>1936.9214</v>
+        <v>2046.6309</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>-0.1420855192722979</v>
+        <v>2.311427515527219</v>
       </c>
       <c r="B115" t="n">
-        <v>0.2999999999999999</v>
+        <v>-0.62</v>
       </c>
       <c r="C115" t="n">
-        <v>26.2268</v>
+        <v>34.4967</v>
       </c>
       <c r="D115" t="n">
-        <v>1938.468</v>
+        <v>2044.6851</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>0.155399963258989</v>
+        <v>-0.4074449258609264</v>
       </c>
       <c r="B116" t="n">
-        <v>1.19</v>
+        <v>1.1</v>
       </c>
       <c r="C116" t="n">
-        <v>27.2312</v>
+        <v>34.2589</v>
       </c>
       <c r="D116" t="n">
-        <v>1938.324</v>
+        <v>2038.2592</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>-1.348226436883199</v>
+        <v>1.247110015103091</v>
       </c>
       <c r="B117" t="n">
-        <v>-0.5399999999999996</v>
+        <v>-0.04999999999999999</v>
       </c>
       <c r="C117" t="n">
-        <v>24.8635</v>
+        <v>37.3416</v>
       </c>
       <c r="D117" t="n">
-        <v>1942.1447</v>
+        <v>2036.8106</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>-0.2673682605626873</v>
+        <v>0.06028607301556475</v>
       </c>
       <c r="B118" t="n">
-        <v>-0.17</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="C118" t="n">
-        <v>24.3275</v>
+        <v>30.7486</v>
       </c>
       <c r="D118" t="n">
-        <v>1943.1603</v>
+        <v>2033.4326</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>0.9175362867030471</v>
+        <v>0.1015132194977339</v>
       </c>
       <c r="B119" t="n">
-        <v>-0.1499999999999999</v>
+        <v>-3.23</v>
       </c>
       <c r="C119" t="n">
-        <v>23.3469</v>
+        <v>34.0856</v>
       </c>
       <c r="D119" t="n">
-        <v>1944.1618</v>
+        <v>2032.3431</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>1.152846414339066</v>
+        <v>1.540028265076392</v>
       </c>
       <c r="B120" t="n">
-        <v>0.04999999999999999</v>
+        <v>1.33</v>
       </c>
       <c r="C120" t="n">
-        <v>22.8974</v>
+        <v>32.3641</v>
       </c>
       <c r="D120" t="n">
-        <v>1945.5042</v>
+        <v>2034.0219</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>-0.2944084642343113</v>
+        <v>0.001592432475892235</v>
       </c>
       <c r="B121" t="n">
-        <v>-0.08000000000000002</v>
+        <v>1.86</v>
       </c>
       <c r="C121" t="n">
-        <v>23.5995</v>
+        <v>35.4155</v>
       </c>
       <c r="D121" t="n">
-        <v>1946.0377</v>
+        <v>2033.4899</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>0.1539887381981505</v>
+        <v>-0.8412283493572421</v>
       </c>
       <c r="B122" t="n">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="C122" t="n">
-        <v>22.7632</v>
+        <v>33.9765</v>
       </c>
       <c r="D122" t="n">
-        <v>1944.1068</v>
+        <v>2037.9093</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>-0.1974502323545066</v>
+        <v>-0.01960417043884909</v>
       </c>
       <c r="B123" t="n">
-        <v>-0.8600000000000001</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="C123" t="n">
-        <v>21.7663</v>
+        <v>33.273</v>
       </c>
       <c r="D123" t="n">
-        <v>1943.9803</v>
+        <v>2040.0019</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>-0.534573708831527</v>
+        <v>0.4080481954448322</v>
       </c>
       <c r="B124" t="n">
-        <v>0.77</v>
+        <v>0.51</v>
       </c>
       <c r="C124" t="n">
-        <v>21.7917</v>
+        <v>32.39</v>
       </c>
       <c r="D124" t="n">
-        <v>1944.2192</v>
+        <v>2040.845</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>-0.2860896157904119</v>
+        <v>0.3812076680976195</v>
       </c>
       <c r="B125" t="n">
-        <v>0.47</v>
+        <v>1.2</v>
       </c>
       <c r="C125" t="n">
-        <v>22.1039</v>
+        <v>32.5006</v>
       </c>
       <c r="D125" t="n">
-        <v>1944.8416</v>
+        <v>2042.853</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>-0.7028479019223636</v>
+        <v>0.1783738500145052</v>
       </c>
       <c r="B126" t="n">
-        <v>0.25</v>
+        <v>2.07</v>
       </c>
       <c r="C126" t="n">
-        <v>22.0013</v>
+        <v>31.4158</v>
       </c>
       <c r="D126" t="n">
-        <v>1945.5285</v>
+        <v>2041.5094</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>1.6194371023448</v>
+        <v>0.0420087389153501</v>
       </c>
       <c r="B127" t="n">
-        <v>-1.03</v>
+        <v>-0.24</v>
       </c>
       <c r="C127" t="n">
-        <v>22.1738</v>
+        <v>29.1466</v>
       </c>
       <c r="D127" t="n">
-        <v>1946.8629</v>
+        <v>2043.3872</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>0.8159904858481906</v>
+        <v>-0.1129648163737324</v>
       </c>
       <c r="B128" t="n">
-        <v>-0.84</v>
+        <v>0.17</v>
       </c>
       <c r="C128" t="n">
-        <v>22.438</v>
+        <v>27.4005</v>
       </c>
       <c r="D128" t="n">
-        <v>1946.9947</v>
+        <v>2045.1283</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>0.3819176464320038</v>
+        <v>1.160719162823975</v>
       </c>
       <c r="B129" t="n">
-        <v>-0.41</v>
+        <v>-1.09</v>
       </c>
       <c r="C129" t="n">
-        <v>21.9685</v>
+        <v>26.1532</v>
       </c>
       <c r="D129" t="n">
-        <v>1946.9678</v>
+        <v>2047.831</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>1.190696124060424</v>
+        <v>-0.1502731429646794</v>
       </c>
       <c r="B130" t="n">
-        <v>1.24</v>
+        <v>0.16</v>
       </c>
       <c r="C130" t="n">
-        <v>21.7593</v>
+        <v>27.0594</v>
       </c>
       <c r="D130" t="n">
-        <v>1946.6738</v>
+        <v>2046.9101</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>0.1335622847657071</v>
+        <v>0.07833239844030805</v>
       </c>
       <c r="B131" t="n">
-        <v>0.79</v>
+        <v>-1.62</v>
       </c>
       <c r="C131" t="n">
-        <v>22.6891</v>
+        <v>24.7641</v>
       </c>
       <c r="D131" t="n">
-        <v>1947.8362</v>
+        <v>2059.732</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>1.154125716562884</v>
+        <v>-0.3939893553162456</v>
       </c>
       <c r="B132" t="n">
-        <v>2.34</v>
+        <v>-0.89</v>
       </c>
       <c r="C132" t="n">
-        <v>21.5353</v>
+        <v>23.5376</v>
       </c>
       <c r="D132" t="n">
-        <v>1947.7813</v>
+        <v>2062.925</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>-1.792024417726009</v>
+        <v>0.138090527686349</v>
       </c>
       <c r="B133" t="n">
-        <v>-1.17</v>
+        <v>-0.9199999999999999</v>
       </c>
       <c r="C133" t="n">
-        <v>20.4375</v>
+        <v>22.3828</v>
       </c>
       <c r="D133" t="n">
-        <v>1948.7368</v>
+        <v>2066.5998</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>-1.456254608952315</v>
+        <v>1.096095271597819</v>
       </c>
       <c r="B134" t="n">
-        <v>-0.36</v>
+        <v>2.52</v>
       </c>
       <c r="C134" t="n">
-        <v>19.5308</v>
+        <v>21.6195</v>
       </c>
       <c r="D134" t="n">
-        <v>1949.6317</v>
+        <v>2065.3414</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>1.750385203160414</v>
+        <v>-0.328154842225129</v>
       </c>
       <c r="B135" t="n">
-        <v>0.54</v>
+        <v>0.65</v>
       </c>
       <c r="C135" t="n">
-        <v>18.4643</v>
+        <v>20.1551</v>
       </c>
       <c r="D135" t="n">
-        <v>1950.2003</v>
+        <v>2064.2529</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>-1.288503528250629</v>
+        <v>0.1902134172874045</v>
       </c>
       <c r="B136" t="n">
-        <v>0.17</v>
+        <v>-0.3299999999999998</v>
       </c>
       <c r="C136" t="n">
-        <v>18.6552</v>
+        <v>19.4041</v>
       </c>
       <c r="D136" t="n">
-        <v>1950.9044</v>
+        <v>2066.9052</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>-0.2444638703166775</v>
+        <v>-0.1340122868473274</v>
       </c>
       <c r="B137" t="n">
-        <v>-0.35</v>
+        <v>-0.16</v>
       </c>
       <c r="C137" t="n">
-        <v>19.2835</v>
+        <v>20.0511</v>
       </c>
       <c r="D137" t="n">
-        <v>1950.8346</v>
+        <v>2068.2851</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>-0.4933875355983171</v>
+        <v>-0.03853996032180741</v>
       </c>
       <c r="B138" t="n">
-        <v>0.06</v>
+        <v>-0.62</v>
       </c>
       <c r="C138" t="n">
-        <v>19.404</v>
+        <v>19.6633</v>
       </c>
       <c r="D138" t="n">
-        <v>1951.0523</v>
+        <v>2070.8218</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>0.9700611206357095</v>
+        <v>-0.03232809075394374</v>
       </c>
       <c r="B139" t="n">
-        <v>-0.3100000000000001</v>
+        <v>1.31</v>
       </c>
       <c r="C139" t="n">
-        <v>19.8276</v>
+        <v>19.6548</v>
       </c>
       <c r="D139" t="n">
-        <v>1951.6762</v>
+        <v>2072.691</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>-0.2079658550933181</v>
+        <v>0.07960316361396752</v>
       </c>
       <c r="B140" t="n">
-        <v>-0.33</v>
+        <v>-1.25</v>
       </c>
       <c r="C140" t="n">
-        <v>17.76</v>
+        <v>20.133</v>
       </c>
       <c r="D140" t="n">
-        <v>1952.154</v>
+        <v>2072.9636</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>-1.313021432282058</v>
+        <v>-0.2676745248928457</v>
       </c>
       <c r="B141" t="n">
-        <v>0.06000000000000005</v>
+        <v>-0.73</v>
       </c>
       <c r="C141" t="n">
-        <v>18.3206</v>
+        <v>20.1176</v>
       </c>
       <c r="D141" t="n">
-        <v>1953.5354</v>
+        <v>2071.8063</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>1.101766461606725</v>
+        <v>-0.150314481423538</v>
       </c>
       <c r="B142" t="n">
-        <v>-0.8599999999999999</v>
+        <v>-0.2200000000000001</v>
       </c>
       <c r="C142" t="n">
-        <v>20.2319</v>
+        <v>19.8209</v>
       </c>
       <c r="D142" t="n">
-        <v>1955.133</v>
+        <v>2075.0554</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>0.2399339740603652</v>
+        <v>0.6299292374919209</v>
       </c>
       <c r="B143" t="n">
-        <v>1.71</v>
+        <v>0.41</v>
       </c>
       <c r="C143" t="n">
-        <v>21.8188</v>
+        <v>19.0991</v>
       </c>
       <c r="D143" t="n">
-        <v>1955.5348</v>
+        <v>2077.3065</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>-1.019977805082273</v>
+        <v>-0.2516868517799842</v>
       </c>
       <c r="B144" t="n">
-        <v>-0.2</v>
+        <v>1.2</v>
       </c>
       <c r="C144" t="n">
-        <v>21.03</v>
+        <v>18.7469</v>
       </c>
       <c r="D144" t="n">
-        <v>1956.1569</v>
+        <v>2080.0332</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>-1.837580914283788</v>
+        <v>-0.5528607967879576</v>
       </c>
       <c r="B145" t="n">
-        <v>0.6599999999999999</v>
+        <v>1.58</v>
       </c>
       <c r="C145" t="n">
-        <v>20.5472</v>
+        <v>18.1276</v>
       </c>
       <c r="D145" t="n">
-        <v>1957.1766</v>
+        <v>2081.2666</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>1.337325724752658</v>
+        <v>0.8523009114478971</v>
       </c>
       <c r="B146" t="n">
-        <v>0.5600000000000001</v>
+        <v>2.21</v>
       </c>
       <c r="C146" t="n">
-        <v>19.9517</v>
+        <v>18.1028</v>
       </c>
       <c r="D146" t="n">
-        <v>1957.5745</v>
+        <v>2082.1872</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>-0.431481587807099</v>
+        <v>0.4397911292678563</v>
       </c>
       <c r="B147" t="n">
-        <v>0.21</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C147" t="n">
-        <v>20.3842</v>
+        <v>18.9284</v>
       </c>
       <c r="D147" t="n">
-        <v>1959.4673</v>
+        <v>2083.6316</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>-1.294946050428921</v>
+        <v>-0.1744535235336446</v>
       </c>
       <c r="B148" t="n">
-        <v>-0.6499999999999999</v>
+        <v>-1.75</v>
       </c>
       <c r="C148" t="n">
-        <v>20.2841</v>
+        <v>21.0173</v>
       </c>
       <c r="D148" t="n">
-        <v>1959.8431</v>
+        <v>2086.6591</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>2.834744628709148</v>
+        <v>0.6641211105483776</v>
       </c>
       <c r="B149" t="n">
-        <v>-0.2700000000000001</v>
+        <v>-2.12</v>
       </c>
       <c r="C149" t="n">
-        <v>19.6136</v>
+        <v>20.2335</v>
       </c>
       <c r="D149" t="n">
-        <v>1960.8095</v>
+        <v>2087.6378</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>2.25131386106634</v>
+        <v>0.102619067169026</v>
       </c>
       <c r="B150" t="n">
-        <v>-0.12</v>
+        <v>-0.22</v>
       </c>
       <c r="C150" t="n">
-        <v>20.2387</v>
+        <v>19.1668</v>
       </c>
       <c r="D150" t="n">
-        <v>1961.9453</v>
+        <v>2083.378</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>0.6537740956575132</v>
+        <v>0.02600575290314795</v>
       </c>
       <c r="B151" t="n">
-        <v>-0.2100000000000001</v>
+        <v>-0.4999999999999999</v>
       </c>
       <c r="C151" t="n">
-        <v>20.1553</v>
+        <v>18.2826</v>
       </c>
       <c r="D151" t="n">
-        <v>1962.0655</v>
+        <v>2081.6859</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>0.497611602464465</v>
+        <v>-0.4370663356725152</v>
       </c>
       <c r="B152" t="n">
-        <v>-1.3</v>
+        <v>0.15</v>
       </c>
       <c r="C152" t="n">
-        <v>20.8092</v>
+        <v>18.6227</v>
       </c>
       <c r="D152" t="n">
-        <v>1964.152</v>
+        <v>2079.3309</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>-0.4630910353707703</v>
+        <v>-0.2706923135646211</v>
       </c>
       <c r="B153" t="n">
-        <v>-0.28</v>
+        <v>-0.38</v>
       </c>
       <c r="C153" t="n">
-        <v>20.6535</v>
+        <v>18.7929</v>
       </c>
       <c r="D153" t="n">
-        <v>1964.3231</v>
+        <v>2075.5039</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>1.822400479644023</v>
+        <v>-0.08414338861781648</v>
       </c>
       <c r="B154" t="n">
-        <v>-0.25</v>
+        <v>-0.8800000000000001</v>
       </c>
       <c r="C154" t="n">
-        <v>19.7954</v>
+        <v>18.6125</v>
       </c>
       <c r="D154" t="n">
-        <v>1964.1868</v>
+        <v>2075.0632</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>1.822400479644023</v>
+        <v>0.2711476933941834</v>
       </c>
       <c r="B155" t="n">
-        <v>-0.11</v>
+        <v>-0.2499999999999999</v>
       </c>
       <c r="C155" t="n">
-        <v>19.6535</v>
+        <v>18.7426</v>
       </c>
       <c r="D155" t="n">
-        <v>1963.5421</v>
+        <v>2073.7418</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>0.3655890066930194</v>
+        <v>-0.5868274053455562</v>
       </c>
       <c r="B156" t="n">
-        <v>1.58</v>
+        <v>-0.98</v>
       </c>
       <c r="C156" t="n">
-        <v>19.9478</v>
+        <v>18.224</v>
       </c>
       <c r="D156" t="n">
-        <v>1963.8106</v>
+        <v>2074.5166</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>0.04664728151023578</v>
+        <v>-0.3381901527736673</v>
       </c>
       <c r="B157" t="n">
-        <v>-1.29</v>
+        <v>1.13</v>
       </c>
       <c r="C157" t="n">
-        <v>21.1169</v>
+        <v>17.9051</v>
       </c>
       <c r="D157" t="n">
-        <v>1963.9415</v>
+        <v>2074.2985</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>2.69945719792479</v>
+        <v>-0.4109942800823903</v>
       </c>
       <c r="B158" t="n">
-        <v>-1.07</v>
+        <v>-0.4800000000000001</v>
       </c>
       <c r="C158" t="n">
-        <v>20.0639</v>
+        <v>17.1088</v>
       </c>
       <c r="D158" t="n">
-        <v>1965.3699</v>
+        <v>2073.1698</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>-0.5154079378670119</v>
+        <v>-0.9998506234199933</v>
       </c>
       <c r="B159" t="n">
-        <v>-0.4999999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="C159" t="n">
-        <v>19.8352</v>
+        <v>17.1986</v>
       </c>
       <c r="D159" t="n">
-        <v>1965.005</v>
+        <v>2071.6706</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>0.09919171116010284</v>
+        <v>0.1665081816778062</v>
       </c>
       <c r="B160" t="n">
-        <v>-0.49</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="C160" t="n">
-        <v>19.0317</v>
+        <v>18.2782</v>
       </c>
       <c r="D160" t="n">
-        <v>1965.0167</v>
+        <v>2070.2917</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>0.4777791856629569</v>
+        <v>0.1455097766834726</v>
       </c>
       <c r="B161" t="n">
-        <v>2.07</v>
+        <v>-0.6300000000000001</v>
       </c>
       <c r="C161" t="n">
-        <v>19.1235</v>
+        <v>21.298</v>
       </c>
       <c r="D161" t="n">
-        <v>1965.0218</v>
+        <v>2069.9834</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>-1.157459723571297</v>
+        <v>0.9172163915322747</v>
       </c>
       <c r="B162" t="n">
-        <v>-1.81</v>
+        <v>0.71</v>
       </c>
       <c r="C162" t="n">
-        <v>18.3834</v>
+        <v>18.926</v>
       </c>
       <c r="D162" t="n">
-        <v>1966.4902</v>
+        <v>2070.3897</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>0.1980331498085701</v>
+        <v>0.1823922762256301</v>
       </c>
       <c r="B163" t="n">
-        <v>-0.84</v>
+        <v>-1.72</v>
       </c>
       <c r="C163" t="n">
-        <v>18.3694</v>
+        <v>18.2836</v>
       </c>
       <c r="D163" t="n">
-        <v>1966.5549</v>
+        <v>2068.8475</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>-0.7918828855687936</v>
+        <v>0.5373686374337189</v>
       </c>
       <c r="B164" t="n">
-        <v>0.25</v>
+        <v>0.15</v>
       </c>
       <c r="C164" t="n">
-        <v>17.8358</v>
+        <v>19.2022</v>
       </c>
       <c r="D164" t="n">
-        <v>1967.4654</v>
+        <v>2063.8593</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>-1.664000277078655</v>
+        <v>0.5748339961350757</v>
       </c>
       <c r="B165" t="n">
-        <v>0.3</v>
+        <v>0.74</v>
       </c>
       <c r="C165" t="n">
-        <v>18.6439</v>
+        <v>18.9528</v>
       </c>
       <c r="D165" t="n">
-        <v>1969.7473</v>
+        <v>2062.908</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>-0.9180059653467468</v>
+        <v>-0.237120572016242</v>
       </c>
       <c r="B166" t="n">
-        <v>0.43</v>
+        <v>-1.11</v>
       </c>
       <c r="C166" t="n">
-        <v>19.1851</v>
+        <v>19.2102</v>
       </c>
       <c r="D166" t="n">
-        <v>1971.4994</v>
+        <v>2063.1733</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>-0.6258390549476549</v>
+        <v>0.09703365881620114</v>
       </c>
       <c r="B167" t="n">
-        <v>-2.43</v>
+        <v>-0.7799999999999998</v>
       </c>
       <c r="C167" t="n">
-        <v>20.1972</v>
+        <v>17.029</v>
       </c>
       <c r="D167" t="n">
-        <v>1973.8151</v>
+        <v>2066.1924</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>0.04249483653437568</v>
+        <v>-0.8823639020223811</v>
       </c>
       <c r="B168" t="n">
-        <v>-0.62</v>
+        <v>0.39</v>
       </c>
       <c r="C168" t="n">
-        <v>19.7455</v>
+        <v>17.1027</v>
       </c>
       <c r="D168" t="n">
-        <v>1973.2141</v>
+        <v>2061.1243</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>0.1441528411070834</v>
+        <v>0.1704011315773598</v>
       </c>
       <c r="B169" t="n">
-        <v>0.43</v>
+        <v>0.25</v>
       </c>
       <c r="C169" t="n">
-        <v>19.6418</v>
+        <v>17.6484</v>
       </c>
       <c r="D169" t="n">
-        <v>1972.1524</v>
+        <v>2052.5918</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>0.3847530364583507</v>
+        <v>-0.09919087225401139</v>
       </c>
       <c r="B170" t="n">
-        <v>0.95</v>
+        <v>-0.4</v>
       </c>
       <c r="C170" t="n">
-        <v>18.9624</v>
+        <v>17.8452</v>
       </c>
       <c r="D170" t="n">
-        <v>1972.1111</v>
+        <v>2051.2713</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>0.04409642236045978</v>
+        <v>-6.146599398605065e-05</v>
       </c>
       <c r="B171" t="n">
-        <v>-1.18</v>
+        <v>0.31</v>
       </c>
       <c r="C171" t="n">
-        <v>18.6725</v>
+        <v>17.0731</v>
       </c>
       <c r="D171" t="n">
-        <v>1972.1367</v>
+        <v>2048.4727</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>-1.399851149599714</v>
+        <v>-0.4275434626714759</v>
       </c>
       <c r="B172" t="n">
-        <v>0.8799999999999999</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="C172" t="n">
-        <v>18.1168</v>
+        <v>17.08</v>
       </c>
       <c r="D172" t="n">
-        <v>1971.3211</v>
+        <v>2046.5699</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>-1.088073603043035</v>
+        <v>-0.3940940415851463</v>
       </c>
       <c r="B173" t="n">
-        <v>0.71</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="C173" t="n">
-        <v>17.7895</v>
+        <v>17.3267</v>
       </c>
       <c r="D173" t="n">
-        <v>1971.0273</v>
+        <v>2048.2747</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="n">
-        <v>-0.4685872508297337</v>
+        <v>-0.2857877011909036</v>
       </c>
       <c r="B174" t="n">
-        <v>-1.1</v>
+        <v>-0.8</v>
       </c>
       <c r="C174" t="n">
-        <v>17.6181</v>
+        <v>17.5211</v>
       </c>
       <c r="D174" t="n">
-        <v>1971.3707</v>
+        <v>2048.5739</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="n">
-        <v>1.177338215516446</v>
+        <v>-0.3809083670348178</v>
       </c>
       <c r="B175" t="n">
-        <v>0.11</v>
+        <v>-0.7400000000000001</v>
       </c>
       <c r="C175" t="n">
-        <v>16.9803</v>
+        <v>18.062</v>
       </c>
       <c r="D175" t="n">
-        <v>1971.0724</v>
+        <v>2049.0301</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="n">
-        <v>0.07489742545956019</v>
+        <v>0.2307322186184628</v>
       </c>
       <c r="B176" t="n">
-        <v>-0.1100000000000001</v>
+        <v>0.2</v>
       </c>
       <c r="C176" t="n">
-        <v>16.8812</v>
+        <v>17.6146</v>
       </c>
       <c r="D176" t="n">
-        <v>1970.9773</v>
+        <v>2051.2282</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="n">
-        <v>1.052110079135902</v>
+        <v>-0.1035661035305248</v>
       </c>
       <c r="B177" t="n">
-        <v>-0.19</v>
+        <v>-1.54</v>
       </c>
       <c r="C177" t="n">
-        <v>16.4876</v>
+        <v>18.9619</v>
       </c>
       <c r="D177" t="n">
-        <v>1971.4915</v>
+        <v>2052.2541</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="n">
-        <v>0.9487217359291215</v>
+        <v>0.6923015656817496</v>
       </c>
       <c r="B178" t="n">
-        <v>1.56</v>
+        <v>-0.6200000000000001</v>
       </c>
       <c r="C178" t="n">
-        <v>16.7105</v>
+        <v>17.2107</v>
       </c>
       <c r="D178" t="n">
-        <v>1970.368</v>
+        <v>2049.0548</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="n">
-        <v>0.3376383896254359</v>
+        <v>0.9657329595623881</v>
       </c>
       <c r="B179" t="n">
-        <v>3.24</v>
+        <v>-0.36</v>
       </c>
       <c r="C179" t="n">
-        <v>16.8382</v>
+        <v>17.4729</v>
       </c>
       <c r="D179" t="n">
-        <v>1969.4364</v>
+        <v>2047.5246</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="n">
-        <v>-0.4677499090040604</v>
+        <v>-0.2647545909811866</v>
       </c>
       <c r="B180" t="n">
-        <v>-0.85</v>
+        <v>0.74</v>
       </c>
       <c r="C180" t="n">
-        <v>17.255</v>
+        <v>17.8168</v>
       </c>
       <c r="D180" t="n">
-        <v>1968.6791</v>
+        <v>2048.2038</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="n">
-        <v>-0.5031034149253126</v>
+        <v>-0.03734480083470736</v>
       </c>
       <c r="B181" t="n">
-        <v>0.04000000000000004</v>
+        <v>0.66</v>
       </c>
       <c r="C181" t="n">
-        <v>17.4738</v>
+        <v>18.1937</v>
       </c>
       <c r="D181" t="n">
-        <v>1969.2818</v>
+        <v>2050.6096</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="n">
-        <v>0.3066999241533003</v>
+        <v>-1.192728618375455</v>
       </c>
       <c r="B182" t="n">
-        <v>0.76</v>
+        <v>-0.8</v>
       </c>
       <c r="C182" t="n">
-        <v>16.1107</v>
+        <v>19.4224</v>
       </c>
       <c r="D182" t="n">
-        <v>1971.1194</v>
+        <v>2048.9978</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="n">
-        <v>1.489491119695676</v>
+        <v>-1.296659141088929</v>
       </c>
       <c r="B183" t="n">
-        <v>-0.9</v>
+        <v>-0.05000000000000002</v>
       </c>
       <c r="C183" t="n">
-        <v>15.3776</v>
+        <v>19.7621</v>
       </c>
       <c r="D183" t="n">
-        <v>1971.7492</v>
+        <v>2045.913</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="n">
-        <v>1.104713552973096</v>
+        <v>-0.5670846937669404</v>
       </c>
       <c r="B184" t="n">
-        <v>-0.9400000000000001</v>
+        <v>0.8</v>
       </c>
       <c r="C184" t="n">
-        <v>15.5586</v>
+        <v>19.4667</v>
       </c>
       <c r="D184" t="n">
-        <v>1972.4866</v>
+        <v>2047.6818</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="n">
-        <v>0.7030711235175153</v>
+        <v>-0.6851627766674674</v>
       </c>
       <c r="B185" t="n">
-        <v>1.37</v>
+        <v>-0.35</v>
       </c>
       <c r="C185" t="n">
-        <v>15.8691</v>
+        <v>18.1904</v>
       </c>
       <c r="D185" t="n">
-        <v>1972.5347</v>
+        <v>2049.8145</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="n">
-        <v>0.5017575116614051</v>
+        <v>-0.2711794695384492</v>
       </c>
       <c r="B186" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-1.17</v>
       </c>
       <c r="C186" t="n">
-        <v>14.845</v>
+        <v>17.3029</v>
       </c>
       <c r="D186" t="n">
-        <v>1972.9574</v>
+        <v>2051.4053</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="n">
-        <v>0.2642553376134946</v>
+        <v>-0.08131436637691397</v>
       </c>
       <c r="B187" t="n">
-        <v>1.53</v>
+        <v>1.99</v>
       </c>
       <c r="C187" t="n">
-        <v>14.3605</v>
+        <v>18.2323</v>
       </c>
       <c r="D187" t="n">
-        <v>1971.8757</v>
+        <v>2053.6636</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="n">
-        <v>0.9236257999459219</v>
+        <v>-0.8629019274474605</v>
       </c>
       <c r="B188" t="n">
-        <v>0.07000000000000001</v>
+        <v>1.29</v>
       </c>
       <c r="C188" t="n">
-        <v>14.2602</v>
+        <v>21.9401</v>
       </c>
       <c r="D188" t="n">
-        <v>1971.4762</v>
+        <v>2056.6686</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="n">
-        <v>0.6198316578600663</v>
+        <v>0.3545981855699386</v>
       </c>
       <c r="B189" t="n">
-        <v>0.34</v>
+        <v>1.43</v>
       </c>
       <c r="C189" t="n">
-        <v>14.6497</v>
+        <v>23.9186</v>
       </c>
       <c r="D189" t="n">
-        <v>1971.8582</v>
+        <v>2058.4893</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="n">
-        <v>0.3966691402193794</v>
+        <v>-0.706095259636666</v>
       </c>
       <c r="B190" t="n">
-        <v>-0.3600000000000001</v>
+        <v>2.98</v>
       </c>
       <c r="C190" t="n">
-        <v>15.0031</v>
+        <v>32.2481</v>
       </c>
       <c r="D190" t="n">
-        <v>1970.9095</v>
+        <v>2060.1277</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="n">
-        <v>0.1199081367114629</v>
+        <v>-0.2996493449853843</v>
       </c>
       <c r="B191" t="n">
-        <v>0.8200000000000001</v>
+        <v>-1.14</v>
       </c>
       <c r="C191" t="n">
-        <v>14.4608</v>
+        <v>31.578</v>
       </c>
       <c r="D191" t="n">
-        <v>1971.5131</v>
+        <v>2056.1128</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="n">
-        <v>0.2450439980142101</v>
+        <v>-0.3658389024438642</v>
       </c>
       <c r="B192" t="n">
-        <v>-1.09</v>
+        <v>-0.8700000000000001</v>
       </c>
       <c r="C192" t="n">
-        <v>14.2045</v>
+        <v>32.5924</v>
       </c>
       <c r="D192" t="n">
-        <v>1971.2666</v>
+        <v>2057.4669</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="n">
-        <v>0.1995415899896377</v>
+        <v>-0.1633881833852132</v>
       </c>
       <c r="B193" t="n">
-        <v>0.16</v>
+        <v>-2.64</v>
       </c>
       <c r="C193" t="n">
-        <v>14.4123</v>
+        <v>32.6272</v>
       </c>
       <c r="D193" t="n">
-        <v>1970.7765</v>
+        <v>2054.6247</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="n">
-        <v>0.3020759067996187</v>
+        <v>-1.039779554220792</v>
       </c>
       <c r="B194" t="n">
-        <v>0.35</v>
+        <v>-2.18</v>
       </c>
       <c r="C194" t="n">
-        <v>14.0568</v>
+        <v>31.5775</v>
       </c>
       <c r="D194" t="n">
-        <v>1970.2777</v>
+        <v>2052.9101</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="n">
-        <v>-0.3205521177849924</v>
+        <v>0.1419565964267256</v>
       </c>
       <c r="B195" t="n">
-        <v>-0.5</v>
+        <v>-2.39</v>
       </c>
       <c r="C195" t="n">
-        <v>13.7203</v>
+        <v>28.6628</v>
       </c>
       <c r="D195" t="n">
-        <v>1970.6628</v>
+        <v>2055.0751</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="n">
-        <v>-0.0165919891125023</v>
+        <v>-1.054449528559425</v>
       </c>
       <c r="B196" t="n">
-        <v>-1.89</v>
+        <v>-0.46</v>
       </c>
       <c r="C196" t="n">
-        <v>13.8436</v>
+        <v>28.7498</v>
       </c>
       <c r="D196" t="n">
-        <v>1970.272</v>
+        <v>2052.5529</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="n">
-        <v>0.3684768567304919</v>
+        <v>0.1693190739457956</v>
       </c>
       <c r="B197" t="n">
-        <v>0.6500000000000001</v>
+        <v>1.89</v>
       </c>
       <c r="C197" t="n">
-        <v>14.0265</v>
+        <v>29.1461</v>
       </c>
       <c r="D197" t="n">
-        <v>1969.1021</v>
+        <v>2052.0167</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="n">
-        <v>0.2251941305913806</v>
+        <v>-0.7517584225089198</v>
       </c>
       <c r="B198" t="n">
-        <v>0.45</v>
+        <v>0.6500000000000004</v>
       </c>
       <c r="C198" t="n">
-        <v>14.3101</v>
+        <v>31.1665</v>
       </c>
       <c r="D198" t="n">
-        <v>1967.4493</v>
+        <v>2048.1663</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="n">
-        <v>0.7648380414824908</v>
+        <v>-0.5466355911047676</v>
       </c>
       <c r="B199" t="n">
-        <v>1.21</v>
+        <v>0.54</v>
       </c>
       <c r="C199" t="n">
-        <v>14.478</v>
+        <v>27.3302</v>
       </c>
       <c r="D199" t="n">
-        <v>1966.0263</v>
+        <v>2048.9198</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="n">
-        <v>0.7631181976875547</v>
+        <v>-0.5417694675137391</v>
       </c>
       <c r="B200" t="n">
-        <v>0.6700000000000002</v>
+        <v>-0.21</v>
       </c>
       <c r="C200" t="n">
-        <v>13.7086</v>
+        <v>27.7307</v>
       </c>
       <c r="D200" t="n">
-        <v>1966.9656</v>
+        <v>2053.2054</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="n">
-        <v>0.5427765513738719</v>
+        <v>-0.3213764138519832</v>
       </c>
       <c r="B201" t="n">
-        <v>0.03000000000000003</v>
+        <v>-0.8200000000000001</v>
       </c>
       <c r="C201" t="n">
-        <v>13.8007</v>
+        <v>26.439</v>
       </c>
       <c r="D201" t="n">
-        <v>1968.163</v>
+        <v>2058.031</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="n">
-        <v>0.1223516056888884</v>
+        <v>-1.288031521159005</v>
       </c>
       <c r="B202" t="n">
-        <v>0.3099999999999999</v>
+        <v>-0.8099999999999999</v>
       </c>
       <c r="C202" t="n">
-        <v>14.0353</v>
+        <v>26.2072</v>
       </c>
       <c r="D202" t="n">
-        <v>1969.1633</v>
+        <v>2061.1563</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="n">
-        <v>-0.1234784147764511</v>
+        <v>0.1188303241756317</v>
       </c>
       <c r="B203" t="n">
-        <v>0.64</v>
+        <v>-0.14</v>
       </c>
       <c r="C203" t="n">
-        <v>13.8457</v>
+        <v>27.1512</v>
       </c>
       <c r="D203" t="n">
-        <v>1969.7564</v>
+        <v>2063.1492</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="n">
-        <v>-0.1797606642423919</v>
+        <v>-0.4975583048570539</v>
       </c>
       <c r="B204" t="n">
-        <v>-0.65</v>
+        <v>0.8799999999999999</v>
       </c>
       <c r="C204" t="n">
-        <v>14.0674</v>
+        <v>30.0846</v>
       </c>
       <c r="D204" t="n">
-        <v>1970.628</v>
+        <v>2059.0562</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="n">
-        <v>0.3091909484867271</v>
+        <v>0.931484090958742</v>
       </c>
       <c r="B205" t="n">
-        <v>-0.3499999999999999</v>
+        <v>0.13</v>
       </c>
       <c r="C205" t="n">
-        <v>14.3448</v>
+        <v>28.7435</v>
       </c>
       <c r="D205" t="n">
-        <v>1971.1352</v>
+        <v>2060.4051</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="n">
-        <v>0.01795450921126611</v>
+        <v>0.06038065233252538</v>
       </c>
       <c r="B206" t="n">
-        <v>1.05</v>
+        <v>-0.3300000000000001</v>
       </c>
       <c r="C206" t="n">
-        <v>15.2748</v>
+        <v>28.2049</v>
       </c>
       <c r="D206" t="n">
-        <v>1970.6331</v>
+        <v>2061.2603</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="n">
-        <v>-0.09111422309893784</v>
+        <v>0.6771359740563524</v>
       </c>
       <c r="B207" t="n">
-        <v>-0.06</v>
+        <v>-1.15</v>
       </c>
       <c r="C207" t="n">
-        <v>14.7736</v>
+        <v>28.7538</v>
       </c>
       <c r="D207" t="n">
-        <v>1972.0518</v>
+        <v>2063.3552</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="n">
-        <v>-0.2466739919045192</v>
+        <v>0.7434422853281355</v>
       </c>
       <c r="B208" t="n">
-        <v>0.17</v>
+        <v>-0.21</v>
       </c>
       <c r="C208" t="n">
-        <v>15.0156</v>
+        <v>28.9244</v>
       </c>
       <c r="D208" t="n">
-        <v>1972.175</v>
+        <v>2061.496</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="n">
-        <v>-0.3149019570057059</v>
+        <v>0.1347561736671437</v>
       </c>
       <c r="B209" t="n">
-        <v>-0.65</v>
+        <v>-0.76</v>
       </c>
       <c r="C209" t="n">
-        <v>15.2936</v>
+        <v>29.9679</v>
       </c>
       <c r="D209" t="n">
-        <v>1973.0004</v>
+        <v>2062.0547</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="n">
-        <v>0.4356035860531328</v>
+        <v>-0.2565543121620475</v>
       </c>
       <c r="B210" t="n">
-        <v>0.76</v>
+        <v>-2.27</v>
       </c>
       <c r="C210" t="n">
-        <v>15.2595</v>
+        <v>30.8769</v>
       </c>
       <c r="D210" t="n">
-        <v>1972.8072</v>
+        <v>2064.4821</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="n">
-        <v>-0.5201464710215937</v>
+        <v>-0.2181689695465377</v>
       </c>
       <c r="B211" t="n">
-        <v>0.18</v>
+        <v>1.59</v>
       </c>
       <c r="C211" t="n">
-        <v>14.4413</v>
+        <v>30.4541</v>
       </c>
       <c r="D211" t="n">
-        <v>1974.7561</v>
+        <v>2064.4078</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="n">
-        <v>-0.2587809302438818</v>
+        <v>-0.8431373101356322</v>
       </c>
       <c r="B212" t="n">
-        <v>-1.21</v>
+        <v>-1.98</v>
       </c>
       <c r="C212" t="n">
-        <v>13.6545</v>
+        <v>30.5483</v>
       </c>
       <c r="D212" t="n">
-        <v>1977.4015</v>
+        <v>2064.6943</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="n">
-        <v>-0.001755931287862278</v>
+        <v>0.205157040778212</v>
       </c>
       <c r="B213" t="n">
-        <v>-0.5900000000000001</v>
+        <v>-0.08</v>
       </c>
       <c r="C213" t="n">
-        <v>13.6818</v>
+        <v>30.6653</v>
       </c>
       <c r="D213" t="n">
-        <v>1977.8773</v>
+        <v>2063.4056</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="n">
-        <v>-0.05791909114829055</v>
+        <v>-0.4342426642546032</v>
       </c>
       <c r="B214" t="n">
-        <v>-0.46</v>
+        <v>0.39</v>
       </c>
       <c r="C214" t="n">
-        <v>13.8587</v>
+        <v>29.8154</v>
       </c>
       <c r="D214" t="n">
-        <v>1979.3761</v>
+        <v>2060.9477</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="n">
-        <v>0.3378042525651752</v>
+        <v>-0.5751731795015288</v>
       </c>
       <c r="B215" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="C215" t="n">
-        <v>14.401</v>
+        <v>29.8255</v>
       </c>
       <c r="D215" t="n">
-        <v>1979.6186</v>
+        <v>2062.5237</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="n">
-        <v>0.08452765282234043</v>
+        <v>-0.21706518209207</v>
       </c>
       <c r="B216" t="n">
-        <v>1.56</v>
+        <v>1.28</v>
       </c>
       <c r="C216" t="n">
-        <v>14.3679</v>
+        <v>28.8792</v>
       </c>
       <c r="D216" t="n">
-        <v>1979.8269</v>
+        <v>2061.2774</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="n">
-        <v>-0.3304705469498909</v>
+        <v>0.838387636660696</v>
       </c>
       <c r="B217" t="n">
-        <v>-0.09</v>
+        <v>1.28</v>
       </c>
       <c r="C217" t="n">
-        <v>14.401</v>
+        <v>28.5233</v>
       </c>
       <c r="D217" t="n">
-        <v>1979.6826</v>
+        <v>2060.3407</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="n">
-        <v>-0.06087143398077225</v>
+        <v>-1.448847283122288</v>
       </c>
       <c r="B218" t="n">
-        <v>-0.05</v>
+        <v>-0.54</v>
       </c>
       <c r="C218" t="n">
-        <v>14.079</v>
+        <v>27.9998</v>
       </c>
       <c r="D218" t="n">
-        <v>1980.117</v>
+        <v>2060.9142</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="n">
-        <v>-0.02552778800219689</v>
+        <v>-0.02442509998120029</v>
       </c>
       <c r="B219" t="n">
-        <v>-0.18</v>
+        <v>0.46</v>
       </c>
       <c r="C219" t="n">
-        <v>13.4649</v>
+        <v>27.4483</v>
       </c>
       <c r="D219" t="n">
-        <v>1980.5624</v>
+        <v>2063.3794</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="n">
-        <v>0.3322169501659979</v>
+        <v>-0.2562554788437582</v>
       </c>
       <c r="B220" t="n">
-        <v>-1.13</v>
+        <v>0.27</v>
       </c>
       <c r="C220" t="n">
-        <v>13.9736</v>
+        <v>30.2625</v>
       </c>
       <c r="D220" t="n">
-        <v>1980.4471</v>
+        <v>2067.859</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="n">
-        <v>0.07042148307866265</v>
+        <v>-0.3551405579002166</v>
       </c>
       <c r="B221" t="n">
-        <v>-0.06</v>
+        <v>-1.01</v>
       </c>
       <c r="C221" t="n">
-        <v>13.4182</v>
+        <v>29.9538</v>
       </c>
       <c r="D221" t="n">
-        <v>1980.7667</v>
+        <v>2068.9295</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="n">
-        <v>0.07213966400977646</v>
+        <v>-0.1962726702520567</v>
       </c>
       <c r="B222" t="n">
-        <v>-0.3</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="C222" t="n">
-        <v>13.1739</v>
+        <v>28.9213</v>
       </c>
       <c r="D222" t="n">
-        <v>1980.7415</v>
+        <v>2065.9478</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="n">
-        <v>0.4139949418853076</v>
+        <v>0.04147619497371069</v>
       </c>
       <c r="B223" t="n">
-        <v>-0.45</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="C223" t="n">
-        <v>13.2029</v>
+        <v>28.431</v>
       </c>
       <c r="D223" t="n">
-        <v>1981.3657</v>
+        <v>2062.9605</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="n">
-        <v>-0.03455435766299945</v>
+        <v>0.2697015861654176</v>
       </c>
       <c r="B224" t="n">
-        <v>-0.4099999999999999</v>
+        <v>0.02000000000000002</v>
       </c>
       <c r="C224" t="n">
-        <v>12.5676</v>
+        <v>28.2941</v>
       </c>
       <c r="D224" t="n">
-        <v>1982.4426</v>
+        <v>2062.4983</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="n">
-        <v>0.7243854270675584</v>
+        <v>0.1651907962307384</v>
       </c>
       <c r="B225" t="n">
-        <v>-0.09999999999999998</v>
+        <v>-0.4</v>
       </c>
       <c r="C225" t="n">
-        <v>12.0093</v>
+        <v>27.4477</v>
       </c>
       <c r="D225" t="n">
-        <v>1983.1374</v>
+        <v>2065.1208</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="n">
-        <v>0.656040556406266</v>
+        <v>-0.08995938998624631</v>
       </c>
       <c r="B226" t="n">
-        <v>-0.59</v>
+        <v>0.92</v>
       </c>
       <c r="C226" t="n">
-        <v>12.2021</v>
+        <v>26.9462</v>
       </c>
       <c r="D226" t="n">
-        <v>1983.5884</v>
+        <v>2063.2499</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="n">
-        <v>0.06420310641884264</v>
+        <v>0.7416423527363192</v>
       </c>
       <c r="B227" t="n">
-        <v>-0.48</v>
+        <v>1.44</v>
       </c>
       <c r="C227" t="n">
-        <v>12.0622</v>
+        <v>27.9534</v>
       </c>
       <c r="D227" t="n">
-        <v>1984.0215</v>
+        <v>2058.7601</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="n">
-        <v>0.572119244990302</v>
+        <v>0.2401631759220637</v>
       </c>
       <c r="B228" t="n">
-        <v>0.8300000000000001</v>
+        <v>-0.6900000000000001</v>
       </c>
       <c r="C228" t="n">
-        <v>12.3144</v>
+        <v>25.8912</v>
       </c>
       <c r="D228" t="n">
-        <v>1984.1043</v>
+        <v>2058.8882</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="n">
-        <v>0.1249148609637351</v>
+        <v>0.8360190134156156</v>
       </c>
       <c r="B229" t="n">
-        <v>-0.38</v>
+        <v>1.08</v>
       </c>
       <c r="C229" t="n">
-        <v>11.9643</v>
+        <v>26.3336</v>
       </c>
       <c r="D229" t="n">
-        <v>1985.1612</v>
+        <v>2060.5438</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="n">
-        <v>0.3384350728596326</v>
+        <v>0.3264971866790427</v>
       </c>
       <c r="B230" t="n">
-        <v>0.9699999999999998</v>
+        <v>-1</v>
       </c>
       <c r="C230" t="n">
-        <v>13.935</v>
+        <v>25.9974</v>
       </c>
       <c r="D230" t="n">
-        <v>1986.4188</v>
+        <v>2060.0879</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="n">
-        <v>-0.04734128181206746</v>
+        <v>0.07744671183048096</v>
       </c>
       <c r="B231" t="n">
-        <v>-2.12</v>
+        <v>-0.14</v>
       </c>
       <c r="C231" t="n">
-        <v>13.2301</v>
+        <v>25.8876</v>
       </c>
       <c r="D231" t="n">
-        <v>1987.6401</v>
+        <v>2061.5994</v>
       </c>
     </row>
     <row r="232">
       <c r="A232" t="n">
-        <v>-0.3151291337398556</v>
+        <v>0.4131647222198945</v>
       </c>
       <c r="B232" t="n">
-        <v>-0.1200000000000001</v>
+        <v>-0.42</v>
       </c>
       <c r="C232" t="n">
-        <v>14.0029</v>
+        <v>26.305</v>
       </c>
       <c r="D232" t="n">
-        <v>1989.0044</v>
+        <v>2059.885</v>
       </c>
     </row>
     <row r="233">
       <c r="A233" t="n">
-        <v>0.08322582461504613</v>
+        <v>-0.03060763205185951</v>
       </c>
       <c r="B233" t="n">
-        <v>-0.21</v>
+        <v>0.7499999999999999</v>
       </c>
       <c r="C233" t="n">
-        <v>14.3602</v>
+        <v>26.378</v>
       </c>
       <c r="D233" t="n">
-        <v>1988.7177</v>
+        <v>2057.6665</v>
       </c>
     </row>
     <row r="234">
       <c r="A234" t="n">
-        <v>0.1896551089012635</v>
+        <v>0.1255169560006198</v>
       </c>
       <c r="B234" t="n">
-        <v>-0.71</v>
+        <v>-0.65</v>
       </c>
       <c r="C234" t="n">
-        <v>14.976</v>
+        <v>26.2348</v>
       </c>
       <c r="D234" t="n">
-        <v>1989.5088</v>
+        <v>2055.4828</v>
       </c>
     </row>
     <row r="235">
       <c r="A235" t="n">
-        <v>-0.15967562369211</v>
+        <v>-0.4325549094742396</v>
       </c>
       <c r="B235" t="n">
-        <v>1.03</v>
+        <v>0.05000000000000004</v>
       </c>
       <c r="C235" t="n">
-        <v>14.6729</v>
+        <v>26.5603</v>
       </c>
       <c r="D235" t="n">
-        <v>1989.5534</v>
+        <v>2051.9294</v>
       </c>
     </row>
     <row r="236">
       <c r="A236" t="n">
-        <v>0.0398939515023459</v>
+        <v>0.2836915889115764</v>
       </c>
       <c r="B236" t="n">
-        <v>1.32</v>
+        <v>0.4700000000000001</v>
       </c>
       <c r="C236" t="n">
-        <v>13.7589</v>
+        <v>25.9072</v>
       </c>
       <c r="D236" t="n">
-        <v>1989.4631</v>
+        <v>2053.1224</v>
       </c>
     </row>
     <row r="237">
       <c r="A237" t="n">
-        <v>-0.4836519222413871</v>
+        <v>0.6132165354913111</v>
       </c>
       <c r="B237" t="n">
-        <v>-1.34</v>
+        <v>1.52</v>
       </c>
       <c r="C237" t="n">
-        <v>13.413</v>
+        <v>26.6721</v>
       </c>
       <c r="D237" t="n">
-        <v>1991.6045</v>
+        <v>2050.7723</v>
       </c>
     </row>
     <row r="238">
       <c r="A238" t="n">
-        <v>-1.088453397425261</v>
+        <v>0.5490554418188717</v>
       </c>
       <c r="B238" t="n">
-        <v>-0.96</v>
+        <v>3.84</v>
       </c>
       <c r="C238" t="n">
-        <v>13.0134</v>
+        <v>24.9678</v>
       </c>
       <c r="D238" t="n">
-        <v>1992.9504</v>
+        <v>2051.1471</v>
       </c>
     </row>
     <row r="239">
       <c r="A239" t="n">
-        <v>-0.6788371657972009</v>
+        <v>0.4122458492513114</v>
       </c>
       <c r="B239" t="n">
-        <v>0.15</v>
+        <v>-1.01</v>
       </c>
       <c r="C239" t="n">
-        <v>13.2607</v>
+        <v>23.7657</v>
       </c>
       <c r="D239" t="n">
-        <v>1995.0525</v>
+        <v>2052.7524</v>
       </c>
     </row>
     <row r="240">
       <c r="A240" t="n">
-        <v>0.3642373512230456</v>
+        <v>0.6228226774344664</v>
       </c>
       <c r="B240" t="n">
-        <v>1.01</v>
+        <v>-0.7000000000000001</v>
       </c>
       <c r="C240" t="n">
-        <v>13.5736</v>
+        <v>22.5006</v>
       </c>
       <c r="D240" t="n">
-        <v>1995.9536</v>
+        <v>2053.3378</v>
       </c>
     </row>
     <row r="241">
       <c r="A241" t="n">
-        <v>-0.8247436945340095</v>
+        <v>0.5508253334152947</v>
       </c>
       <c r="B241" t="n">
-        <v>0.92</v>
+        <v>0.22</v>
       </c>
       <c r="C241" t="n">
-        <v>14.5704</v>
+        <v>22.0246</v>
       </c>
       <c r="D241" t="n">
-        <v>1998.1383</v>
+        <v>2055.0832</v>
       </c>
     </row>
     <row r="242">
       <c r="A242" t="n">
-        <v>0.1588807990188736</v>
+        <v>0.606057329029722</v>
       </c>
       <c r="B242" t="n">
-        <v>-0.65</v>
+        <v>0.34</v>
       </c>
       <c r="C242" t="n">
-        <v>15.0492</v>
+        <v>21.2899</v>
       </c>
       <c r="D242" t="n">
-        <v>1998.9271</v>
+        <v>2055.8168</v>
       </c>
     </row>
     <row r="243">
       <c r="A243" t="n">
-        <v>0.3329419891829684</v>
+        <v>-0.1930547744880352</v>
       </c>
       <c r="B243" t="n">
-        <v>-1.07</v>
+        <v>-1.12</v>
       </c>
       <c r="C243" t="n">
-        <v>15.4504</v>
+        <v>21.4342</v>
       </c>
       <c r="D243" t="n">
-        <v>1999.7239</v>
+        <v>2056.2328</v>
       </c>
     </row>
     <row r="244">
       <c r="A244" t="n">
-        <v>-0.6487227376440989</v>
+        <v>0.2083808266095442</v>
       </c>
       <c r="B244" t="n">
-        <v>-0.9299999999999999</v>
+        <v>1.02</v>
       </c>
       <c r="C244" t="n">
-        <v>14.9596</v>
+        <v>22.6796</v>
       </c>
       <c r="D244" t="n">
-        <v>1999.6054</v>
+        <v>2059.5642</v>
       </c>
     </row>
     <row r="245">
       <c r="A245" t="n">
-        <v>0.03008891042569832</v>
+        <v>-0.06042777787704462</v>
       </c>
       <c r="B245" t="n">
-        <v>-1.73</v>
+        <v>-1.04</v>
       </c>
       <c r="C245" t="n">
-        <v>15.6222</v>
+        <v>23.0742</v>
       </c>
       <c r="D245" t="n">
-        <v>2000.4161</v>
+        <v>2060.1538</v>
       </c>
     </row>
     <row r="246">
       <c r="A246" t="n">
-        <v>0.2164490091857229</v>
+        <v>-0.2828022052681528</v>
       </c>
       <c r="B246" t="n">
-        <v>-0.96</v>
+        <v>0.3700000000000001</v>
       </c>
       <c r="C246" t="n">
-        <v>15.8362</v>
+        <v>23.3064</v>
       </c>
       <c r="D246" t="n">
-        <v>2001.6679</v>
+        <v>2059.4426</v>
       </c>
     </row>
     <row r="247">
       <c r="A247" t="n">
-        <v>-0.2623437674105635</v>
+        <v>0.5658470834641379</v>
       </c>
       <c r="B247" t="n">
-        <v>0.1900000000000002</v>
+        <v>-0.5299999999999999</v>
       </c>
       <c r="C247" t="n">
-        <v>16.0295</v>
+        <v>22.6863</v>
       </c>
       <c r="D247" t="n">
-        <v>2001.5285</v>
+        <v>2060.6383</v>
       </c>
     </row>
     <row r="248">
       <c r="A248" t="n">
-        <v>0.101669791162954</v>
+        <v>-0.06794268992520083</v>
       </c>
       <c r="B248" t="n">
-        <v>-0.6100000000000001</v>
+        <v>1</v>
       </c>
       <c r="C248" t="n">
-        <v>15.3041</v>
+        <v>23.8224</v>
       </c>
       <c r="D248" t="n">
-        <v>2002.8869</v>
+        <v>2057.8931</v>
       </c>
     </row>
     <row r="249">
       <c r="A249" t="n">
-        <v>0.2154528075040434</v>
+        <v>0.4778497731763156</v>
       </c>
       <c r="B249" t="n">
-        <v>0.22</v>
+        <v>0.95</v>
       </c>
       <c r="C249" t="n">
-        <v>14.8701</v>
+        <v>24.1656</v>
       </c>
       <c r="D249" t="n">
-        <v>2003.7863</v>
+        <v>2056.8243</v>
       </c>
     </row>
     <row r="250">
       <c r="A250" t="n">
-        <v>-0.2819883262002058</v>
+        <v>-0.1883993904923016</v>
       </c>
       <c r="B250" t="n">
-        <v>-0.55</v>
+        <v>1.91</v>
       </c>
       <c r="C250" t="n">
-        <v>15.0204</v>
+        <v>25.3868</v>
       </c>
       <c r="D250" t="n">
-        <v>2006.0238</v>
+        <v>2056.7929</v>
       </c>
     </row>
     <row r="251">
       <c r="A251" t="n">
-        <v>-0.4129550745252139</v>
+        <v>0.3220129427258229</v>
       </c>
       <c r="B251" t="n">
-        <v>-0.1</v>
+        <v>-1.36</v>
       </c>
       <c r="C251" t="n">
-        <v>14.1725</v>
+        <v>26.5441</v>
       </c>
       <c r="D251" t="n">
-        <v>2005.6437</v>
+        <v>2057.3071</v>
       </c>
     </row>
     <row r="252">
       <c r="A252" t="n">
-        <v>0.05887699947388144</v>
+        <v>0.8328189981371363</v>
       </c>
       <c r="B252" t="n">
-        <v>-0.72</v>
+        <v>-0.21</v>
       </c>
       <c r="C252" t="n">
-        <v>14.275</v>
+        <v>27.1499</v>
       </c>
       <c r="D252" t="n">
-        <v>2005.2127</v>
+        <v>2056.2925</v>
       </c>
     </row>
     <row r="253">
       <c r="A253" t="n">
-        <v>-0.4294644833968563</v>
+        <v>0.5254428125107691</v>
       </c>
       <c r="B253" t="n">
-        <v>-0.3</v>
+        <v>-1.42</v>
       </c>
       <c r="C253" t="n">
-        <v>13.7159</v>
+        <v>22.0307</v>
       </c>
       <c r="D253" t="n">
-        <v>2005.5256</v>
+        <v>2058.5821</v>
       </c>
     </row>
     <row r="254">
       <c r="A254" t="n">
-        <v>-0.7621984140492518</v>
+        <v>0.2607046158174149</v>
       </c>
       <c r="B254" t="n">
-        <v>0.71</v>
+        <v>-0.07000000000000028</v>
       </c>
       <c r="C254" t="n">
-        <v>13.1982</v>
+        <v>23.8191</v>
       </c>
       <c r="D254" t="n">
-        <v>2006.2776</v>
+        <v>2061.8022</v>
       </c>
     </row>
     <row r="255">
       <c r="A255" t="n">
-        <v>0.228016774858301</v>
+        <v>0.8865751596692462</v>
       </c>
       <c r="B255" t="n">
-        <v>-0.8600000000000001</v>
+        <v>-0.28</v>
       </c>
       <c r="C255" t="n">
-        <v>13.6694</v>
+        <v>23.6512</v>
       </c>
       <c r="D255" t="n">
-        <v>2008.7983</v>
+        <v>2062.5415</v>
       </c>
     </row>
     <row r="256">
       <c r="A256" t="n">
-        <v>-0.6210263936114032</v>
+        <v>0.6923400123725574</v>
       </c>
       <c r="B256" t="n">
-        <v>-0.87</v>
+        <v>0.42</v>
       </c>
       <c r="C256" t="n">
-        <v>15.7377</v>
+        <v>22.9206</v>
       </c>
       <c r="D256" t="n">
-        <v>2008.9715</v>
+        <v>2061.4302</v>
       </c>
     </row>
     <row r="257">
       <c r="A257" t="n">
-        <v>-0.6060176880239458</v>
+        <v>0.187372500085364</v>
       </c>
       <c r="B257" t="n">
-        <v>-0.11</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="C257" t="n">
-        <v>15.0123</v>
+        <v>23.3983</v>
       </c>
       <c r="D257" t="n">
-        <v>2010.5944</v>
+        <v>2060.7434</v>
       </c>
     </row>
     <row r="258">
       <c r="A258" t="n">
-        <v>-0.3200825642068474</v>
+        <v>0.3621660382813523</v>
       </c>
       <c r="B258" t="n">
-        <v>0.8999999999999999</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="C258" t="n">
-        <v>16.7793</v>
+        <v>23.2325</v>
       </c>
       <c r="D258" t="n">
-        <v>2009.3824</v>
+        <v>2060.3506</v>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="n">
-        <v>-0.1701706067052816</v>
+        <v>0.1431055516426011</v>
       </c>
       <c r="B259" t="n">
-        <v>1.75</v>
+        <v>-0.07000000000000006</v>
       </c>
       <c r="C259" t="n">
-        <v>19.1026</v>
+        <v>22.4484</v>
       </c>
       <c r="D259" t="n">
-        <v>2017.1592</v>
+        <v>2059.9631</v>
       </c>
     </row>
     <row r="260">
       <c r="A260" t="n">
-        <v>0.05296850406453361</v>
+        <v>0.2279239700525853</v>
       </c>
       <c r="B260" t="n">
-        <v>2.25</v>
+        <v>-0.6799999999999999</v>
       </c>
       <c r="C260" t="n">
-        <v>23.1268</v>
+        <v>21.8307</v>
       </c>
       <c r="D260" t="n">
-        <v>2018.5954</v>
+        <v>2062.199</v>
       </c>
     </row>
     <row r="261">
       <c r="A261" t="n">
-        <v>-0.5565061244203608</v>
+        <v>0.5186346737814823</v>
       </c>
       <c r="B261" t="n">
-        <v>-1.96</v>
+        <v>1.97</v>
       </c>
       <c r="C261" t="n">
-        <v>20.4829</v>
+        <v>21.9918</v>
       </c>
       <c r="D261" t="n">
-        <v>2019.4528</v>
+        <v>2062.3725</v>
       </c>
     </row>
     <row r="262">
       <c r="A262" t="n">
-        <v>0.2521308394122019</v>
+        <v>-0.2299497574642391</v>
       </c>
       <c r="B262" t="n">
-        <v>-1.64</v>
+        <v>0.41</v>
       </c>
       <c r="C262" t="n">
-        <v>20.6198</v>
+        <v>22.2597</v>
       </c>
       <c r="D262" t="n">
-        <v>2021.0566</v>
+        <v>2063.3727</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="n">
-        <v>-0.3331102767014826</v>
+        <v>-0.4159110784392137</v>
       </c>
       <c r="B263" t="n">
-        <v>-1.34</v>
+        <v>1.25</v>
       </c>
       <c r="C263" t="n">
-        <v>21.9349</v>
+        <v>22.6537</v>
       </c>
       <c r="D263" t="n">
-        <v>2022.8995</v>
+        <v>2062.4348</v>
       </c>
     </row>
     <row r="264">
       <c r="A264" t="n">
-        <v>-0.2705427082274862</v>
+        <v>-0.2343267970392732</v>
       </c>
       <c r="B264" t="n">
-        <v>-1.46</v>
+        <v>-1.36</v>
       </c>
       <c r="C264" t="n">
-        <v>21.531</v>
+        <v>22.6375</v>
       </c>
       <c r="D264" t="n">
-        <v>2025.4557</v>
+        <v>2062.4296</v>
       </c>
     </row>
     <row r="265">
       <c r="A265" t="n">
-        <v>-0.1931677874000943</v>
+        <v>0.1705853781702835</v>
       </c>
       <c r="B265" t="n">
-        <v>1.73</v>
+        <v>-0.8300000000000001</v>
       </c>
       <c r="C265" t="n">
-        <v>19.7756</v>
+        <v>22.8111</v>
       </c>
       <c r="D265" t="n">
-        <v>2026.6094</v>
+        <v>2062.7353</v>
       </c>
     </row>
     <row r="266">
       <c r="A266" t="n">
-        <v>-0.09802565599546496</v>
+        <v>0.2778684079606453</v>
       </c>
       <c r="B266" t="n">
-        <v>-1.78</v>
+        <v>0.5399999999999999</v>
       </c>
       <c r="C266" t="n">
-        <v>18.9608</v>
+        <v>22.3861</v>
       </c>
       <c r="D266" t="n">
-        <v>2027.4278</v>
+        <v>2064.0569</v>
       </c>
     </row>
     <row r="267">
       <c r="A267" t="n">
-        <v>-0.1217079883607715</v>
+        <v>-0.3981929289312142</v>
       </c>
       <c r="B267" t="n">
-        <v>0.1200000000000001</v>
+        <v>0.5</v>
       </c>
       <c r="C267" t="n">
-        <v>19.4232</v>
+        <v>22.1537</v>
       </c>
       <c r="D267" t="n">
-        <v>2027.3488</v>
+        <v>2064.5509</v>
       </c>
     </row>
     <row r="268">
       <c r="A268" t="n">
-        <v>-0.05992726852082594</v>
+        <v>1.042305720913563</v>
       </c>
       <c r="B268" t="n">
-        <v>0.3200000000000001</v>
+        <v>1.12</v>
       </c>
       <c r="C268" t="n">
-        <v>18.5282</v>
+        <v>23.0549</v>
       </c>
       <c r="D268" t="n">
-        <v>2028.3308</v>
+        <v>2062.6346</v>
       </c>
     </row>
     <row r="269">
       <c r="A269" t="n">
-        <v>0.1551041207396734</v>
+        <v>0.5827182792433176</v>
       </c>
       <c r="B269" t="n">
-        <v>-1.74</v>
+        <v>-0.48</v>
       </c>
       <c r="C269" t="n">
-        <v>18.6563</v>
+        <v>23.8637</v>
       </c>
       <c r="D269" t="n">
-        <v>2030.8458</v>
+        <v>2064.2619</v>
       </c>
     </row>
     <row r="270">
       <c r="A270" t="n">
-        <v>-0.5132265489894746</v>
+        <v>0.4753641346723136</v>
       </c>
       <c r="B270" t="n">
-        <v>-3.16</v>
+        <v>-0.7799999999999998</v>
       </c>
       <c r="C270" t="n">
-        <v>18.8297</v>
+        <v>23.813</v>
       </c>
       <c r="D270" t="n">
-        <v>2031.1482</v>
+        <v>2066.4578</v>
       </c>
     </row>
     <row r="271">
       <c r="A271" t="n">
-        <v>-0.2012797419969302</v>
+        <v>0.07847760726949465</v>
       </c>
       <c r="B271" t="n">
-        <v>0.87</v>
+        <v>0.97</v>
       </c>
       <c r="C271" t="n">
-        <v>19.1301</v>
+        <v>22.2728</v>
       </c>
       <c r="D271" t="n">
-        <v>2030.8366</v>
+        <v>2067.3914</v>
       </c>
     </row>
     <row r="272">
       <c r="A272" t="n">
-        <v>-0.4320907533469767</v>
+        <v>1.162646626770311</v>
       </c>
       <c r="B272" t="n">
-        <v>-0.06999999999999984</v>
+        <v>-0.72</v>
       </c>
       <c r="C272" t="n">
-        <v>19.3823</v>
+        <v>21.7345</v>
       </c>
       <c r="D272" t="n">
-        <v>2032.3102</v>
+        <v>2069.9632</v>
       </c>
     </row>
     <row r="273">
       <c r="A273" t="n">
-        <v>0.08909452209932434</v>
+        <v>-0.4796813520817931</v>
       </c>
       <c r="B273" t="n">
-        <v>-2.12</v>
+        <v>0.6699999999999999</v>
       </c>
       <c r="C273" t="n">
-        <v>20.5533</v>
+        <v>21.3545</v>
       </c>
       <c r="D273" t="n">
-        <v>2033.7791</v>
+        <v>2069.087</v>
       </c>
     </row>
     <row r="274">
       <c r="A274" t="n">
-        <v>0.4673048216521356</v>
+        <v>0.2166279189465745</v>
       </c>
       <c r="B274" t="n">
-        <v>-3.47</v>
+        <v>-0.6799999999999999</v>
       </c>
       <c r="C274" t="n">
-        <v>22.4713</v>
+        <v>22.4904</v>
       </c>
       <c r="D274" t="n">
-        <v>2035.9974</v>
+        <v>2071.7721</v>
       </c>
     </row>
     <row r="275">
       <c r="A275" t="n">
-        <v>0.417420518905381</v>
+        <v>0.4886508862498378</v>
       </c>
       <c r="B275" t="n">
-        <v>-1.13</v>
+        <v>1</v>
       </c>
       <c r="C275" t="n">
-        <v>22.905</v>
+        <v>22.3315</v>
       </c>
       <c r="D275" t="n">
-        <v>2037.0541</v>
+        <v>2070.4622</v>
       </c>
     </row>
     <row r="276">
       <c r="A276" t="n">
-        <v>-0.185050411964413</v>
+        <v>0.236691442080736</v>
       </c>
       <c r="B276" t="n">
-        <v>2.63</v>
+        <v>1.57</v>
       </c>
       <c r="C276" t="n">
-        <v>23.5757</v>
+        <v>21.8077</v>
       </c>
       <c r="D276" t="n">
-        <v>2036.117</v>
+        <v>2068.4398</v>
       </c>
     </row>
     <row r="277">
       <c r="A277" t="n">
-        <v>-0.05246170711137355</v>
+        <v>0.003856583803127622</v>
       </c>
       <c r="B277" t="n">
-        <v>0.2</v>
+        <v>-0.6</v>
       </c>
       <c r="C277" t="n">
-        <v>20.2366</v>
+        <v>21.3363</v>
       </c>
       <c r="D277" t="n">
-        <v>2037.8741</v>
+        <v>2068.1827</v>
       </c>
     </row>
     <row r="278">
       <c r="A278" t="n">
-        <v>-0.2637850565935925</v>
+        <v>0.03633729916582651</v>
       </c>
       <c r="B278" t="n">
-        <v>2.67</v>
+        <v>-1.89</v>
       </c>
       <c r="C278" t="n">
-        <v>23.5348</v>
+        <v>20.6565</v>
       </c>
       <c r="D278" t="n">
-        <v>2036.5137</v>
+        <v>2065.3101</v>
       </c>
     </row>
     <row r="279">
       <c r="A279" t="n">
-        <v>0.2395487111309345</v>
+        <v>0.4868199645201107</v>
       </c>
       <c r="B279" t="n">
-        <v>-1.05</v>
+        <v>0.2399999999999999</v>
       </c>
       <c r="C279" t="n">
-        <v>20.8815</v>
+        <v>20.6335</v>
       </c>
       <c r="D279" t="n">
-        <v>2041.0907</v>
+        <v>2066.2655</v>
       </c>
     </row>
     <row r="280">
       <c r="A280" t="n">
-        <v>0.3008672664644931</v>
+        <v>0.3585498894867196</v>
       </c>
       <c r="B280" t="n">
-        <v>-0.8800000000000001</v>
+        <v>1.04</v>
       </c>
       <c r="C280" t="n">
-        <v>20.5151</v>
+        <v>20.3451</v>
       </c>
       <c r="D280" t="n">
-        <v>2041.7792</v>
+        <v>2064.1157</v>
       </c>
     </row>
     <row r="281">
       <c r="A281" t="n">
-        <v>0.5957515376484669</v>
+        <v>-0.9867634475542634</v>
       </c>
       <c r="B281" t="n">
-        <v>0.4</v>
+        <v>0.22</v>
       </c>
       <c r="C281" t="n">
-        <v>20.5143</v>
+        <v>20.9417</v>
       </c>
       <c r="D281" t="n">
-        <v>2044.2475</v>
+        <v>2062.5047</v>
       </c>
     </row>
     <row r="282">
       <c r="A282" t="n">
-        <v>1.062934452034389</v>
+        <v>0.2956428513460772</v>
       </c>
       <c r="B282" t="n">
-        <v>0.9600000000000002</v>
+        <v>0.14</v>
       </c>
       <c r="C282" t="n">
-        <v>21.2373</v>
+        <v>21.3076</v>
       </c>
       <c r="D282" t="n">
-        <v>2047.464</v>
+        <v>2061.6124</v>
       </c>
     </row>
     <row r="283">
       <c r="A283" t="n">
-        <v>0.01479441642296653</v>
+        <v>1.440122167138699</v>
       </c>
       <c r="B283" t="n">
-        <v>-1.46</v>
+        <v>-0.6599999999999999</v>
       </c>
       <c r="C283" t="n">
-        <v>22.5488</v>
+        <v>20.3531</v>
       </c>
       <c r="D283" t="n">
-        <v>2047.9498</v>
+        <v>2060.9335</v>
       </c>
     </row>
     <row r="284">
       <c r="A284" t="n">
-        <v>0.5216424074237008</v>
+        <v>1.578650422858413</v>
       </c>
       <c r="B284" t="n">
-        <v>0.6799999999999997</v>
+        <v>1.08</v>
       </c>
       <c r="C284" t="n">
-        <v>27.701</v>
+        <v>21.5993</v>
       </c>
       <c r="D284" t="n">
-        <v>2050.0986</v>
+        <v>2062.6408</v>
       </c>
     </row>
     <row r="285">
       <c r="A285" t="n">
-        <v>1.333100448605881</v>
+        <v>-0.9803725004471417</v>
       </c>
       <c r="B285" t="n">
-        <v>-0.6599999999999999</v>
+        <v>-0.78</v>
       </c>
       <c r="C285" t="n">
-        <v>27.1659</v>
+        <v>20.8409</v>
       </c>
       <c r="D285" t="n">
-        <v>2052.0037</v>
+        <v>2062.1639</v>
       </c>
     </row>
     <row r="286">
       <c r="A286" t="n">
-        <v>0.6356650443609214</v>
+        <v>-1.366382759169176</v>
       </c>
       <c r="B286" t="n">
-        <v>0.1200000000000001</v>
+        <v>1.06</v>
       </c>
       <c r="C286" t="n">
-        <v>27.0297</v>
+        <v>20.4822</v>
       </c>
       <c r="D286" t="n">
-        <v>2048.4922</v>
+        <v>2060.3031</v>
       </c>
     </row>
     <row r="287">
       <c r="A287" t="n">
-        <v>1.15527169983039</v>
+        <v>-1.338075207471897</v>
       </c>
       <c r="B287" t="n">
-        <v>0.3999999999999997</v>
+        <v>1.47</v>
       </c>
       <c r="C287" t="n">
-        <v>29.4112</v>
+        <v>19.3846</v>
       </c>
       <c r="D287" t="n">
-        <v>2046.6309</v>
+        <v>2060.9187</v>
       </c>
     </row>
     <row r="288">
       <c r="A288" t="n">
-        <v>0.9532166271349221</v>
+        <v>1.461236676797225</v>
       </c>
       <c r="B288" t="n">
-        <v>-0.62</v>
+        <v>1.56</v>
       </c>
       <c r="C288" t="n">
-        <v>34.4967</v>
+        <v>20.0817</v>
       </c>
       <c r="D288" t="n">
-        <v>2044.6851</v>
+        <v>2062.1097</v>
       </c>
     </row>
     <row r="289">
       <c r="A289" t="n">
-        <v>1.35136865047998</v>
+        <v>-0.54914489928194</v>
       </c>
       <c r="B289" t="n">
-        <v>1.1</v>
+        <v>-0.55</v>
       </c>
       <c r="C289" t="n">
-        <v>34.2589</v>
+        <v>20.2669</v>
       </c>
       <c r="D289" t="n">
-        <v>2038.2592</v>
+        <v>2064.263</v>
       </c>
     </row>
     <row r="290">
       <c r="A290" t="n">
-        <v>0.02639545907930207</v>
+        <v>0.6907262145178501</v>
       </c>
       <c r="B290" t="n">
-        <v>-0.04999999999999999</v>
+        <v>1.07</v>
       </c>
       <c r="C290" t="n">
-        <v>37.3416</v>
+        <v>22.6407</v>
       </c>
       <c r="D290" t="n">
-        <v>2036.8106</v>
+        <v>2066.5425</v>
       </c>
     </row>
     <row r="291">
       <c r="A291" t="n">
-        <v>0.05342421711292374</v>
+        <v>-0.4980759934412964</v>
       </c>
       <c r="B291" t="n">
-        <v>-0.6899999999999999</v>
+        <v>-0.5700000000000001</v>
       </c>
       <c r="C291" t="n">
-        <v>30.7486</v>
+        <v>23.3146</v>
       </c>
       <c r="D291" t="n">
-        <v>2033.4326</v>
+        <v>2066.6967</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="n">
-        <v>0.519344706490694</v>
+        <v>0.6992190947779373</v>
       </c>
       <c r="B292" t="n">
-        <v>-3.23</v>
+        <v>0.11</v>
       </c>
       <c r="C292" t="n">
-        <v>34.0856</v>
+        <v>23.0196</v>
       </c>
       <c r="D292" t="n">
-        <v>2032.3431</v>
+        <v>2066.7966</v>
       </c>
     </row>
     <row r="293">
       <c r="A293" t="n">
-        <v>0.3055275172524401</v>
+        <v>0.8184282675790747</v>
       </c>
       <c r="B293" t="n">
-        <v>1.33</v>
+        <v>-0.39</v>
       </c>
       <c r="C293" t="n">
-        <v>32.3641</v>
+        <v>22.1757</v>
       </c>
       <c r="D293" t="n">
-        <v>2034.0219</v>
+        <v>2067.963</v>
       </c>
     </row>
     <row r="294">
       <c r="A294" t="n">
-        <v>0.2069261761242152</v>
+        <v>-0.3558576970733319</v>
       </c>
       <c r="B294" t="n">
-        <v>1.86</v>
+        <v>-0.6899999999999999</v>
       </c>
       <c r="C294" t="n">
-        <v>35.4155</v>
+        <v>21.0351</v>
       </c>
       <c r="D294" t="n">
-        <v>2033.4899</v>
+        <v>2067.3941</v>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="n">
-        <v>0.2686362567499541</v>
+        <v>-0.09748279599332965</v>
       </c>
       <c r="B295" t="n">
-        <v>1.26</v>
+        <v>-0.33</v>
       </c>
       <c r="C295" t="n">
-        <v>33.9765</v>
+        <v>20.0121</v>
       </c>
       <c r="D295" t="n">
-        <v>2037.9093</v>
+        <v>2067.8817</v>
       </c>
     </row>
     <row r="296">
       <c r="A296" t="n">
-        <v>0.3742805633618968</v>
+        <v>-0.655130687724905</v>
       </c>
       <c r="B296" t="n">
-        <v>-0.04000000000000004</v>
+        <v>1.09</v>
       </c>
       <c r="C296" t="n">
-        <v>33.273</v>
+        <v>19.3263</v>
       </c>
       <c r="D296" t="n">
-        <v>2040.0019</v>
+        <v>2065.8482</v>
       </c>
     </row>
     <row r="297">
       <c r="A297" t="n">
-        <v>0.1891740123697813</v>
+        <v>-0.6507758996844083</v>
       </c>
       <c r="B297" t="n">
-        <v>0.51</v>
+        <v>-0.31</v>
       </c>
       <c r="C297" t="n">
-        <v>32.39</v>
+        <v>18.4324</v>
       </c>
       <c r="D297" t="n">
-        <v>2040.845</v>
+        <v>2066.6414</v>
       </c>
     </row>
     <row r="298">
       <c r="A298" t="n">
-        <v>0.6921954111076248</v>
+        <v>-1.076163502177476</v>
       </c>
       <c r="B298" t="n">
-        <v>1.2</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="C298" t="n">
-        <v>32.5006</v>
+        <v>18.9507</v>
       </c>
       <c r="D298" t="n">
-        <v>2042.853</v>
+        <v>2063.8818</v>
       </c>
     </row>
     <row r="299">
       <c r="A299" t="n">
-        <v>0.4371175361510806</v>
+        <v>-1.288825006710846</v>
       </c>
       <c r="B299" t="n">
-        <v>2.07</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="C299" t="n">
-        <v>31.4158</v>
+        <v>18.2108</v>
       </c>
       <c r="D299" t="n">
-        <v>2041.5094</v>
+        <v>2065.2853</v>
       </c>
     </row>
     <row r="300">
       <c r="A300" t="n">
-        <v>0.2469117993169637</v>
+        <v>0.1513898174093151</v>
       </c>
       <c r="B300" t="n">
-        <v>-0.24</v>
+        <v>-0.27</v>
       </c>
       <c r="C300" t="n">
-        <v>29.1466</v>
+        <v>18.1614</v>
       </c>
       <c r="D300" t="n">
-        <v>2043.3872</v>
+        <v>2066.7008</v>
       </c>
     </row>
     <row r="301">
       <c r="A301" t="n">
-        <v>-0.08192897885573118</v>
+        <v>1.785170946929592</v>
       </c>
       <c r="B301" t="n">
-        <v>0.17</v>
+        <v>1.29</v>
       </c>
       <c r="C301" t="n">
-        <v>27.4005</v>
+        <v>18.2654</v>
       </c>
       <c r="D301" t="n">
-        <v>2045.1283</v>
+        <v>2067.9459</v>
       </c>
     </row>
     <row r="302">
       <c r="A302" t="n">
-        <v>-0.03348692242551417</v>
+        <v>2.5423757789031</v>
       </c>
       <c r="B302" t="n">
-        <v>-1.09</v>
+        <v>0.7200000000000001</v>
       </c>
       <c r="C302" t="n">
-        <v>26.1532</v>
+        <v>18.6501</v>
       </c>
       <c r="D302" t="n">
-        <v>2047.831</v>
+        <v>2069.2665</v>
       </c>
     </row>
     <row r="303">
       <c r="A303" t="n">
-        <v>-0.1419651540297112</v>
+        <v>0.6099948499308756</v>
       </c>
       <c r="B303" t="n">
-        <v>0.16</v>
+        <v>-0.52</v>
       </c>
       <c r="C303" t="n">
-        <v>27.0594</v>
+        <v>18.0901</v>
       </c>
       <c r="D303" t="n">
-        <v>2046.9101</v>
+        <v>2068.3517</v>
       </c>
     </row>
     <row r="304">
       <c r="A304" t="n">
-        <v>0.003054482761840375</v>
+        <v>0.7147072505958465</v>
       </c>
       <c r="B304" t="n">
-        <v>-1.62</v>
+        <v>-1.39</v>
       </c>
       <c r="C304" t="n">
-        <v>24.7641</v>
+        <v>19.2189</v>
       </c>
       <c r="D304" t="n">
-        <v>2059.732</v>
+        <v>2071.9605</v>
       </c>
     </row>
     <row r="305">
       <c r="A305" t="n">
-        <v>-0.4639418464241913</v>
+        <v>3.633939657252657</v>
       </c>
       <c r="B305" t="n">
-        <v>-0.89</v>
+        <v>0.6600000000000001</v>
       </c>
       <c r="C305" t="n">
-        <v>23.5376</v>
+        <v>18.9618</v>
       </c>
       <c r="D305" t="n">
-        <v>2062.925</v>
+        <v>2072.0228</v>
       </c>
     </row>
     <row r="306">
       <c r="A306" t="n">
-        <v>-0.3611541149281708</v>
+        <v>-2.96856589929853</v>
       </c>
       <c r="B306" t="n">
-        <v>-0.9199999999999999</v>
+        <v>-0.09999999999999998</v>
       </c>
       <c r="C306" t="n">
-        <v>22.3828</v>
+        <v>18.8503</v>
       </c>
       <c r="D306" t="n">
-        <v>2066.5998</v>
+        <v>2073.9439</v>
       </c>
     </row>
     <row r="307">
       <c r="A307" t="n">
-        <v>0.01916588757180421</v>
+        <v>-0.1533779248163329</v>
       </c>
       <c r="B307" t="n">
-        <v>2.52</v>
+        <v>1.44</v>
       </c>
       <c r="C307" t="n">
-        <v>21.6195</v>
+        <v>18.0434</v>
       </c>
       <c r="D307" t="n">
-        <v>2065.3414</v>
+        <v>2072.4224</v>
       </c>
     </row>
     <row r="308">
       <c r="A308" t="n">
-        <v>-0.307650783635634</v>
+        <v>0.3613635757197672</v>
       </c>
       <c r="B308" t="n">
-        <v>0.65</v>
+        <v>-0.33</v>
       </c>
       <c r="C308" t="n">
-        <v>20.1551</v>
+        <v>17.8474</v>
       </c>
       <c r="D308" t="n">
-        <v>2064.2529</v>
+        <v>2075.1803</v>
       </c>
     </row>
     <row r="309">
       <c r="A309" t="n">
-        <v>-1.029412936819853</v>
+        <v>0.3381352573176892</v>
       </c>
       <c r="B309" t="n">
-        <v>-0.3299999999999998</v>
+        <v>0.96</v>
       </c>
       <c r="C309" t="n">
-        <v>19.4041</v>
+        <v>18.2024</v>
       </c>
       <c r="D309" t="n">
-        <v>2066.9052</v>
+        <v>2076.1785</v>
       </c>
     </row>
     <row r="310">
       <c r="A310" t="n">
-        <v>-0.2317869695570675</v>
+        <v>-0.4315481614041465</v>
       </c>
       <c r="B310" t="n">
-        <v>-0.16</v>
+        <v>0.47</v>
       </c>
       <c r="C310" t="n">
-        <v>20.0511</v>
+        <v>18.638</v>
       </c>
       <c r="D310" t="n">
-        <v>2068.2851</v>
+        <v>2076.2973</v>
       </c>
     </row>
     <row r="311">
       <c r="A311" t="n">
-        <v>-0.1014279735941917</v>
+        <v>0.2300523053598849</v>
       </c>
       <c r="B311" t="n">
-        <v>-0.62</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="C311" t="n">
-        <v>19.6633</v>
+        <v>18.6911</v>
       </c>
       <c r="D311" t="n">
-        <v>2070.8218</v>
+        <v>2079.6206</v>
       </c>
     </row>
     <row r="312">
       <c r="A312" t="n">
-        <v>0.05860089382547033</v>
+        <v>1.634532476652143</v>
       </c>
       <c r="B312" t="n">
-        <v>1.31</v>
+        <v>0.03000000000000003</v>
       </c>
       <c r="C312" t="n">
-        <v>19.6548</v>
+        <v>19.7377</v>
       </c>
       <c r="D312" t="n">
-        <v>2072.691</v>
+        <v>2082.0284</v>
       </c>
     </row>
     <row r="313">
       <c r="A313" t="n">
-        <v>-0.602652644529868</v>
+        <v>-1.264593801128893</v>
       </c>
       <c r="B313" t="n">
-        <v>-1.25</v>
+        <v>-2.22</v>
       </c>
       <c r="C313" t="n">
-        <v>20.133</v>
+        <v>20.3733</v>
       </c>
       <c r="D313" t="n">
-        <v>2072.9636</v>
+        <v>2084.1957</v>
       </c>
     </row>
     <row r="314">
       <c r="A314" t="n">
-        <v>-0.1821193631228479</v>
+        <v>-0.05576960820269833</v>
       </c>
       <c r="B314" t="n">
-        <v>-0.73</v>
+        <v>0.9700000000000001</v>
       </c>
       <c r="C314" t="n">
-        <v>20.1176</v>
+        <v>20.3355</v>
       </c>
       <c r="D314" t="n">
-        <v>2071.8063</v>
+        <v>2086.7012</v>
       </c>
     </row>
     <row r="315">
       <c r="A315" t="n">
-        <v>0.0518249100198791</v>
+        <v>-0.004045041096508606</v>
       </c>
       <c r="B315" t="n">
-        <v>-0.2200000000000001</v>
+        <v>2.66</v>
       </c>
       <c r="C315" t="n">
-        <v>19.8209</v>
+        <v>21.9662</v>
       </c>
       <c r="D315" t="n">
-        <v>2075.0554</v>
+        <v>2088.2709</v>
       </c>
     </row>
     <row r="316">
       <c r="A316" t="n">
-        <v>0.9118439455623827</v>
+        <v>-0.2628049755408705</v>
       </c>
       <c r="B316" t="n">
-        <v>0.41</v>
+        <v>3.52</v>
       </c>
       <c r="C316" t="n">
-        <v>19.0991</v>
+        <v>25.0629</v>
       </c>
       <c r="D316" t="n">
-        <v>2077.3065</v>
+        <v>2091.6913</v>
       </c>
     </row>
     <row r="317">
       <c r="A317" t="n">
-        <v>1.113150369714466</v>
+        <v>0.06985072845338514</v>
       </c>
       <c r="B317" t="n">
-        <v>1.2</v>
+        <v>-0.05000000000000004</v>
       </c>
       <c r="C317" t="n">
-        <v>18.7469</v>
+        <v>25.0915</v>
       </c>
       <c r="D317" t="n">
-        <v>2080.0332</v>
+        <v>2092.3248</v>
       </c>
     </row>
     <row r="318">
       <c r="A318" t="n">
-        <v>0.9094219447989058</v>
+        <v>-0.6762392509048277</v>
       </c>
       <c r="B318" t="n">
-        <v>1.58</v>
+        <v>1.35</v>
       </c>
       <c r="C318" t="n">
-        <v>18.1276</v>
+        <v>22.7964</v>
       </c>
       <c r="D318" t="n">
-        <v>2081.2666</v>
+        <v>2090.0395</v>
       </c>
     </row>
     <row r="319">
       <c r="A319" t="n">
-        <v>0.8717601336670153</v>
+        <v>0.7069099026765959</v>
       </c>
       <c r="B319" t="n">
-        <v>2.21</v>
+        <v>2.06</v>
       </c>
       <c r="C319" t="n">
-        <v>18.1028</v>
+        <v>24.1206</v>
       </c>
       <c r="D319" t="n">
-        <v>2082.1872</v>
+        <v>2094.4453</v>
       </c>
     </row>
     <row r="320">
       <c r="A320" t="n">
-        <v>-0.06719844388043533</v>
+        <v>-2.799882558157114</v>
       </c>
       <c r="B320" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.05999999999999994</v>
       </c>
       <c r="C320" t="n">
-        <v>18.9284</v>
+        <v>23.8405</v>
       </c>
       <c r="D320" t="n">
-        <v>2083.6316</v>
+        <v>2095.081</v>
       </c>
     </row>
     <row r="321">
       <c r="A321" t="n">
-        <v>0.2390119557683094</v>
+        <v>-0.1305008542058439</v>
       </c>
       <c r="B321" t="n">
-        <v>-1.75</v>
+        <v>-1.5</v>
       </c>
       <c r="C321" t="n">
-        <v>21.0173</v>
+        <v>23.457</v>
       </c>
       <c r="D321" t="n">
-        <v>2086.6591</v>
+        <v>2094.2301</v>
       </c>
     </row>
     <row r="322">
       <c r="A322" t="n">
-        <v>0.3563558743932959</v>
+        <v>-1.007826847146394</v>
       </c>
       <c r="B322" t="n">
-        <v>-2.12</v>
+        <v>-0.15</v>
       </c>
       <c r="C322" t="n">
-        <v>20.2335</v>
+        <v>21.6663</v>
       </c>
       <c r="D322" t="n">
-        <v>2087.6378</v>
+        <v>2092.9745</v>
       </c>
     </row>
     <row r="323">
       <c r="A323" t="n">
-        <v>-0.1557127041632104</v>
+        <v>-0.08192630523539271</v>
       </c>
       <c r="B323" t="n">
-        <v>-0.22</v>
+        <v>-1.07</v>
       </c>
       <c r="C323" t="n">
-        <v>19.1668</v>
+        <v>22.0351</v>
       </c>
       <c r="D323" t="n">
-        <v>2083.378</v>
+        <v>2093.3783</v>
       </c>
     </row>
     <row r="324">
       <c r="A324" t="n">
-        <v>0.05904233817876033</v>
+        <v>0.7966546998306804</v>
       </c>
       <c r="B324" t="n">
-        <v>-0.4999999999999999</v>
+        <v>-0.4900000000000001</v>
       </c>
       <c r="C324" t="n">
-        <v>18.2826</v>
+        <v>22.2011</v>
       </c>
       <c r="D324" t="n">
-        <v>2081.6859</v>
+        <v>2091.062</v>
       </c>
     </row>
     <row r="325">
       <c r="A325" t="n">
-        <v>-0.1170666898063973</v>
+        <v>0.477233577883648</v>
       </c>
       <c r="B325" t="n">
-        <v>0.15</v>
+        <v>-0.71</v>
       </c>
       <c r="C325" t="n">
-        <v>18.6227</v>
+        <v>21.976</v>
       </c>
       <c r="D325" t="n">
-        <v>2079.3309</v>
+        <v>2092.8105</v>
       </c>
     </row>
     <row r="326">
       <c r="A326" t="n">
-        <v>-0.04394523480128065</v>
+        <v>0.2700433176287178</v>
       </c>
       <c r="B326" t="n">
-        <v>-0.38</v>
+        <v>-0.17</v>
       </c>
       <c r="C326" t="n">
-        <v>18.7929</v>
+        <v>23.1673</v>
       </c>
       <c r="D326" t="n">
-        <v>2075.5039</v>
+        <v>2096.501</v>
       </c>
     </row>
     <row r="327">
       <c r="A327" t="n">
-        <v>0.0772545077127673</v>
+        <v>-0.2188349567387967</v>
       </c>
       <c r="B327" t="n">
-        <v>-0.8800000000000001</v>
+        <v>0.24</v>
       </c>
       <c r="C327" t="n">
-        <v>18.6125</v>
+        <v>22.1423</v>
       </c>
       <c r="D327" t="n">
-        <v>2075.0632</v>
+        <v>2097.0782</v>
       </c>
     </row>
     <row r="328">
       <c r="A328" t="n">
-        <v>0.4660317787272917</v>
+        <v>1.008627589677711</v>
       </c>
       <c r="B328" t="n">
-        <v>-0.2499999999999999</v>
+        <v>2.31</v>
       </c>
       <c r="C328" t="n">
-        <v>18.7426</v>
+        <v>22.9036</v>
       </c>
       <c r="D328" t="n">
-        <v>2073.7418</v>
+        <v>2098.3298</v>
       </c>
     </row>
     <row r="329">
       <c r="A329" t="n">
-        <v>-0.2546568819048254</v>
+        <v>-0.6535730266166992</v>
       </c>
       <c r="B329" t="n">
-        <v>-0.98</v>
+        <v>-0.3300000000000001</v>
       </c>
       <c r="C329" t="n">
-        <v>18.224</v>
+        <v>22.7349</v>
       </c>
       <c r="D329" t="n">
-        <v>2074.5166</v>
+        <v>2093.1</v>
       </c>
     </row>
     <row r="330">
       <c r="A330" t="n">
-        <v>-0.7069507477800901</v>
+        <v>-0.584453525200836</v>
       </c>
       <c r="B330" t="n">
-        <v>1.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C330" t="n">
-        <v>17.9051</v>
+        <v>22.242</v>
       </c>
       <c r="D330" t="n">
-        <v>2074.2985</v>
+        <v>2093.0376</v>
       </c>
     </row>
     <row r="331">
       <c r="A331" t="n">
-        <v>-0.3754276995052703</v>
+        <v>0.1711959336310201</v>
       </c>
       <c r="B331" t="n">
-        <v>-0.4800000000000001</v>
+        <v>-0.06000000000000005</v>
       </c>
       <c r="C331" t="n">
-        <v>17.1088</v>
+        <v>23.7183</v>
       </c>
       <c r="D331" t="n">
-        <v>2073.1698</v>
+        <v>2087.3412</v>
       </c>
     </row>
     <row r="332">
       <c r="A332" t="n">
-        <v>-0.3883180863072027</v>
+        <v>-0.5755750586235527</v>
       </c>
       <c r="B332" t="n">
-        <v>1.03</v>
+        <v>0.9</v>
       </c>
       <c r="C332" t="n">
-        <v>17.1986</v>
+        <v>23.871</v>
       </c>
       <c r="D332" t="n">
-        <v>2071.6706</v>
+        <v>2085.646</v>
       </c>
     </row>
     <row r="333">
       <c r="A333" t="n">
-        <v>0.4154689970943831</v>
+        <v>-0.4982703255975764</v>
       </c>
       <c r="B333" t="n">
-        <v>0.9299999999999999</v>
+        <v>0.23</v>
       </c>
       <c r="C333" t="n">
-        <v>18.2782</v>
+        <v>24.2613</v>
       </c>
       <c r="D333" t="n">
-        <v>2070.2917</v>
+        <v>2088.2937</v>
       </c>
     </row>
     <row r="334">
       <c r="A334" t="n">
-        <v>-0.593421916663092</v>
+        <v>-0.110377534992523</v>
       </c>
       <c r="B334" t="n">
-        <v>-0.6300000000000001</v>
+        <v>-0.4599999999999999</v>
       </c>
       <c r="C334" t="n">
-        <v>21.298</v>
+        <v>22.4766</v>
       </c>
       <c r="D334" t="n">
-        <v>2069.9834</v>
+        <v>2090.8149</v>
       </c>
     </row>
     <row r="335">
       <c r="A335" t="n">
-        <v>0.2302206675333465</v>
+        <v>0.05815493276503575</v>
       </c>
       <c r="B335" t="n">
-        <v>0.71</v>
+        <v>1.83</v>
       </c>
       <c r="C335" t="n">
-        <v>18.926</v>
+        <v>21.2919</v>
       </c>
       <c r="D335" t="n">
-        <v>2070.3897</v>
+        <v>2088.9258</v>
       </c>
     </row>
     <row r="336">
       <c r="A336" t="n">
-        <v>-0.07108860934107027</v>
+        <v>0.1795005595593585</v>
       </c>
       <c r="B336" t="n">
-        <v>-1.72</v>
+        <v>2.9</v>
       </c>
       <c r="C336" t="n">
-        <v>18.2836</v>
+        <v>22.2674</v>
       </c>
       <c r="D336" t="n">
-        <v>2068.8475</v>
+        <v>2087.1471</v>
       </c>
     </row>
     <row r="337">
       <c r="A337" t="n">
-        <v>-0.3119745551182928</v>
+        <v>0.3793209399157941</v>
       </c>
       <c r="B337" t="n">
-        <v>0.15</v>
+        <v>3.02</v>
       </c>
       <c r="C337" t="n">
-        <v>19.2022</v>
+        <v>22.6528</v>
       </c>
       <c r="D337" t="n">
-        <v>2063.8593</v>
+        <v>2085.6344</v>
       </c>
     </row>
     <row r="338">
       <c r="A338" t="n">
-        <v>-0.4070148636361546</v>
+        <v>0.1241243382342598</v>
       </c>
       <c r="B338" t="n">
-        <v>0.74</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="C338" t="n">
-        <v>18.9528</v>
+        <v>23.0375</v>
       </c>
       <c r="D338" t="n">
-        <v>2062.908</v>
+        <v>2087.8213</v>
       </c>
     </row>
     <row r="339">
       <c r="A339" t="n">
-        <v>0.008704514380979042</v>
+        <v>-0.2578515617051466</v>
       </c>
       <c r="B339" t="n">
         <v>-1.11</v>
       </c>
       <c r="C339" t="n">
-        <v>19.2102</v>
+        <v>22.5988</v>
       </c>
       <c r="D339" t="n">
-        <v>2063.1733</v>
+        <v>2091.3594</v>
       </c>
     </row>
     <row r="340">
       <c r="A340" t="n">
-        <v>0.01251599640786042</v>
+        <v>-0.2562493315866473</v>
       </c>
       <c r="B340" t="n">
-        <v>-0.7799999999999998</v>
+        <v>1.13</v>
       </c>
       <c r="C340" t="n">
-        <v>17.029</v>
+        <v>23.9516</v>
       </c>
       <c r="D340" t="n">
-        <v>2066.1924</v>
+        <v>2094.0139</v>
       </c>
     </row>
     <row r="341">
       <c r="A341" t="n">
-        <v>1.083477195987367</v>
+        <v>-0.9973165021412436</v>
       </c>
       <c r="B341" t="n">
-        <v>0.39</v>
+        <v>-1.96</v>
       </c>
       <c r="C341" t="n">
-        <v>17.1027</v>
+        <v>23.7039</v>
       </c>
       <c r="D341" t="n">
-        <v>2061.1243</v>
+        <v>2093.7194</v>
       </c>
     </row>
     <row r="342">
       <c r="A342" t="n">
-        <v>0.6077911973627611</v>
+        <v>-0.6604606286666543</v>
       </c>
       <c r="B342" t="n">
-        <v>0.25</v>
+        <v>-1.92</v>
       </c>
       <c r="C342" t="n">
-        <v>17.6484</v>
+        <v>21.6256</v>
       </c>
       <c r="D342" t="n">
-        <v>2052.5918</v>
+        <v>2095.6777</v>
       </c>
     </row>
     <row r="343">
       <c r="A343" t="n">
-        <v>0.1113712917863675</v>
+        <v>-1.579685864196572</v>
       </c>
       <c r="B343" t="n">
-        <v>-0.4</v>
+        <v>-3.41</v>
       </c>
       <c r="C343" t="n">
-        <v>17.8452</v>
+        <v>23.8177</v>
       </c>
       <c r="D343" t="n">
-        <v>2051.2713</v>
+        <v>2092.9165</v>
       </c>
     </row>
     <row r="344">
       <c r="A344" t="n">
-        <v>-0.1089601676637249</v>
+        <v>0.329615323418446</v>
       </c>
       <c r="B344" t="n">
-        <v>0.31</v>
+        <v>1.09</v>
       </c>
       <c r="C344" t="n">
-        <v>17.0731</v>
+        <v>23.3102</v>
       </c>
       <c r="D344" t="n">
-        <v>2048.4727</v>
+        <v>2093.1128</v>
       </c>
     </row>
     <row r="345">
       <c r="A345" t="n">
-        <v>-0.2478614454549369</v>
+        <v>-2.442019344547978</v>
       </c>
       <c r="B345" t="n">
-        <v>0.6900000000000001</v>
+        <v>-1.57</v>
       </c>
       <c r="C345" t="n">
-        <v>17.08</v>
+        <v>24.0828</v>
       </c>
       <c r="D345" t="n">
-        <v>2046.5699</v>
+        <v>2091.4717</v>
       </c>
     </row>
     <row r="346">
       <c r="A346" t="n">
-        <v>-0.05198669073701447</v>
+        <v>1.296654542665848</v>
       </c>
       <c r="B346" t="n">
-        <v>-0.04000000000000004</v>
+        <v>1.8</v>
       </c>
       <c r="C346" t="n">
-        <v>17.3267</v>
+        <v>22.5616</v>
       </c>
       <c r="D346" t="n">
-        <v>2048.2747</v>
+        <v>2090.8082</v>
       </c>
     </row>
     <row r="347">
       <c r="A347" t="n">
-        <v>-0.5852633352818732</v>
+        <v>-0.4201638749708452</v>
       </c>
       <c r="B347" t="n">
-        <v>-0.8</v>
+        <v>-1.29</v>
       </c>
       <c r="C347" t="n">
-        <v>17.5211</v>
+        <v>25.2355</v>
       </c>
       <c r="D347" t="n">
-        <v>2048.5739</v>
+        <v>2087.0658</v>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="n">
-        <v>0.4779268084472592</v>
+        <v>0.0947331365135744</v>
       </c>
       <c r="B348" t="n">
-        <v>-0.7400000000000001</v>
+        <v>-1.85</v>
       </c>
       <c r="C348" t="n">
-        <v>18.062</v>
+        <v>23.5919</v>
       </c>
       <c r="D348" t="n">
-        <v>2049.0301</v>
+        <v>2090.7492</v>
       </c>
     </row>
     <row r="349">
       <c r="A349" t="n">
-        <v>1.12387029330252</v>
+        <v>-1.041869345309949</v>
       </c>
       <c r="B349" t="n">
-        <v>0.2</v>
+        <v>-1.38</v>
       </c>
       <c r="C349" t="n">
-        <v>17.6146</v>
+        <v>22.9442</v>
       </c>
       <c r="D349" t="n">
-        <v>2051.2282</v>
+        <v>2090.0509</v>
       </c>
     </row>
     <row r="350">
       <c r="A350" t="n">
-        <v>0.7600656781809082</v>
+        <v>0.7159273245404851</v>
       </c>
       <c r="B350" t="n">
-        <v>-1.54</v>
+        <v>1.31</v>
       </c>
       <c r="C350" t="n">
-        <v>18.9619</v>
+        <v>22.7197</v>
       </c>
       <c r="D350" t="n">
-        <v>2052.2541</v>
+        <v>2092.6011</v>
       </c>
     </row>
     <row r="351">
       <c r="A351" t="n">
-        <v>0.5179830734725821</v>
+        <v>-0.9263788170054164</v>
       </c>
       <c r="B351" t="n">
-        <v>-0.6200000000000001</v>
+        <v>-1.04</v>
       </c>
       <c r="C351" t="n">
-        <v>17.2107</v>
+        <v>24.5002</v>
       </c>
       <c r="D351" t="n">
-        <v>2049.0548</v>
+        <v>2089.0214</v>
       </c>
     </row>
     <row r="352">
       <c r="A352" t="n">
-        <v>0.1463700948373352</v>
+        <v>0.221385917495028</v>
       </c>
       <c r="B352" t="n">
-        <v>-0.36</v>
+        <v>-0.8700000000000001</v>
       </c>
       <c r="C352" t="n">
-        <v>17.4729</v>
+        <v>25.1762</v>
       </c>
       <c r="D352" t="n">
-        <v>2047.5246</v>
+        <v>2089.4069</v>
       </c>
     </row>
     <row r="353">
       <c r="A353" t="n">
-        <v>0.2260374195107392</v>
+        <v>-0.9508557398261663</v>
       </c>
       <c r="B353" t="n">
-        <v>0.74</v>
+        <v>-1.13</v>
       </c>
       <c r="C353" t="n">
-        <v>17.8168</v>
+        <v>26.584</v>
       </c>
       <c r="D353" t="n">
-        <v>2048.2038</v>
+        <v>2086.6604</v>
       </c>
     </row>
     <row r="354">
       <c r="A354" t="n">
-        <v>0.3755383344845591</v>
+        <v>1.235958597118704</v>
       </c>
       <c r="B354" t="n">
-        <v>0.66</v>
+        <v>1.39</v>
       </c>
       <c r="C354" t="n">
-        <v>18.1937</v>
+        <v>26.2669</v>
       </c>
       <c r="D354" t="n">
-        <v>2050.6096</v>
+        <v>2083.1652</v>
       </c>
     </row>
     <row r="355">
       <c r="A355" t="n">
-        <v>-0.001882696200583826</v>
+        <v>0.588679504707995</v>
       </c>
       <c r="B355" t="n">
-        <v>-0.8</v>
+        <v>1.42</v>
       </c>
       <c r="C355" t="n">
-        <v>19.4224</v>
+        <v>25.5064</v>
       </c>
       <c r="D355" t="n">
-        <v>2048.9978</v>
+        <v>2083.737</v>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="n">
-        <v>-0.287018290667396</v>
+        <v>0.4476267389812077</v>
       </c>
       <c r="B356" t="n">
-        <v>-0.05000000000000002</v>
+        <v>0.3100000000000001</v>
       </c>
       <c r="C356" t="n">
-        <v>19.7621</v>
+        <v>23.5374</v>
       </c>
       <c r="D356" t="n">
-        <v>2045.913</v>
+        <v>2087.1256</v>
       </c>
     </row>
     <row r="357">
       <c r="A357" t="n">
-        <v>-0.06613717458440872</v>
+        <v>0.1114144728314727</v>
       </c>
       <c r="B357" t="n">
-        <v>0.8</v>
+        <v>0.19</v>
       </c>
       <c r="C357" t="n">
-        <v>19.4667</v>
+        <v>22.1245</v>
       </c>
       <c r="D357" t="n">
-        <v>2047.6818</v>
+        <v>2087.4893</v>
       </c>
     </row>
     <row r="358">
       <c r="A358" t="n">
-        <v>-0.7574373272889088</v>
+        <v>-0.3288992158927501</v>
       </c>
       <c r="B358" t="n">
-        <v>-0.35</v>
+        <v>-1.12</v>
       </c>
       <c r="C358" t="n">
-        <v>18.1904</v>
+        <v>22.8812</v>
       </c>
       <c r="D358" t="n">
-        <v>2049.8145</v>
+        <v>2085.438</v>
       </c>
     </row>
     <row r="359">
       <c r="A359" t="n">
-        <v>-0.2799768340513978</v>
+        <v>0.3420803556745624</v>
       </c>
       <c r="B359" t="n">
-        <v>-1.17</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="C359" t="n">
-        <v>17.3029</v>
+        <v>22.1754</v>
       </c>
       <c r="D359" t="n">
-        <v>2051.4053</v>
+        <v>2086.9344</v>
       </c>
     </row>
     <row r="360">
       <c r="A360" t="n">
-        <v>0.06912161945264639</v>
+        <v>0.02200349297074541</v>
       </c>
       <c r="B360" t="n">
-        <v>1.99</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="C360" t="n">
-        <v>18.2323</v>
+        <v>22.3959</v>
       </c>
       <c r="D360" t="n">
-        <v>2053.6636</v>
+        <v>2088.0823</v>
       </c>
     </row>
     <row r="361">
       <c r="A361" t="n">
-        <v>-1.409409923545338</v>
+        <v>0.597304244632248</v>
       </c>
       <c r="B361" t="n">
-        <v>1.29</v>
+        <v>0.06999999999999995</v>
       </c>
       <c r="C361" t="n">
-        <v>21.9401</v>
+        <v>22.1415</v>
       </c>
       <c r="D361" t="n">
-        <v>2056.6686</v>
+        <v>2088.6818</v>
       </c>
     </row>
     <row r="362">
       <c r="A362" t="n">
-        <v>-0.4570326993305067</v>
+        <v>-0.1947966513269634</v>
       </c>
       <c r="B362" t="n">
-        <v>1.43</v>
+        <v>-1.84</v>
       </c>
       <c r="C362" t="n">
-        <v>23.9186</v>
+        <v>22.6167</v>
       </c>
       <c r="D362" t="n">
-        <v>2058.4893</v>
+        <v>2087.0893</v>
       </c>
     </row>
     <row r="363">
       <c r="A363" t="n">
-        <v>0.2009780492453022</v>
+        <v>-0.08464940660416365</v>
       </c>
       <c r="B363" t="n">
-        <v>2.98</v>
+        <v>-0.99</v>
       </c>
       <c r="C363" t="n">
-        <v>32.2481</v>
+        <v>21.9032</v>
       </c>
       <c r="D363" t="n">
-        <v>2060.1277</v>
+        <v>2089.5939</v>
       </c>
     </row>
     <row r="364">
       <c r="A364" t="n">
-        <v>1.017860538237279</v>
+        <v>0.02035368363485486</v>
       </c>
       <c r="B364" t="n">
-        <v>-1.14</v>
+        <v>0.4900000000000001</v>
       </c>
       <c r="C364" t="n">
-        <v>31.578</v>
+        <v>21.1278</v>
       </c>
       <c r="D364" t="n">
-        <v>2056.1128</v>
+        <v>2088.1596</v>
       </c>
     </row>
     <row r="365">
       <c r="A365" t="n">
-        <v>-0.6170850956308817</v>
+        <v>0.3293000303286185</v>
       </c>
       <c r="B365" t="n">
-        <v>-0.8700000000000001</v>
+        <v>0.04000000000000004</v>
       </c>
       <c r="C365" t="n">
-        <v>32.5924</v>
+        <v>21.6136</v>
       </c>
       <c r="D365" t="n">
-        <v>2057.4669</v>
+        <v>2087.8649</v>
       </c>
     </row>
     <row r="366">
       <c r="A366" t="n">
-        <v>-0.1541517339677579</v>
+        <v>0.4324453101693392</v>
       </c>
       <c r="B366" t="n">
-        <v>-2.64</v>
+        <v>0.03</v>
       </c>
       <c r="C366" t="n">
-        <v>32.6272</v>
+        <v>20.752</v>
       </c>
       <c r="D366" t="n">
-        <v>2054.6247</v>
+        <v>2088.3656</v>
       </c>
     </row>
     <row r="367">
       <c r="A367" t="n">
-        <v>0.02375965237742454</v>
+        <v>0.01913932708487483</v>
       </c>
       <c r="B367" t="n">
-        <v>-2.18</v>
+        <v>0.1099999999999999</v>
       </c>
       <c r="C367" t="n">
-        <v>31.5775</v>
+        <v>19.777</v>
       </c>
       <c r="D367" t="n">
-        <v>2052.9101</v>
+        <v>2091.2326</v>
       </c>
     </row>
     <row r="368">
       <c r="A368" t="n">
-        <v>0.2807851578762015</v>
+        <v>-0.110815735330507</v>
       </c>
       <c r="B368" t="n">
-        <v>-2.39</v>
+        <v>-0.17</v>
       </c>
       <c r="C368" t="n">
-        <v>28.6628</v>
+        <v>19.7745</v>
       </c>
       <c r="D368" t="n">
-        <v>2055.0751</v>
+        <v>2091.8282</v>
       </c>
     </row>
     <row r="369">
       <c r="A369" t="n">
-        <v>-0.01214612493466853</v>
+        <v>0.2141137705101295</v>
       </c>
       <c r="B369" t="n">
-        <v>-0.46</v>
+        <v>1.52</v>
       </c>
       <c r="C369" t="n">
-        <v>28.7498</v>
+        <v>19.7748</v>
       </c>
       <c r="D369" t="n">
-        <v>2052.5529</v>
+        <v>2093.0316</v>
       </c>
     </row>
     <row r="370">
       <c r="A370" t="n">
-        <v>-0.4394280382975249</v>
+        <v>0.06465490914820572</v>
       </c>
       <c r="B370" t="n">
-        <v>1.89</v>
+        <v>-0.93</v>
       </c>
       <c r="C370" t="n">
-        <v>29.1461</v>
+        <v>19.4418</v>
       </c>
       <c r="D370" t="n">
-        <v>2052.0167</v>
+        <v>2092.7529</v>
       </c>
     </row>
     <row r="371">
       <c r="A371" t="n">
-        <v>-0.08736984385657888</v>
+        <v>0.1130826156114852</v>
       </c>
       <c r="B371" t="n">
-        <v>0.6500000000000004</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="C371" t="n">
-        <v>31.1665</v>
+        <v>18.7592</v>
       </c>
       <c r="D371" t="n">
-        <v>2048.1663</v>
+        <v>2094.5336</v>
       </c>
     </row>
     <row r="372">
       <c r="A372" t="n">
-        <v>-0.3453969104498846</v>
+        <v>0.2906119177310585</v>
       </c>
       <c r="B372" t="n">
-        <v>0.54</v>
+        <v>0.5499999999999999</v>
       </c>
       <c r="C372" t="n">
-        <v>27.3302</v>
+        <v>18.909</v>
       </c>
       <c r="D372" t="n">
-        <v>2048.9198</v>
+        <v>2095.7739</v>
       </c>
     </row>
     <row r="373">
       <c r="A373" t="n">
-        <v>0.1660452726203229</v>
+        <v>-0.1837199559659845</v>
       </c>
       <c r="B373" t="n">
-        <v>-0.21</v>
+        <v>-1.56</v>
       </c>
       <c r="C373" t="n">
-        <v>27.7307</v>
+        <v>19.2177</v>
       </c>
       <c r="D373" t="n">
-        <v>2053.2054</v>
+        <v>2095.5986</v>
       </c>
     </row>
     <row r="374">
       <c r="A374" t="n">
-        <v>-0.1454902249692032</v>
+        <v>-0.4591221339460156</v>
       </c>
       <c r="B374" t="n">
-        <v>-0.8200000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="C374" t="n">
-        <v>26.439</v>
+        <v>18.5433</v>
       </c>
       <c r="D374" t="n">
-        <v>2058.031</v>
+        <v>2095.1236</v>
       </c>
     </row>
     <row r="375">
       <c r="A375" t="n">
-        <v>-0.0854909255259384</v>
+        <v>0.4746784849393956</v>
       </c>
       <c r="B375" t="n">
-        <v>-0.8099999999999999</v>
+        <v>0.7</v>
       </c>
       <c r="C375" t="n">
-        <v>26.2072</v>
+        <v>18.2129</v>
       </c>
       <c r="D375" t="n">
-        <v>2061.1563</v>
+        <v>2095.2317</v>
       </c>
     </row>
     <row r="376">
       <c r="A376" t="n">
-        <v>0.101167662965254</v>
+        <v>0.4597325686991332</v>
       </c>
       <c r="B376" t="n">
-        <v>-0.14</v>
+        <v>-1.58</v>
       </c>
       <c r="C376" t="n">
-        <v>27.1512</v>
+        <v>18.0671</v>
       </c>
       <c r="D376" t="n">
-        <v>2063.1492</v>
+        <v>2094.6511</v>
       </c>
     </row>
     <row r="377">
       <c r="A377" t="n">
-        <v>0.6791277225087203</v>
+        <v>0.5820072239501736</v>
       </c>
       <c r="B377" t="n">
-        <v>0.8799999999999999</v>
+        <v>1.08</v>
       </c>
       <c r="C377" t="n">
-        <v>30.0846</v>
+        <v>18.9914</v>
       </c>
       <c r="D377" t="n">
-        <v>2059.0562</v>
+        <v>2093.5424</v>
       </c>
     </row>
     <row r="378">
       <c r="A378" t="n">
-        <v>0.1750268393619951</v>
+        <v>-0.03424267203151301</v>
       </c>
       <c r="B378" t="n">
-        <v>0.13</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="C378" t="n">
-        <v>28.7435</v>
+        <v>18.9387</v>
       </c>
       <c r="D378" t="n">
-        <v>2060.4051</v>
+        <v>2095.3857</v>
       </c>
     </row>
     <row r="379">
       <c r="A379" t="n">
-        <v>0.05339659882991234</v>
+        <v>0.6080630306729995</v>
       </c>
       <c r="B379" t="n">
-        <v>-0.3300000000000001</v>
+        <v>-1.21</v>
       </c>
       <c r="C379" t="n">
-        <v>28.2049</v>
+        <v>18.8088</v>
       </c>
       <c r="D379" t="n">
-        <v>2061.2603</v>
+        <v>2097.0258</v>
       </c>
     </row>
     <row r="380">
       <c r="A380" t="n">
-        <v>-0.02064576784401388</v>
+        <v>0.1552079593522485</v>
       </c>
       <c r="B380" t="n">
-        <v>-1.15</v>
+        <v>-0.7200000000000001</v>
       </c>
       <c r="C380" t="n">
-        <v>28.7538</v>
+        <v>18.9297</v>
       </c>
       <c r="D380" t="n">
-        <v>2063.3552</v>
+        <v>2097.1161</v>
       </c>
     </row>
     <row r="381">
       <c r="A381" t="n">
-        <v>0.1723302947246543</v>
+        <v>0.2315372900578778</v>
       </c>
       <c r="B381" t="n">
-        <v>-0.21</v>
+        <v>-0.6699999999999999</v>
       </c>
       <c r="C381" t="n">
-        <v>28.9244</v>
+        <v>18.6693</v>
       </c>
       <c r="D381" t="n">
-        <v>2061.496</v>
+        <v>2097.8772</v>
       </c>
     </row>
     <row r="382">
       <c r="A382" t="n">
-        <v>0.2286805901218046</v>
+        <v>-0.4823191751902871</v>
       </c>
       <c r="B382" t="n">
-        <v>-0.76</v>
+        <v>0.1899999999999999</v>
       </c>
       <c r="C382" t="n">
-        <v>29.9679</v>
+        <v>19.1571</v>
       </c>
       <c r="D382" t="n">
-        <v>2062.0547</v>
+        <v>2101.6458</v>
       </c>
     </row>
     <row r="383">
       <c r="A383" t="n">
-        <v>0.3391730139668492</v>
+        <v>0.07175444290022254</v>
       </c>
       <c r="B383" t="n">
-        <v>-2.27</v>
+        <v>0.22</v>
       </c>
       <c r="C383" t="n">
-        <v>30.8769</v>
+        <v>19.1982</v>
       </c>
       <c r="D383" t="n">
-        <v>2064.4821</v>
+        <v>2102.9645</v>
       </c>
     </row>
     <row r="384">
       <c r="A384" t="n">
-        <v>0.347836449650004</v>
+        <v>0.05673470425919871</v>
       </c>
       <c r="B384" t="n">
-        <v>1.59</v>
+        <v>0.17</v>
       </c>
       <c r="C384" t="n">
-        <v>30.4541</v>
+        <v>19.4262</v>
       </c>
       <c r="D384" t="n">
-        <v>2064.4078</v>
+        <v>2103.8624</v>
       </c>
     </row>
     <row r="385">
       <c r="A385" t="n">
-        <v>-0.1048498197690194</v>
+        <v>-0.1777229517976215</v>
       </c>
       <c r="B385" t="n">
-        <v>-1.98</v>
+        <v>-1.25</v>
       </c>
       <c r="C385" t="n">
-        <v>30.5483</v>
+        <v>19.3801</v>
       </c>
       <c r="D385" t="n">
-        <v>2064.6943</v>
+        <v>2104.1995</v>
       </c>
     </row>
     <row r="386">
       <c r="A386" t="n">
-        <v>0.4815587750806036</v>
+        <v>0.3180665544703184</v>
       </c>
       <c r="B386" t="n">
-        <v>0.39</v>
+        <v>1.54</v>
       </c>
       <c r="C386" t="n">
-        <v>29.8154</v>
+        <v>19.4327</v>
       </c>
       <c r="D386" t="n">
-        <v>2060.9477</v>
+        <v>2105.3535</v>
       </c>
     </row>
     <row r="387">
       <c r="A387" t="n">
-        <v>0.3043236488818282</v>
+        <v>-0.3116311021540524</v>
       </c>
       <c r="B387" t="n">
-        <v>0.41</v>
+        <v>-1.26</v>
       </c>
       <c r="C387" t="n">
-        <v>29.8255</v>
+        <v>20.0875</v>
       </c>
       <c r="D387" t="n">
-        <v>2062.5237</v>
+        <v>2103.6186</v>
       </c>
     </row>
     <row r="388">
       <c r="A388" t="n">
-        <v>0.1858752382657002</v>
+        <v>-0.3168260944495008</v>
       </c>
       <c r="B388" t="n">
-        <v>1.28</v>
+        <v>0.72</v>
       </c>
       <c r="C388" t="n">
-        <v>28.8792</v>
+        <v>19.749</v>
       </c>
       <c r="D388" t="n">
-        <v>2061.2774</v>
+        <v>2103.4145</v>
       </c>
     </row>
     <row r="389">
       <c r="A389" t="n">
-        <v>0.5124650578877578</v>
+        <v>-0.1089873489847209</v>
       </c>
       <c r="B389" t="n">
-        <v>1.28</v>
+        <v>-0.6599999999999999</v>
       </c>
       <c r="C389" t="n">
-        <v>28.5233</v>
+        <v>19.4142</v>
       </c>
       <c r="D389" t="n">
-        <v>2060.3407</v>
+        <v>2104.9352</v>
       </c>
     </row>
     <row r="390">
       <c r="A390" t="n">
-        <v>-0.2019432798288029</v>
+        <v>0.2897674527561269</v>
       </c>
       <c r="B390" t="n">
-        <v>-0.54</v>
+        <v>1.77</v>
       </c>
       <c r="C390" t="n">
-        <v>27.9998</v>
+        <v>19.2813</v>
       </c>
       <c r="D390" t="n">
-        <v>2060.9142</v>
+        <v>2106.2075</v>
       </c>
     </row>
     <row r="391">
       <c r="A391" t="n">
-        <v>0.8022244543674927</v>
+        <v>-0.4069362723584605</v>
       </c>
       <c r="B391" t="n">
-        <v>0.46</v>
+        <v>-0.38</v>
       </c>
       <c r="C391" t="n">
-        <v>27.4483</v>
+        <v>19.0242</v>
       </c>
       <c r="D391" t="n">
-        <v>2063.3794</v>
+        <v>2106.8796</v>
       </c>
     </row>
     <row r="392">
       <c r="A392" t="n">
-        <v>0.3753299223166834</v>
+        <v>-0.3186306038526556</v>
       </c>
       <c r="B392" t="n">
-        <v>0.27</v>
+        <v>-1.44</v>
       </c>
       <c r="C392" t="n">
-        <v>30.2625</v>
+        <v>19.0084</v>
       </c>
       <c r="D392" t="n">
-        <v>2067.859</v>
+        <v>2107.4723</v>
       </c>
     </row>
     <row r="393">
       <c r="A393" t="n">
-        <v>0.2991527888771632</v>
+        <v>-0.7421399665769901</v>
       </c>
       <c r="B393" t="n">
-        <v>-1.01</v>
+        <v>-0.04000000000000004</v>
       </c>
       <c r="C393" t="n">
-        <v>29.9538</v>
+        <v>18.7897</v>
       </c>
       <c r="D393" t="n">
-        <v>2068.9295</v>
+        <v>2107.0019</v>
       </c>
     </row>
     <row r="394">
       <c r="A394" t="n">
-        <v>0.594232145394729</v>
+        <v>1.018214017666247</v>
       </c>
       <c r="B394" t="n">
-        <v>0.3100000000000001</v>
+        <v>-0.48</v>
       </c>
       <c r="C394" t="n">
-        <v>28.9213</v>
+        <v>18.6727</v>
       </c>
       <c r="D394" t="n">
-        <v>2065.9478</v>
+        <v>2108.2059</v>
       </c>
     </row>
     <row r="395">
       <c r="A395" t="n">
-        <v>0.1694701362528615</v>
+        <v>0.5614519488430546</v>
       </c>
       <c r="B395" t="n">
-        <v>0.1499999999999999</v>
+        <v>1.03</v>
       </c>
       <c r="C395" t="n">
-        <v>28.431</v>
+        <v>18.9572</v>
       </c>
       <c r="D395" t="n">
-        <v>2062.9605</v>
+        <v>2109.85</v>
       </c>
     </row>
     <row r="396">
       <c r="A396" t="n">
-        <v>-0.1969337692255609</v>
+        <v>0.6525531406170764</v>
       </c>
       <c r="B396" t="n">
-        <v>0.02000000000000002</v>
+        <v>-0.9099999999999999</v>
       </c>
       <c r="C396" t="n">
-        <v>28.2941</v>
+        <v>19.1744</v>
       </c>
       <c r="D396" t="n">
-        <v>2062.4983</v>
+        <v>2111.5598</v>
       </c>
     </row>
     <row r="397">
       <c r="A397" t="n">
-        <v>0.5569358152079084</v>
+        <v>0.07558620400016472</v>
       </c>
       <c r="B397" t="n">
-        <v>-0.4</v>
+        <v>-0.28</v>
       </c>
       <c r="C397" t="n">
-        <v>27.4477</v>
+        <v>19.2425</v>
       </c>
       <c r="D397" t="n">
-        <v>2065.1208</v>
+        <v>2109.6774</v>
       </c>
     </row>
     <row r="398">
       <c r="A398" t="n">
-        <v>0.03693755866469806</v>
+        <v>0.2559922178754336</v>
       </c>
       <c r="B398" t="n">
-        <v>0.92</v>
+        <v>1.24</v>
       </c>
       <c r="C398" t="n">
-        <v>26.9462</v>
+        <v>19.5383</v>
       </c>
       <c r="D398" t="n">
-        <v>2063.2499</v>
+        <v>2113.0163</v>
       </c>
     </row>
     <row r="399">
       <c r="A399" t="n">
-        <v>0.3674653598260576</v>
+        <v>0.3811203514799183</v>
       </c>
       <c r="B399" t="n">
-        <v>1.44</v>
+        <v>1.13</v>
       </c>
       <c r="C399" t="n">
-        <v>27.9534</v>
+        <v>20.3405</v>
       </c>
       <c r="D399" t="n">
-        <v>2058.7601</v>
+        <v>2114.929</v>
       </c>
     </row>
     <row r="400">
       <c r="A400" t="n">
-        <v>0.4425255242541403</v>
+        <v>0.05885695872314295</v>
       </c>
       <c r="B400" t="n">
-        <v>-0.6900000000000001</v>
+        <v>-0.52</v>
       </c>
       <c r="C400" t="n">
-        <v>25.8912</v>
+        <v>19.9784</v>
       </c>
       <c r="D400" t="n">
-        <v>2058.8882</v>
+        <v>2115.1226</v>
       </c>
     </row>
     <row r="401">
       <c r="A401" t="n">
-        <v>0.9890934651842785</v>
+        <v>-0.001808346734609015</v>
       </c>
       <c r="B401" t="n">
-        <v>1.08</v>
+        <v>-0.77</v>
       </c>
       <c r="C401" t="n">
-        <v>26.3336</v>
+        <v>19.3556</v>
       </c>
       <c r="D401" t="n">
-        <v>2060.5438</v>
+        <v>2116.0544</v>
       </c>
     </row>
     <row r="402">
       <c r="A402" t="n">
-        <v>1.549580748516687</v>
+        <v>0.2698959125255116</v>
       </c>
       <c r="B402" t="n">
-        <v>-1</v>
+        <v>0.4</v>
       </c>
       <c r="C402" t="n">
-        <v>25.9974</v>
+        <v>19.4177</v>
       </c>
       <c r="D402" t="n">
-        <v>2060.0879</v>
+        <v>2117.2621</v>
       </c>
     </row>
     <row r="403">
       <c r="A403" t="n">
-        <v>0.7328379875497087</v>
+        <v>0.1630774635971958</v>
       </c>
       <c r="B403" t="n">
-        <v>-0.14</v>
+        <v>-1.11</v>
       </c>
       <c r="C403" t="n">
-        <v>25.8876</v>
+        <v>19.076</v>
       </c>
       <c r="D403" t="n">
-        <v>2061.5994</v>
+        <v>2117.6397</v>
       </c>
     </row>
     <row r="404">
       <c r="A404" t="n">
-        <v>0.6681902178220492</v>
+        <v>-0.1641110009042345</v>
       </c>
       <c r="B404" t="n">
-        <v>-0.42</v>
+        <v>-0.43</v>
       </c>
       <c r="C404" t="n">
-        <v>26.305</v>
+        <v>19.0797</v>
       </c>
       <c r="D404" t="n">
-        <v>2059.885</v>
+        <v>2118.7473</v>
       </c>
     </row>
     <row r="405">
       <c r="A405" t="n">
-        <v>0.4136923418488185</v>
+        <v>0.8743429927963244</v>
       </c>
       <c r="B405" t="n">
-        <v>0.7499999999999999</v>
+        <v>2.91</v>
       </c>
       <c r="C405" t="n">
-        <v>26.378</v>
+        <v>21.1064</v>
       </c>
       <c r="D405" t="n">
-        <v>2057.6665</v>
+        <v>2122.031</v>
       </c>
     </row>
     <row r="406">
       <c r="A406" t="n">
-        <v>0.5860758598072624</v>
+        <v>0.2091648152731024</v>
       </c>
       <c r="B406" t="n">
-        <v>-0.65</v>
+        <v>0</v>
       </c>
       <c r="C406" t="n">
-        <v>26.2348</v>
+        <v>21.1007</v>
       </c>
       <c r="D406" t="n">
-        <v>2055.4828</v>
+        <v>2123.1245</v>
       </c>
     </row>
     <row r="407">
       <c r="A407" t="n">
-        <v>0.8461319442258021</v>
+        <v>-0.08549890383176101</v>
       </c>
       <c r="B407" t="n">
-        <v>0.05000000000000004</v>
+        <v>-0.7000000000000001</v>
       </c>
       <c r="C407" t="n">
-        <v>26.5603</v>
+        <v>22.1277</v>
       </c>
       <c r="D407" t="n">
-        <v>2051.9294</v>
+        <v>2123.5112</v>
       </c>
     </row>
     <row r="408">
       <c r="A408" t="n">
-        <v>-0.2019551043149955</v>
+        <v>-0.09501297303466</v>
       </c>
       <c r="B408" t="n">
-        <v>0.4700000000000001</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="C408" t="n">
-        <v>25.9072</v>
+        <v>21.909</v>
       </c>
       <c r="D408" t="n">
-        <v>2053.1224</v>
+        <v>2122.8908</v>
       </c>
     </row>
     <row r="409">
       <c r="A409" t="n">
-        <v>0.2825127366599728</v>
+        <v>-0.1772072033832704</v>
       </c>
       <c r="B409" t="n">
-        <v>1.52</v>
+        <v>-2.04</v>
       </c>
       <c r="C409" t="n">
-        <v>26.6721</v>
+        <v>22.3933</v>
       </c>
       <c r="D409" t="n">
-        <v>2050.7723</v>
+        <v>2124.1473</v>
       </c>
     </row>
     <row r="410">
       <c r="A410" t="n">
-        <v>-0.4253604611503762</v>
+        <v>-0.2793345739690479</v>
       </c>
       <c r="B410" t="n">
-        <v>3.84</v>
+        <v>-0.57</v>
       </c>
       <c r="C410" t="n">
-        <v>24.9678</v>
+        <v>22.1533</v>
       </c>
       <c r="D410" t="n">
-        <v>2051.1471</v>
+        <v>2125.2048</v>
       </c>
     </row>
     <row r="411">
       <c r="A411" t="n">
-        <v>0.2378829508711436</v>
+        <v>-0.2966584511057194</v>
       </c>
       <c r="B411" t="n">
-        <v>-1.01</v>
+        <v>0.6099999999999999</v>
       </c>
       <c r="C411" t="n">
-        <v>23.7657</v>
+        <v>20.7529</v>
       </c>
       <c r="D411" t="n">
-        <v>2052.7524</v>
+        <v>2123.5362</v>
       </c>
     </row>
     <row r="412">
       <c r="A412" t="n">
-        <v>0.8491227840999279</v>
+        <v>-0.5201972839398272</v>
       </c>
       <c r="B412" t="n">
-        <v>-0.7000000000000001</v>
+        <v>-0.78</v>
       </c>
       <c r="C412" t="n">
-        <v>22.5006</v>
+        <v>19.963</v>
       </c>
       <c r="D412" t="n">
-        <v>2053.3378</v>
+        <v>2123.0857</v>
       </c>
     </row>
     <row r="413">
       <c r="A413" t="n">
-        <v>0.07829400982331507</v>
+        <v>-0.01293556602023668</v>
       </c>
       <c r="B413" t="n">
-        <v>0.22</v>
+        <v>0.13</v>
       </c>
       <c r="C413" t="n">
-        <v>22.0246</v>
+        <v>20.121</v>
       </c>
       <c r="D413" t="n">
-        <v>2055.0832</v>
+        <v>2123.0207</v>
       </c>
     </row>
     <row r="414">
       <c r="A414" t="n">
-        <v>0.2578305662695714</v>
+        <v>-0.158094238386997</v>
       </c>
       <c r="B414" t="n">
-        <v>0.34</v>
+        <v>-1.44</v>
       </c>
       <c r="C414" t="n">
-        <v>21.2899</v>
+        <v>20.7033</v>
       </c>
       <c r="D414" t="n">
-        <v>2055.8168</v>
+        <v>2121.4058</v>
       </c>
     </row>
     <row r="415">
       <c r="A415" t="n">
-        <v>0.6354530078191548</v>
+        <v>-0.2635075247000779</v>
       </c>
       <c r="B415" t="n">
-        <v>-1.12</v>
+        <v>0.18</v>
       </c>
       <c r="C415" t="n">
-        <v>21.4342</v>
+        <v>21.25</v>
       </c>
       <c r="D415" t="n">
-        <v>2056.2328</v>
+        <v>2119.7892</v>
       </c>
     </row>
     <row r="416">
       <c r="A416" t="n">
-        <v>-0.2226307339338733</v>
+        <v>0.1316623893981388</v>
       </c>
       <c r="B416" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="C416" t="n">
-        <v>22.6796</v>
+        <v>20.3949</v>
       </c>
       <c r="D416" t="n">
-        <v>2059.5642</v>
+        <v>2119.761</v>
       </c>
     </row>
     <row r="417">
       <c r="A417" t="n">
-        <v>0.1811290725984434</v>
+        <v>-0.874360142403348</v>
       </c>
       <c r="B417" t="n">
-        <v>-1.04</v>
+        <v>-0.54</v>
       </c>
       <c r="C417" t="n">
-        <v>23.0742</v>
+        <v>19.6225</v>
       </c>
       <c r="D417" t="n">
-        <v>2060.1538</v>
+        <v>2121.6548</v>
       </c>
     </row>
     <row r="418">
       <c r="A418" t="n">
-        <v>-0.08921457711908976</v>
+        <v>-1.650325287283898</v>
       </c>
       <c r="B418" t="n">
-        <v>0.3700000000000001</v>
+        <v>-0.2</v>
       </c>
       <c r="C418" t="n">
-        <v>23.3064</v>
+        <v>19.7808</v>
       </c>
       <c r="D418" t="n">
-        <v>2059.4426</v>
+        <v>2120.319</v>
       </c>
     </row>
     <row r="419">
       <c r="A419" t="n">
-        <v>0.284066726480739</v>
+        <v>-1.300768490976739</v>
       </c>
       <c r="B419" t="n">
-        <v>-0.5299999999999999</v>
+        <v>-0.8</v>
       </c>
       <c r="C419" t="n">
-        <v>22.6863</v>
+        <v>19.4741</v>
       </c>
       <c r="D419" t="n">
-        <v>2060.6383</v>
+        <v>2119.482</v>
       </c>
     </row>
     <row r="420">
       <c r="A420" t="n">
-        <v>0.2357764108598189</v>
+        <v>-0.04871031570164472</v>
       </c>
       <c r="B420" t="n">
-        <v>1</v>
+        <v>0.8800000000000001</v>
       </c>
       <c r="C420" t="n">
-        <v>23.8224</v>
+        <v>20.4945</v>
       </c>
       <c r="D420" t="n">
-        <v>2057.8931</v>
+        <v>2117.7567</v>
       </c>
     </row>
     <row r="421">
       <c r="A421" t="n">
-        <v>0.241253183422836</v>
+        <v>-0.5600853582315565</v>
       </c>
       <c r="B421" t="n">
-        <v>0.95</v>
+        <v>-1.84</v>
       </c>
       <c r="C421" t="n">
-        <v>24.1656</v>
+        <v>19.4735</v>
       </c>
       <c r="D421" t="n">
-        <v>2056.8243</v>
+        <v>2118.0355</v>
       </c>
     </row>
     <row r="422">
       <c r="A422" t="n">
-        <v>1.189053293047344</v>
+        <v>-1.187403999739662</v>
       </c>
       <c r="B422" t="n">
-        <v>1.91</v>
+        <v>-1.9</v>
       </c>
       <c r="C422" t="n">
-        <v>25.3868</v>
+        <v>19.5326</v>
       </c>
       <c r="D422" t="n">
-        <v>2056.7929</v>
+        <v>2118.5873</v>
       </c>
     </row>
     <row r="423">
       <c r="A423" t="n">
-        <v>-0.3012643377225889</v>
+        <v>-0.3148076986038597</v>
       </c>
       <c r="B423" t="n">
-        <v>-1.36</v>
+        <v>-2.2</v>
       </c>
       <c r="C423" t="n">
-        <v>26.5441</v>
+        <v>19.9395</v>
       </c>
       <c r="D423" t="n">
-        <v>2057.3071</v>
+        <v>2120.8485</v>
       </c>
     </row>
     <row r="424">
       <c r="A424" t="n">
-        <v>-0.3569044452761015</v>
+        <v>-0.2441845779555829</v>
       </c>
       <c r="B424" t="n">
-        <v>-0.21</v>
+        <v>0.51</v>
       </c>
       <c r="C424" t="n">
-        <v>27.1499</v>
+        <v>19.559</v>
       </c>
       <c r="D424" t="n">
-        <v>2056.2925</v>
+        <v>2121.469</v>
       </c>
     </row>
     <row r="425">
       <c r="A425" t="n">
-        <v>0.1178667247299918</v>
+        <v>-0.3718757559313725</v>
       </c>
       <c r="B425" t="n">
-        <v>-1.42</v>
+        <v>-0.47</v>
       </c>
       <c r="C425" t="n">
-        <v>22.0307</v>
+        <v>18.2481</v>
       </c>
       <c r="D425" t="n">
-        <v>2058.5821</v>
+        <v>2122.9311</v>
       </c>
     </row>
     <row r="426">
       <c r="A426" t="n">
-        <v>0.1153935191514724</v>
+        <v>0.5116612361480156</v>
       </c>
       <c r="B426" t="n">
-        <v>-0.07000000000000028</v>
+        <v>1.38</v>
       </c>
       <c r="C426" t="n">
-        <v>23.8191</v>
+        <v>17.5055</v>
       </c>
       <c r="D426" t="n">
-        <v>2061.8022</v>
+        <v>2123.542</v>
       </c>
     </row>
     <row r="427">
       <c r="A427" t="n">
-        <v>0.4474428221032022</v>
+        <v>0.548728649812747</v>
       </c>
       <c r="B427" t="n">
-        <v>-0.28</v>
+        <v>1.1</v>
       </c>
       <c r="C427" t="n">
-        <v>23.6512</v>
+        <v>17.7495</v>
       </c>
       <c r="D427" t="n">
-        <v>2062.5415</v>
+        <v>2125.435</v>
       </c>
     </row>
     <row r="428">
       <c r="A428" t="n">
-        <v>0.2561242719600338</v>
+        <v>0.2885395324466513</v>
       </c>
       <c r="B428" t="n">
-        <v>0.42</v>
+        <v>-1.3</v>
       </c>
       <c r="C428" t="n">
-        <v>22.9206</v>
+        <v>18.0178</v>
       </c>
       <c r="D428" t="n">
-        <v>2061.4302</v>
+        <v>2126.3947</v>
       </c>
     </row>
     <row r="429">
       <c r="A429" t="n">
-        <v>-0.06806603290468816</v>
+        <v>-1.669009056457971</v>
       </c>
       <c r="B429" t="n">
-        <v>0.9399999999999999</v>
+        <v>-0.2400000000000001</v>
       </c>
       <c r="C429" t="n">
-        <v>23.3983</v>
+        <v>17.8143</v>
       </c>
       <c r="D429" t="n">
-        <v>2060.7434</v>
+        <v>2125.3949</v>
       </c>
     </row>
     <row r="430">
       <c r="A430" t="n">
-        <v>0.142646631873343</v>
+        <v>0.123087211736413</v>
       </c>
       <c r="B430" t="n">
-        <v>0.5600000000000001</v>
+        <v>-0.6699999999999999</v>
       </c>
       <c r="C430" t="n">
-        <v>23.2325</v>
+        <v>18.3645</v>
       </c>
       <c r="D430" t="n">
-        <v>2060.3506</v>
+        <v>2126.9833</v>
       </c>
     </row>
     <row r="431">
       <c r="A431" t="n">
-        <v>-0.2639851356550851</v>
+        <v>1.399753408988789</v>
       </c>
       <c r="B431" t="n">
-        <v>-0.07000000000000006</v>
+        <v>2.66</v>
       </c>
       <c r="C431" t="n">
-        <v>22.4484</v>
+        <v>17.9983</v>
       </c>
       <c r="D431" t="n">
-        <v>2059.9631</v>
+        <v>2126.6776</v>
       </c>
     </row>
     <row r="432">
       <c r="A432" t="n">
-        <v>-0.1897780418440036</v>
+        <v>-0.9782662337962477</v>
       </c>
       <c r="B432" t="n">
-        <v>-0.6799999999999999</v>
+        <v>-2.72</v>
       </c>
       <c r="C432" t="n">
-        <v>21.8307</v>
+        <v>18.7065</v>
       </c>
       <c r="D432" t="n">
-        <v>2062.199</v>
+        <v>2125.6305</v>
       </c>
     </row>
     <row r="433">
       <c r="A433" t="n">
-        <v>-0.5620666233496405</v>
+        <v>0.9240189476418803</v>
       </c>
       <c r="B433" t="n">
-        <v>1.97</v>
+        <v>-1.52</v>
       </c>
       <c r="C433" t="n">
-        <v>21.9918</v>
+        <v>17.9774</v>
       </c>
       <c r="D433" t="n">
-        <v>2062.3725</v>
+        <v>2127.4551</v>
       </c>
     </row>
     <row r="434">
       <c r="A434" t="n">
-        <v>-0.2895603911588858</v>
+        <v>0.2778124612712604</v>
       </c>
       <c r="B434" t="n">
-        <v>0.41</v>
+        <v>0.4</v>
       </c>
       <c r="C434" t="n">
-        <v>22.2597</v>
+        <v>17.7327</v>
       </c>
       <c r="D434" t="n">
-        <v>2063.3727</v>
+        <v>2127.8785</v>
       </c>
     </row>
     <row r="435">
       <c r="A435" t="n">
-        <v>0.1480918749776566</v>
+        <v>0.06653714254291682</v>
       </c>
       <c r="B435" t="n">
-        <v>1.25</v>
+        <v>-1.02</v>
       </c>
       <c r="C435" t="n">
-        <v>22.6537</v>
+        <v>17.3215</v>
       </c>
       <c r="D435" t="n">
-        <v>2062.4348</v>
+        <v>2130.0621</v>
       </c>
     </row>
     <row r="436">
       <c r="A436" t="n">
-        <v>-1.539159580146105</v>
+        <v>0.2807106048191867</v>
       </c>
       <c r="B436" t="n">
-        <v>-1.36</v>
+        <v>-1.63</v>
       </c>
       <c r="C436" t="n">
-        <v>22.6375</v>
+        <v>18.1722</v>
       </c>
       <c r="D436" t="n">
-        <v>2062.4296</v>
+        <v>2134.1274</v>
       </c>
     </row>
     <row r="437">
       <c r="A437" t="n">
-        <v>-0.859490677557314</v>
+        <v>-0.2733032846701364</v>
       </c>
       <c r="B437" t="n">
-        <v>-0.8300000000000001</v>
+        <v>-0.96</v>
       </c>
       <c r="C437" t="n">
-        <v>22.8111</v>
+        <v>18.1247</v>
       </c>
       <c r="D437" t="n">
-        <v>2062.7353</v>
+        <v>2134.6736</v>
       </c>
     </row>
     <row r="438">
       <c r="A438" t="n">
-        <v>-0.4868970808586481</v>
+        <v>0.2749274175489009</v>
       </c>
       <c r="B438" t="n">
-        <v>0.5399999999999999</v>
+        <v>-1.3</v>
       </c>
       <c r="C438" t="n">
-        <v>22.3861</v>
+        <v>18.6317</v>
       </c>
       <c r="D438" t="n">
-        <v>2064.0569</v>
+        <v>2139.8946</v>
       </c>
     </row>
     <row r="439">
       <c r="A439" t="n">
-        <v>-0.174732228313445</v>
+        <v>0.5577046477752349</v>
       </c>
       <c r="B439" t="n">
-        <v>0.5</v>
+        <v>-0.4400000000000001</v>
       </c>
       <c r="C439" t="n">
-        <v>22.1537</v>
+        <v>18.3296</v>
       </c>
       <c r="D439" t="n">
-        <v>2064.5509</v>
+        <v>2142.4987</v>
       </c>
     </row>
     <row r="440">
       <c r="A440" t="n">
-        <v>0.4307777996946944</v>
+        <v>-0.8981990405896221</v>
       </c>
       <c r="B440" t="n">
-        <v>1.12</v>
+        <v>-0.3400000000000001</v>
       </c>
       <c r="C440" t="n">
-        <v>23.0549</v>
+        <v>18.3811</v>
       </c>
       <c r="D440" t="n">
-        <v>2062.6346</v>
+        <v>2143.4021</v>
       </c>
     </row>
     <row r="441">
       <c r="A441" t="n">
-        <v>-0.3463168892810153</v>
+        <v>0.4971228326458268</v>
       </c>
       <c r="B441" t="n">
-        <v>-0.48</v>
+        <v>2.18</v>
       </c>
       <c r="C441" t="n">
-        <v>23.8637</v>
+        <v>18.0057</v>
       </c>
       <c r="D441" t="n">
-        <v>2064.2619</v>
+        <v>2143.8128</v>
       </c>
     </row>
     <row r="442">
       <c r="A442" t="n">
-        <v>-0.3154422660035243</v>
+        <v>-0.01343418346449049</v>
       </c>
       <c r="B442" t="n">
-        <v>-0.7799999999999998</v>
+        <v>-1.03</v>
       </c>
       <c r="C442" t="n">
-        <v>23.813</v>
+        <v>18.1182</v>
       </c>
       <c r="D442" t="n">
-        <v>2066.4578</v>
+        <v>2144.7864</v>
       </c>
     </row>
     <row r="443">
       <c r="A443" t="n">
-        <v>-0.3639069665509447</v>
+        <v>1.180986081962199</v>
       </c>
       <c r="B443" t="n">
-        <v>0.97</v>
+        <v>0.78</v>
       </c>
       <c r="C443" t="n">
-        <v>22.2728</v>
+        <v>18.2756</v>
       </c>
       <c r="D443" t="n">
-        <v>2067.3914</v>
+        <v>2145.4036</v>
       </c>
     </row>
     <row r="444">
       <c r="A444" t="n">
-        <v>0.5338282078362225</v>
+        <v>0.3185157320714218</v>
       </c>
       <c r="B444" t="n">
-        <v>-0.72</v>
+        <v>-0.8700000000000001</v>
       </c>
       <c r="C444" t="n">
-        <v>21.7345</v>
+        <v>18.6459</v>
       </c>
       <c r="D444" t="n">
-        <v>2069.9632</v>
+        <v>2146.2281</v>
       </c>
     </row>
     <row r="445">
       <c r="A445" t="n">
-        <v>0.7903602433356404</v>
+        <v>0.4487592543323342</v>
       </c>
       <c r="B445" t="n">
-        <v>0.6699999999999999</v>
+        <v>-1.72</v>
       </c>
       <c r="C445" t="n">
-        <v>21.3545</v>
+        <v>18.1343</v>
       </c>
       <c r="D445" t="n">
-        <v>2069.087</v>
+        <v>2148.7748</v>
       </c>
     </row>
     <row r="446">
       <c r="A446" t="n">
-        <v>0.1827243622059964</v>
+        <v>-1.657804390121566</v>
       </c>
       <c r="B446" t="n">
-        <v>-0.6799999999999999</v>
+        <v>-0.52</v>
       </c>
       <c r="C446" t="n">
-        <v>22.4904</v>
+        <v>18.0415</v>
       </c>
       <c r="D446" t="n">
-        <v>2071.7721</v>
+        <v>2149.9787</v>
       </c>
     </row>
     <row r="447">
       <c r="A447" t="n">
-        <v>0.3821730564413524</v>
+        <v>-2.176827403195837</v>
       </c>
       <c r="B447" t="n">
-        <v>1</v>
+        <v>-0.14</v>
       </c>
       <c r="C447" t="n">
-        <v>22.3315</v>
+        <v>17.9462</v>
       </c>
       <c r="D447" t="n">
-        <v>2070.4622</v>
+        <v>2150.2177</v>
       </c>
     </row>
     <row r="448">
       <c r="A448" t="n">
-        <v>0.326353180789538</v>
+        <v>-2.290824657699583</v>
       </c>
       <c r="B448" t="n">
-        <v>1.57</v>
+        <v>-2.57</v>
       </c>
       <c r="C448" t="n">
-        <v>21.8077</v>
+        <v>21.3343</v>
       </c>
       <c r="D448" t="n">
-        <v>2068.4398</v>
+        <v>2149.6827</v>
       </c>
     </row>
     <row r="449">
       <c r="A449" t="n">
-        <v>0.3853917088178178</v>
+        <v>-1.776154536920585</v>
       </c>
       <c r="B449" t="n">
-        <v>-0.6</v>
+        <v>-0.52</v>
       </c>
       <c r="C449" t="n">
-        <v>21.3363</v>
+        <v>23.3302</v>
       </c>
       <c r="D449" t="n">
-        <v>2068.1827</v>
+        <v>2145.2571</v>
       </c>
     </row>
     <row r="450">
       <c r="A450" t="n">
-        <v>-0.1258893612059702</v>
+        <v>0.7627754478016122</v>
       </c>
       <c r="B450" t="n">
-        <v>-1.89</v>
+        <v>2.99</v>
       </c>
       <c r="C450" t="n">
-        <v>20.6565</v>
+        <v>22.1249</v>
       </c>
       <c r="D450" t="n">
-        <v>2065.3101</v>
+        <v>2144.0853</v>
       </c>
     </row>
     <row r="451">
       <c r="A451" t="n">
-        <v>-0.4374467466156073</v>
+        <v>-0.3260576115459238</v>
       </c>
       <c r="B451" t="n">
-        <v>0.2399999999999999</v>
+        <v>-2.88</v>
       </c>
       <c r="C451" t="n">
-        <v>20.6335</v>
+        <v>20.5261</v>
       </c>
       <c r="D451" t="n">
-        <v>2066.2655</v>
+        <v>2146.8894</v>
       </c>
     </row>
     <row r="452">
       <c r="A452" t="n">
-        <v>0.2364383534565805</v>
+        <v>-0.8816196708807509</v>
       </c>
       <c r="B452" t="n">
-        <v>1.04</v>
+        <v>-2.33</v>
       </c>
       <c r="C452" t="n">
-        <v>20.3451</v>
+        <v>19.973</v>
       </c>
       <c r="D452" t="n">
-        <v>2064.1157</v>
+        <v>2148.8494</v>
       </c>
     </row>
     <row r="453">
       <c r="A453" t="n">
-        <v>-0.04380018099021812</v>
+        <v>1.215052042008604</v>
       </c>
       <c r="B453" t="n">
-        <v>0.22</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="C453" t="n">
-        <v>20.9417</v>
+        <v>20.0397</v>
       </c>
       <c r="D453" t="n">
-        <v>2062.5047</v>
+        <v>2153.3411</v>
       </c>
     </row>
     <row r="454">
       <c r="A454" t="n">
-        <v>-0.2241919997225872</v>
+        <v>-1.174767117073491</v>
       </c>
       <c r="B454" t="n">
-        <v>0.14</v>
+        <v>1.65</v>
       </c>
       <c r="C454" t="n">
-        <v>21.3076</v>
+        <v>19.2156</v>
       </c>
       <c r="D454" t="n">
-        <v>2061.6124</v>
+        <v>2152.3675</v>
       </c>
     </row>
     <row r="455">
       <c r="A455" t="n">
-        <v>-0.1355329820018712</v>
+        <v>-0.6143409366504022</v>
       </c>
       <c r="B455" t="n">
-        <v>-0.6599999999999999</v>
+        <v>-2.03</v>
       </c>
       <c r="C455" t="n">
-        <v>20.3531</v>
+        <v>19.3627</v>
       </c>
       <c r="D455" t="n">
-        <v>2060.9335</v>
+        <v>2153.8235</v>
       </c>
     </row>
     <row r="456">
       <c r="A456" t="n">
-        <v>0.02670893268257794</v>
+        <v>-3.071895707498597</v>
       </c>
       <c r="B456" t="n">
-        <v>1.08</v>
+        <v>0.22</v>
       </c>
       <c r="C456" t="n">
-        <v>21.5993</v>
+        <v>19.0525</v>
       </c>
       <c r="D456" t="n">
-        <v>2062.6408</v>
+        <v>2154.8413</v>
       </c>
     </row>
     <row r="457">
       <c r="A457" t="n">
-        <v>0.2439876257794446</v>
+        <v>0.1196405924675264</v>
       </c>
       <c r="B457" t="n">
-        <v>1.06</v>
+        <v>-1.44</v>
       </c>
       <c r="C457" t="n">
-        <v>20.4822</v>
+        <v>18.5878</v>
       </c>
       <c r="D457" t="n">
-        <v>2060.3031</v>
+        <v>2154.4243</v>
       </c>
     </row>
     <row r="458">
       <c r="A458" t="n">
-        <v>-0.003093388649214379</v>
+        <v>1.506055967997577</v>
       </c>
       <c r="B458" t="n">
-        <v>1.47</v>
+        <v>0.9099999999999999</v>
       </c>
       <c r="C458" t="n">
-        <v>19.3846</v>
+        <v>18.6672</v>
       </c>
       <c r="D458" t="n">
-        <v>2060.9187</v>
+        <v>2153.7862</v>
       </c>
     </row>
     <row r="459">
       <c r="A459" t="n">
-        <v>-0.1071378662459667</v>
+        <v>0.4893740987648056</v>
       </c>
       <c r="B459" t="n">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="C459" t="n">
-        <v>20.0817</v>
+        <v>19.1981</v>
       </c>
       <c r="D459" t="n">
-        <v>2062.1097</v>
+        <v>2154.6884</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="n">
-        <v>-0.1439925438807944</v>
+        <v>-0.3600964698559548</v>
       </c>
       <c r="B460" t="n">
-        <v>-0.55</v>
+        <v>-1.54</v>
       </c>
       <c r="C460" t="n">
-        <v>20.2669</v>
+        <v>18.9498</v>
       </c>
       <c r="D460" t="n">
-        <v>2064.263</v>
+        <v>2153.8439</v>
       </c>
     </row>
     <row r="461">
       <c r="A461" t="n">
-        <v>-0.3182412180055435</v>
+        <v>-0.3730653711051211</v>
       </c>
       <c r="B461" t="n">
-        <v>1.07</v>
+        <v>-1.8</v>
       </c>
       <c r="C461" t="n">
-        <v>22.6407</v>
+        <v>18.8356</v>
       </c>
       <c r="D461" t="n">
-        <v>2066.5425</v>
+        <v>2153.9428</v>
       </c>
     </row>
     <row r="462">
       <c r="A462" t="n">
-        <v>-0.4701480645567667</v>
+        <v>-0.179282375880952</v>
       </c>
       <c r="B462" t="n">
-        <v>-0.5700000000000001</v>
+        <v>-0.06</v>
       </c>
       <c r="C462" t="n">
-        <v>23.3146</v>
+        <v>18.6521</v>
       </c>
       <c r="D462" t="n">
-        <v>2066.6967</v>
+        <v>2153.9202</v>
       </c>
     </row>
     <row r="463">
       <c r="A463" t="n">
-        <v>-0.1846276878849214</v>
+        <v>-0.7637048251153008</v>
       </c>
       <c r="B463" t="n">
-        <v>0.11</v>
+        <v>1.12</v>
       </c>
       <c r="C463" t="n">
-        <v>23.0196</v>
+        <v>19.2154</v>
       </c>
       <c r="D463" t="n">
-        <v>2066.7966</v>
+        <v>2153.4354</v>
       </c>
     </row>
     <row r="464">
       <c r="A464" t="n">
-        <v>0.02601649340387062</v>
+        <v>0.4678895642882503</v>
       </c>
       <c r="B464" t="n">
-        <v>-0.39</v>
+        <v>0.4900000000000002</v>
       </c>
       <c r="C464" t="n">
-        <v>22.1757</v>
+        <v>20.1487</v>
       </c>
       <c r="D464" t="n">
-        <v>2067.963</v>
+        <v>2151.2073</v>
       </c>
     </row>
     <row r="465">
       <c r="A465" t="n">
-        <v>0.1404614434129877</v>
+        <v>0.2522378479169752</v>
       </c>
       <c r="B465" t="n">
-        <v>-0.6899999999999999</v>
+        <v>0.67</v>
       </c>
       <c r="C465" t="n">
-        <v>21.0351</v>
+        <v>19.1588</v>
       </c>
       <c r="D465" t="n">
-        <v>2067.3941</v>
+        <v>2153.5008</v>
       </c>
     </row>
     <row r="466">
       <c r="A466" t="n">
-        <v>0.1087607641664319</v>
+        <v>-0.1640314243961866</v>
       </c>
       <c r="B466" t="n">
-        <v>-0.33</v>
+        <v>-2.3</v>
       </c>
       <c r="C466" t="n">
-        <v>20.0121</v>
+        <v>19.7385</v>
       </c>
       <c r="D466" t="n">
-        <v>2067.8817</v>
+        <v>2153.9229</v>
       </c>
     </row>
     <row r="467">
       <c r="A467" t="n">
-        <v>0.4465428562726975</v>
+        <v>0.08781570065515421</v>
       </c>
       <c r="B467" t="n">
-        <v>1.09</v>
+        <v>-2.26</v>
       </c>
       <c r="C467" t="n">
-        <v>19.3263</v>
+        <v>21.3243</v>
       </c>
       <c r="D467" t="n">
-        <v>2065.8482</v>
+        <v>2152.5988</v>
       </c>
     </row>
     <row r="468">
       <c r="A468" t="n">
-        <v>-0.3495459327012254</v>
+        <v>-0.3096172205850479</v>
       </c>
       <c r="B468" t="n">
-        <v>-0.31</v>
+        <v>-1.6</v>
       </c>
       <c r="C468" t="n">
-        <v>18.4324</v>
+        <v>20.8267</v>
       </c>
       <c r="D468" t="n">
-        <v>2066.6414</v>
+        <v>2153.905</v>
       </c>
     </row>
     <row r="469">
       <c r="A469" t="n">
-        <v>-0.2787861407602096</v>
+        <v>0.321791887719883</v>
       </c>
       <c r="B469" t="n">
         <v>0.7200000000000001</v>
       </c>
       <c r="C469" t="n">
-        <v>18.9507</v>
+        <v>19.6992</v>
       </c>
       <c r="D469" t="n">
-        <v>2063.8818</v>
+        <v>2155.3896</v>
       </c>
     </row>
     <row r="470">
       <c r="A470" t="n">
-        <v>-0.2176591214010811</v>
+        <v>1.004391335357923</v>
       </c>
       <c r="B470" t="n">
-        <v>-0.05000000000000004</v>
+        <v>-0.33</v>
       </c>
       <c r="C470" t="n">
-        <v>18.2108</v>
+        <v>19.6251</v>
       </c>
       <c r="D470" t="n">
-        <v>2065.2853</v>
+        <v>2156.9371</v>
       </c>
     </row>
     <row r="471">
       <c r="A471" t="n">
-        <v>-0.6914171305773951</v>
+        <v>0.4822340643218251</v>
       </c>
       <c r="B471" t="n">
-        <v>-0.27</v>
+        <v>-0.96</v>
       </c>
       <c r="C471" t="n">
-        <v>18.1614</v>
+        <v>20.0645</v>
       </c>
       <c r="D471" t="n">
-        <v>2066.7008</v>
+        <v>2154.2431</v>
       </c>
     </row>
     <row r="472">
       <c r="A472" t="n">
-        <v>-0.2656545837763314</v>
+        <v>1.00796554295802</v>
       </c>
       <c r="B472" t="n">
-        <v>1.29</v>
+        <v>0.9700000000000001</v>
       </c>
       <c r="C472" t="n">
-        <v>18.2654</v>
+        <v>19.7379</v>
       </c>
       <c r="D472" t="n">
-        <v>2067.9459</v>
+        <v>2155.1209</v>
       </c>
     </row>
     <row r="473">
       <c r="A473" t="n">
-        <v>-0.446756008608257</v>
+        <v>0.6082317548586555</v>
       </c>
       <c r="B473" t="n">
-        <v>0.7200000000000001</v>
+        <v>-0.95</v>
       </c>
       <c r="C473" t="n">
-        <v>18.6501</v>
+        <v>20.5087</v>
       </c>
       <c r="D473" t="n">
-        <v>2069.2665</v>
+        <v>2156.393</v>
       </c>
     </row>
     <row r="474">
       <c r="A474" t="n">
-        <v>0.2774740801074352</v>
+        <v>-0.6134971207914579</v>
       </c>
       <c r="B474" t="n">
-        <v>-0.52</v>
+        <v>-0.51</v>
       </c>
       <c r="C474" t="n">
-        <v>18.0901</v>
+        <v>20.2865</v>
       </c>
       <c r="D474" t="n">
-        <v>2068.3517</v>
+        <v>2156.8718</v>
       </c>
     </row>
     <row r="475">
       <c r="A475" t="n">
-        <v>0.01105352057625784</v>
+        <v>1.235203463540031</v>
       </c>
       <c r="B475" t="n">
-        <v>-1.39</v>
+        <v>3.76</v>
       </c>
       <c r="C475" t="n">
-        <v>19.2189</v>
+        <v>20.5957</v>
       </c>
       <c r="D475" t="n">
-        <v>2071.9605</v>
+        <v>2158.9032</v>
       </c>
     </row>
     <row r="476">
       <c r="A476" t="n">
-        <v>0.278563603127503</v>
+        <v>1.27738079325826</v>
       </c>
       <c r="B476" t="n">
-        <v>0.6600000000000001</v>
+        <v>-1.03</v>
       </c>
       <c r="C476" t="n">
-        <v>18.9618</v>
+        <v>21.0608</v>
       </c>
       <c r="D476" t="n">
-        <v>2072.0228</v>
+        <v>2159.9605</v>
       </c>
     </row>
     <row r="477">
       <c r="A477" t="n">
-        <v>0.3331840637039899</v>
+        <v>0.07570308906793015</v>
       </c>
       <c r="B477" t="n">
-        <v>-0.09999999999999998</v>
+        <v>1.06</v>
       </c>
       <c r="C477" t="n">
-        <v>18.8503</v>
+        <v>20.8127</v>
       </c>
       <c r="D477" t="n">
-        <v>2073.9439</v>
+        <v>2159.49</v>
       </c>
     </row>
     <row r="478">
       <c r="A478" t="n">
-        <v>0.4160443016966528</v>
+        <v>-0.1149396786292648</v>
       </c>
       <c r="B478" t="n">
-        <v>1.44</v>
+        <v>-0.26</v>
       </c>
       <c r="C478" t="n">
-        <v>18.0434</v>
+        <v>20.6306</v>
       </c>
       <c r="D478" t="n">
-        <v>2072.4224</v>
+        <v>2161.5909</v>
       </c>
     </row>
     <row r="479">
       <c r="A479" t="n">
-        <v>-0.6378746291602755</v>
+        <v>-0.06479172636235087</v>
       </c>
       <c r="B479" t="n">
-        <v>-0.33</v>
+        <v>-0.7000000000000002</v>
       </c>
       <c r="C479" t="n">
-        <v>17.8474</v>
+        <v>20.7213</v>
       </c>
       <c r="D479" t="n">
-        <v>2075.1803</v>
+        <v>2163.0333</v>
       </c>
     </row>
     <row r="480">
       <c r="A480" t="n">
-        <v>-1.045323074644884</v>
+        <v>-1.96713835993255</v>
       </c>
       <c r="B480" t="n">
-        <v>0.96</v>
+        <v>-1.27</v>
       </c>
       <c r="C480" t="n">
-        <v>18.2024</v>
+        <v>20.9695</v>
       </c>
       <c r="D480" t="n">
-        <v>2076.1785</v>
+        <v>2162.4365</v>
       </c>
     </row>
     <row r="481">
       <c r="A481" t="n">
-        <v>-0.4008263535302978</v>
+        <v>-1.445072527632975</v>
       </c>
       <c r="B481" t="n">
-        <v>0.47</v>
+        <v>-0.36</v>
       </c>
       <c r="C481" t="n">
-        <v>18.638</v>
+        <v>20.76</v>
       </c>
       <c r="D481" t="n">
-        <v>2076.2973</v>
+        <v>2162.7248</v>
       </c>
     </row>
     <row r="482">
       <c r="A482" t="n">
-        <v>0.1132390390714216</v>
+        <v>-0.772635295014807</v>
       </c>
       <c r="B482" t="n">
-        <v>0.8400000000000001</v>
+        <v>1.09</v>
       </c>
       <c r="C482" t="n">
-        <v>18.6911</v>
+        <v>20.4</v>
       </c>
       <c r="D482" t="n">
-        <v>2079.6206</v>
+        <v>2162.5774</v>
       </c>
     </row>
     <row r="483">
       <c r="A483" t="n">
-        <v>-0.4609955751739857</v>
+        <v>-0.8108159231826944</v>
       </c>
       <c r="B483" t="n">
-        <v>0.03000000000000003</v>
+        <v>-0.51</v>
       </c>
       <c r="C483" t="n">
-        <v>19.7377</v>
+        <v>20.7713</v>
       </c>
       <c r="D483" t="n">
-        <v>2082.0284</v>
+        <v>2162.4135</v>
       </c>
     </row>
     <row r="484">
       <c r="A484" t="n">
-        <v>-0.1703907122824362</v>
+        <v>0.2535414712439878</v>
       </c>
       <c r="B484" t="n">
-        <v>-2.22</v>
+        <v>-1.28</v>
       </c>
       <c r="C484" t="n">
-        <v>20.3733</v>
+        <v>20.4008</v>
       </c>
       <c r="D484" t="n">
-        <v>2084.1957</v>
+        <v>2159.8973</v>
       </c>
     </row>
     <row r="485">
       <c r="A485" t="n">
-        <v>0.1886874957929412</v>
+        <v>-0.2157218240444554</v>
       </c>
       <c r="B485" t="n">
-        <v>0.9700000000000001</v>
+        <v>-2.01</v>
       </c>
       <c r="C485" t="n">
-        <v>20.3355</v>
+        <v>20.6215</v>
       </c>
       <c r="D485" t="n">
-        <v>2086.7012</v>
+        <v>2159.4371</v>
       </c>
     </row>
     <row r="486">
       <c r="A486" t="n">
-        <v>0.10568601414522</v>
+        <v>1.061812019407489</v>
       </c>
       <c r="B486" t="n">
-        <v>2.66</v>
+        <v>2.16</v>
       </c>
       <c r="C486" t="n">
-        <v>21.9662</v>
+        <v>21.4267</v>
       </c>
       <c r="D486" t="n">
-        <v>2088.2709</v>
+        <v>2158.0106</v>
       </c>
     </row>
     <row r="487">
       <c r="A487" t="n">
-        <v>-0.3165804150321213</v>
+        <v>0.1370912241837357</v>
       </c>
       <c r="B487" t="n">
-        <v>3.52</v>
+        <v>1.39</v>
       </c>
       <c r="C487" t="n">
-        <v>25.0629</v>
+        <v>19.9374</v>
       </c>
       <c r="D487" t="n">
-        <v>2091.6913</v>
+        <v>2158.5212</v>
       </c>
     </row>
     <row r="488">
       <c r="A488" t="n">
-        <v>0.3961409209090371</v>
+        <v>-0.06577305957482586</v>
       </c>
       <c r="B488" t="n">
-        <v>-0.05000000000000004</v>
+        <v>-1.75</v>
       </c>
       <c r="C488" t="n">
-        <v>25.0915</v>
+        <v>21.3949</v>
       </c>
       <c r="D488" t="n">
-        <v>2092.3248</v>
+        <v>2159.8591</v>
       </c>
     </row>
     <row r="489">
       <c r="A489" t="n">
-        <v>-0.1966894591458705</v>
+        <v>0.01224828225955025</v>
       </c>
       <c r="B489" t="n">
-        <v>1.35</v>
+        <v>-0.31</v>
       </c>
       <c r="C489" t="n">
-        <v>22.7964</v>
+        <v>20.5342</v>
       </c>
       <c r="D489" t="n">
-        <v>2090.0395</v>
+        <v>2160.0835</v>
       </c>
     </row>
     <row r="490">
       <c r="A490" t="n">
-        <v>-0.6721829486738981</v>
+        <v>0.5857749931326297</v>
       </c>
       <c r="B490" t="n">
-        <v>2.06</v>
+        <v>1.97</v>
       </c>
       <c r="C490" t="n">
-        <v>24.1206</v>
+        <v>19.4981</v>
       </c>
       <c r="D490" t="n">
-        <v>2094.4453</v>
+        <v>2159.1088</v>
       </c>
     </row>
     <row r="491">
       <c r="A491" t="n">
-        <v>-0.1372202593889626</v>
+        <v>1.248723862049884</v>
       </c>
       <c r="B491" t="n">
-        <v>-0.05999999999999994</v>
+        <v>4.7</v>
       </c>
       <c r="C491" t="n">
-        <v>23.8405</v>
+        <v>19.9064</v>
       </c>
       <c r="D491" t="n">
-        <v>2095.081</v>
+        <v>2158.0331</v>
       </c>
     </row>
     <row r="492">
       <c r="A492" t="n">
-        <v>-0.581629381297558</v>
+        <v>-0.08662583638472698</v>
       </c>
       <c r="B492" t="n">
-        <v>-1.5</v>
+        <v>0.34</v>
       </c>
       <c r="C492" t="n">
-        <v>23.457</v>
+        <v>20.2006</v>
       </c>
       <c r="D492" t="n">
-        <v>2094.2301</v>
+        <v>2157.4584</v>
       </c>
     </row>
     <row r="493">
       <c r="A493" t="n">
-        <v>-0.4953106059363625</v>
+        <v>0.2401132191068936</v>
       </c>
       <c r="B493" t="n">
-        <v>-0.15</v>
+        <v>3.24</v>
       </c>
       <c r="C493" t="n">
-        <v>21.6663</v>
+        <v>20.8416</v>
       </c>
       <c r="D493" t="n">
-        <v>2092.9745</v>
+        <v>2156.2186</v>
       </c>
     </row>
     <row r="494">
       <c r="A494" t="n">
-        <v>-0.1505116711534682</v>
+        <v>-0.0585591250253142</v>
       </c>
       <c r="B494" t="n">
-        <v>-1.07</v>
+        <v>-2.94</v>
       </c>
       <c r="C494" t="n">
-        <v>22.0351</v>
+        <v>21.0166</v>
       </c>
       <c r="D494" t="n">
-        <v>2093.3783</v>
+        <v>2156.8765</v>
       </c>
     </row>
     <row r="495">
       <c r="A495" t="n">
-        <v>0.2619818016970232</v>
+        <v>0.3214744700439279</v>
       </c>
       <c r="B495" t="n">
-        <v>-0.4900000000000001</v>
+        <v>1.58</v>
       </c>
       <c r="C495" t="n">
-        <v>22.2011</v>
+        <v>19.2122</v>
       </c>
       <c r="D495" t="n">
-        <v>2091.062</v>
+        <v>2157.4921</v>
       </c>
     </row>
     <row r="496">
       <c r="A496" t="n">
-        <v>-0.129769842018665</v>
+        <v>0.3931359821743836</v>
       </c>
       <c r="B496" t="n">
-        <v>-0.71</v>
+        <v>1.17</v>
       </c>
       <c r="C496" t="n">
-        <v>21.976</v>
+        <v>19.0389</v>
       </c>
       <c r="D496" t="n">
-        <v>2092.8105</v>
+        <v>2156.6024</v>
       </c>
     </row>
     <row r="497">
       <c r="A497" t="n">
-        <v>-0.0236326058191719</v>
+        <v>0.0681675891492762</v>
       </c>
       <c r="B497" t="n">
-        <v>-0.17</v>
+        <v>1.87</v>
       </c>
       <c r="C497" t="n">
-        <v>23.1673</v>
+        <v>18.8702</v>
       </c>
       <c r="D497" t="n">
-        <v>2096.501</v>
+        <v>2154.3634</v>
       </c>
     </row>
     <row r="498">
       <c r="A498" t="n">
-        <v>-0.1271296359331682</v>
+        <v>0.00898501558621978</v>
       </c>
       <c r="B498" t="n">
-        <v>0.24</v>
+        <v>-0.1000000000000001</v>
       </c>
       <c r="C498" t="n">
-        <v>22.1423</v>
+        <v>18.9627</v>
       </c>
       <c r="D498" t="n">
-        <v>2097.0782</v>
+        <v>2153.8666</v>
       </c>
     </row>
     <row r="499">
       <c r="A499" t="n">
-        <v>0.2477404285044179</v>
+        <v>-0.3927517022997375</v>
       </c>
       <c r="B499" t="n">
-        <v>2.31</v>
+        <v>-1.4</v>
       </c>
       <c r="C499" t="n">
-        <v>22.9036</v>
+        <v>18.7834</v>
       </c>
       <c r="D499" t="n">
-        <v>2098.3298</v>
+        <v>2153.8251</v>
       </c>
     </row>
     <row r="500">
       <c r="A500" t="n">
-        <v>-0.08376194695398823</v>
+        <v>0.2251380462909604</v>
       </c>
       <c r="B500" t="n">
-        <v>-0.3300000000000001</v>
+        <v>0.63</v>
       </c>
       <c r="C500" t="n">
-        <v>22.7349</v>
+        <v>18.4591</v>
       </c>
       <c r="D500" t="n">
-        <v>2093.1</v>
+        <v>2153.4279</v>
       </c>
     </row>
     <row r="501">
       <c r="A501" t="n">
-        <v>0.220788545250493</v>
+        <v>-0.142524192993187</v>
       </c>
       <c r="B501" t="n">
-        <v>0.07000000000000001</v>
+        <v>-3.06</v>
       </c>
       <c r="C501" t="n">
-        <v>22.242</v>
+        <v>19.4316</v>
       </c>
       <c r="D501" t="n">
-        <v>2093.0376</v>
+        <v>2151.4919</v>
       </c>
     </row>
   </sheetData>
